--- a/TES/Salariales/Nueva Escala 3210/Escala_Salarial_3210_Nueva.xlsx
+++ b/TES/Salariales/Nueva Escala 3210/Escala_Salarial_3210_Nueva.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Escala Salarial 3210" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Escala por correlacion" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detalle Plantilla 87" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metodologia y fuentes" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Escala Salarial 3210" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Escala por correlacion" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Detalle Plantilla 87" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Metodologia y fuentes" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Detalle Plantilla 87'!$A$1:$E$184</definedName>
@@ -645,7 +645,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generado el 27/10/2026. La columna G se alimenta del archivo “propuesta de plantilla por la resolucion 87.xls”. Montos en pesos cubanos (CUP).</t>
+          <t>Generado el 28/10/2026. La columna G se alimenta del archivo “propuesta de plantilla por la resolucion 87.xls”. Montos en pesos cubanos (CUP).</t>
         </is>
       </c>
     </row>

--- a/TES/Salariales/Nueva Escala 3210/Escala_Salarial_3210_Nueva.xlsx
+++ b/TES/Salariales/Nueva Escala 3210/Escala_Salarial_3210_Nueva.xlsx
@@ -11,9 +11,13 @@
     <sheet name="Escala por correlacion" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Detalle Plantilla 87" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Metodologia y fuentes" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Trazabilidad SHA-256" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Detalle Plantilla 87'!$A$1:$E$184</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Trazabilidad SHA-256'!$A$6:$G$12</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Trazabilidad SHA-256'!$1:$6</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Trazabilidad SHA-256'!$A$1:$G$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -26,7 +30,7 @@
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
     <numFmt numFmtId="166" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -82,8 +86,34 @@
       <color rgb="00000000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00536875"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -125,8 +155,18 @@
         <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAF0F4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5EE"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -148,11 +188,16 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <bottom style="hair">
+        <color rgb="00CBD5DC"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -256,6 +301,26 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -330,6 +395,22 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ManifiestoSHA256" displayName="ManifiestoSHA256" ref="A6:G12" headerRowCount="1">
+  <autoFilter ref="A6:G12"/>
+  <tableColumns count="7">
+    <tableColumn id="1" name="ID"/>
+    <tableColumn id="2" name="Fuente"/>
+    <tableColumn id="3" name="Ruta del repositorio"/>
+    <tableColumn id="4" name="Estado"/>
+    <tableColumn id="5" name="SHA-256 aprobado"/>
+    <tableColumn id="6" name="SHA-256 actual"/>
+    <tableColumn id="7" name="Tamaño (bytes)"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6907,4 +6988,339 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="76" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="68" customWidth="1" min="5" max="5"/>
+    <col width="68" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="35" t="inlineStr">
+        <is>
+          <t>TRAZABILIDAD DE FUENTES · CAPITAL HUMANO</t>
+        </is>
+      </c>
+      <c r="B1" s="35" t="n"/>
+      <c r="C1" s="35" t="n"/>
+      <c r="D1" s="35" t="n"/>
+      <c r="E1" s="35" t="n"/>
+      <c r="F1" s="35" t="n"/>
+      <c r="G1" s="35" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="36" t="inlineStr">
+        <is>
+          <t>Versión de la aplicación</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0.1.0-dev</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="36" t="inlineStr">
+        <is>
+          <t>Integridad del manifiesto</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>VERIFICADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="36" t="inlineStr">
+        <is>
+          <t>Verificación UTC</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-10-28T21:19:21+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="37" t="inlineStr">
+        <is>
+          <t>SHA-256 compara los bytes con el manifiesto versionado; no sustituye revisión normativa ni firma digital.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="38" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B6" s="38" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="C6" s="38" t="inlineStr">
+        <is>
+          <t>Ruta del repositorio</t>
+        </is>
+      </c>
+      <c r="D6" s="38" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="E6" s="38" t="inlineStr">
+        <is>
+          <t>SHA-256 aprobado</t>
+        </is>
+      </c>
+      <c r="F6" s="38" t="inlineStr">
+        <is>
+          <t>SHA-256 actual</t>
+        </is>
+      </c>
+      <c r="G6" s="38" t="inlineStr">
+        <is>
+          <t>Tamaño (bytes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="39" t="inlineStr">
+        <is>
+          <t>plantilla_res87</t>
+        </is>
+      </c>
+      <c r="B7" s="40" t="inlineStr">
+        <is>
+          <t>Plantilla de cargos · propuesta Resolución 87</t>
+        </is>
+      </c>
+      <c r="C7" s="40" t="inlineStr">
+        <is>
+          <t>Nueva Estructura de Plantilla/Organigrama/propuesta de plantilla por la resolucion 87.xls</t>
+        </is>
+      </c>
+      <c r="D7" s="41" t="inlineStr">
+        <is>
+          <t>VERIFICADA</t>
+        </is>
+      </c>
+      <c r="E7" s="42" t="inlineStr">
+        <is>
+          <t>02399d1abf33cb821829df57f146e9011488ed86a11e539c664a2114c7b8b6cc</t>
+        </is>
+      </c>
+      <c r="F7" s="42" t="inlineStr">
+        <is>
+          <t>02399d1abf33cb821829df57f146e9011488ed86a11e539c664a2114c7b8b6cc</t>
+        </is>
+      </c>
+      <c r="G7" s="39" t="n">
+        <v>2780672</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="39" t="inlineStr">
+        <is>
+          <t>escala_res29</t>
+        </is>
+      </c>
+      <c r="B8" s="40" t="inlineStr">
+        <is>
+          <t>Escala histórica · Resolución 29/2020</t>
+        </is>
+      </c>
+      <c r="C8" s="40" t="inlineStr">
+        <is>
+          <t>TES/Salariales/Escala 3210_OK.xlsx</t>
+        </is>
+      </c>
+      <c r="D8" s="41" t="inlineStr">
+        <is>
+          <t>VERIFICADA</t>
+        </is>
+      </c>
+      <c r="E8" s="42" t="inlineStr">
+        <is>
+          <t>fbf1764dd6d77a5845dbbd01a7453e119915feb798dc7b43f25e431f67217d01</t>
+        </is>
+      </c>
+      <c r="F8" s="42" t="inlineStr">
+        <is>
+          <t>fbf1764dd6d77a5845dbbd01a7453e119915feb798dc7b43f25e431f67217d01</t>
+        </is>
+      </c>
+      <c r="G8" s="39" t="n">
+        <v>13968</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="39" t="inlineStr">
+        <is>
+          <t>gaceta_2026</t>
+        </is>
+      </c>
+      <c r="B9" s="40" t="inlineStr">
+        <is>
+          <t>Gaceta Oficial · Resoluciones 14/2026 y 15/2026</t>
+        </is>
+      </c>
+      <c r="C9" s="40" t="inlineStr">
+        <is>
+          <t>TES/Salariales/goc-2026-o60.pdf</t>
+        </is>
+      </c>
+      <c r="D9" s="41" t="inlineStr">
+        <is>
+          <t>VERIFICADA</t>
+        </is>
+      </c>
+      <c r="E9" s="42" t="inlineStr">
+        <is>
+          <t>7dfe261ae1db5de5ceee1e9ebe141693a5a1ca474809158960c6bd94a2c0a1e1</t>
+        </is>
+      </c>
+      <c r="F9" s="42" t="inlineStr">
+        <is>
+          <t>7dfe261ae1db5de5ceee1e9ebe141693a5a1ca474809158960c6bd94a2c0a1e1</t>
+        </is>
+      </c>
+      <c r="G9" s="39" t="n">
+        <v>1104320</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="39" t="inlineStr">
+        <is>
+          <t>motor_calculo</t>
+        </is>
+      </c>
+      <c r="B10" s="40" t="inlineStr">
+        <is>
+          <t>Código de extracción y cálculo</t>
+        </is>
+      </c>
+      <c r="C10" s="40" t="inlineStr">
+        <is>
+          <t>TES/Salariales/Nueva Escala 3210/generar_escala.py</t>
+        </is>
+      </c>
+      <c r="D10" s="41" t="inlineStr">
+        <is>
+          <t>VERIFICADA</t>
+        </is>
+      </c>
+      <c r="E10" s="42" t="inlineStr">
+        <is>
+          <t>c41ad5dfcdabc308705d391cca7309377ba1dd7ec855c06bfe49b28a32c272e8</t>
+        </is>
+      </c>
+      <c r="F10" s="42" t="inlineStr">
+        <is>
+          <t>c41ad5dfcdabc308705d391cca7309377ba1dd7ec855c06bfe49b28a32c272e8</t>
+        </is>
+      </c>
+      <c r="G10" s="39" t="n">
+        <v>37562</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="39" t="inlineStr">
+        <is>
+          <t>interfaz_app</t>
+        </is>
+      </c>
+      <c r="B11" s="40" t="inlineStr">
+        <is>
+          <t>Código de la aplicación y exportadores</t>
+        </is>
+      </c>
+      <c r="C11" s="40" t="inlineStr">
+        <is>
+          <t>TES/Salariales/Nueva Escala 3210/app_escala.py</t>
+        </is>
+      </c>
+      <c r="D11" s="41" t="inlineStr">
+        <is>
+          <t>VERIFICADA</t>
+        </is>
+      </c>
+      <c r="E11" s="42" t="inlineStr">
+        <is>
+          <t>710421e5c5d23bf9ab5626b37c60f164720012678a82454c98fad5aa0ac900cb</t>
+        </is>
+      </c>
+      <c r="F11" s="42" t="inlineStr">
+        <is>
+          <t>710421e5c5d23bf9ab5626b37c60f164720012678a82454c98fad5aa0ac900cb</t>
+        </is>
+      </c>
+      <c r="G11" s="39" t="n">
+        <v>39479</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="39" t="inlineStr">
+        <is>
+          <t>actualizador_manifest</t>
+        </is>
+      </c>
+      <c r="B12" s="40" t="inlineStr">
+        <is>
+          <t>Herramienta de actualización del manifiesto</t>
+        </is>
+      </c>
+      <c r="C12" s="40" t="inlineStr">
+        <is>
+          <t>tools/actualizar_manifiesto_fuentes.py</t>
+        </is>
+      </c>
+      <c r="D12" s="41" t="inlineStr">
+        <is>
+          <t>VERIFICADA</t>
+        </is>
+      </c>
+      <c r="E12" s="42" t="inlineStr">
+        <is>
+          <t>6b820ded8d9c01129c0d5fbfa223e43039be6126db75809c15d5ea675f2c5e85</t>
+        </is>
+      </c>
+      <c r="F12" s="42" t="inlineStr">
+        <is>
+          <t>6b820ded8d9c01129c0d5fbfa223e43039be6126db75809c15d5ea675f2c5e85</t>
+        </is>
+      </c>
+      <c r="G12" s="39" t="n">
+        <v>865</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A6:G12"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A5:G5"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="2"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/TES/Salariales/Nueva Escala 3210/Escala_Salarial_3210_Nueva.xlsx
+++ b/TES/Salariales/Nueva Escala 3210/Escala_Salarial_3210_Nueva.xlsx
@@ -7053,7 +7053,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-28T21:19:21+00:00</t>
+          <t>2026-10-28T21:28:01+00:00</t>
         </is>
       </c>
     </row>
@@ -7264,16 +7264,16 @@
       </c>
       <c r="E11" s="42" t="inlineStr">
         <is>
-          <t>710421e5c5d23bf9ab5626b37c60f164720012678a82454c98fad5aa0ac900cb</t>
+          <t>a23da7c8ab2f8da01dc68cdadb8509874137c86b8fb1b8ad7f7587b591a6edae</t>
         </is>
       </c>
       <c r="F11" s="42" t="inlineStr">
         <is>
-          <t>710421e5c5d23bf9ab5626b37c60f164720012678a82454c98fad5aa0ac900cb</t>
+          <t>a23da7c8ab2f8da01dc68cdadb8509874137c86b8fb1b8ad7f7587b591a6edae</t>
         </is>
       </c>
       <c r="G11" s="39" t="n">
-        <v>39479</v>
+        <v>40079</v>
       </c>
     </row>
     <row r="12">

--- a/TES/Salariales/Nueva Escala 3210/Escala_Salarial_3210_Nueva.xlsx
+++ b/TES/Salariales/Nueva Escala 3210/Escala_Salarial_3210_Nueva.xlsx
@@ -7053,7 +7053,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-28T21:28:01+00:00</t>
+          <t>2026-10-28T22:03:38+00:00</t>
         </is>
       </c>
     </row>
@@ -7264,16 +7264,16 @@
       </c>
       <c r="E11" s="42" t="inlineStr">
         <is>
-          <t>a23da7c8ab2f8da01dc68cdadb8509874137c86b8fb1b8ad7f7587b591a6edae</t>
+          <t>ee25477b30fad036b861ebc1f46f21922de217576a95200ed27b836a0d6421de</t>
         </is>
       </c>
       <c r="F11" s="42" t="inlineStr">
         <is>
-          <t>a23da7c8ab2f8da01dc68cdadb8509874137c86b8fb1b8ad7f7587b591a6edae</t>
+          <t>ee25477b30fad036b861ebc1f46f21922de217576a95200ed27b836a0d6421de</t>
         </is>
       </c>
       <c r="G11" s="39" t="n">
-        <v>40079</v>
+        <v>51698</v>
       </c>
     </row>
     <row r="12">

--- a/TES/Salariales/Nueva Escala 3210/Escala_Salarial_3210_Nueva.xlsx
+++ b/TES/Salariales/Nueva Escala 3210/Escala_Salarial_3210_Nueva.xlsx
@@ -14,7 +14,7 @@
     <sheet name="Trazabilidad SHA-256" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Detalle Plantilla 87'!$A$1:$E$184</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Detalle Plantilla 87'!$A$1:$F$184</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Trazabilidad SHA-256'!$A$6:$G$12</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Trazabilidad SHA-256'!$1:$6</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Trazabilidad SHA-256'!$A$1:$G$12</definedName>
@@ -2635,4254 +2635,4809 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E184"/>
+  <dimension ref="A1:F184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="52" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
+          <t>Id.</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
           <t>Hoja fuente</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Fila</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Cargo</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Grupo propuesto</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Salario propuesto (CUP)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="26" t="inlineStr">
+      <c r="A2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="26" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
       </c>
-      <c r="B2" s="7" t="n">
+      <c r="C2" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="C2" s="26" t="inlineStr">
+      <c r="D2" s="26" t="inlineStr">
         <is>
           <t>Director</t>
         </is>
       </c>
-      <c r="D2" s="27" t="inlineStr">
+      <c r="E2" s="27" t="inlineStr">
         <is>
           <t>XVIII</t>
         </is>
       </c>
-      <c r="E2" s="28" t="n">
+      <c r="F2" s="28" t="n">
         <v>9072</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="29" t="inlineStr">
+      <c r="A3" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="29" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
       </c>
-      <c r="B3" s="30" t="n">
+      <c r="C3" s="30" t="n">
         <v>21</v>
       </c>
-      <c r="C3" s="29" t="inlineStr">
+      <c r="D3" s="29" t="inlineStr">
         <is>
           <t>Director Adjunto</t>
         </is>
       </c>
-      <c r="D3" s="31" t="inlineStr">
+      <c r="E3" s="31" t="inlineStr">
         <is>
           <t>XVII</t>
         </is>
       </c>
-      <c r="E3" s="32" t="n">
+      <c r="F3" s="32" t="n">
         <v>8400</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="26" t="inlineStr">
+      <c r="A4" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="26" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
       </c>
-      <c r="B4" s="7" t="n">
+      <c r="C4" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="C4" s="26" t="inlineStr">
+      <c r="D4" s="26" t="inlineStr">
         <is>
           <t>Especialista  en Cuadro</t>
         </is>
       </c>
-      <c r="D4" s="27" t="inlineStr">
+      <c r="E4" s="27" t="inlineStr">
         <is>
           <t>XIV</t>
         </is>
       </c>
-      <c r="E4" s="28" t="n">
+      <c r="F4" s="28" t="n">
         <v>6668</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="29" t="inlineStr">
+      <c r="A5" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
       </c>
-      <c r="B5" s="30" t="n">
+      <c r="C5" s="30" t="n">
         <v>23</v>
       </c>
-      <c r="C5" s="29" t="inlineStr">
+      <c r="D5" s="29" t="inlineStr">
         <is>
           <t>Inspector  Sup. del Servicio Turistico</t>
         </is>
       </c>
-      <c r="D5" s="31" t="inlineStr">
+      <c r="E5" s="31" t="inlineStr">
         <is>
           <t>XIV</t>
         </is>
       </c>
-      <c r="E5" s="32" t="n">
+      <c r="F5" s="32" t="n">
         <v>6668</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="26" t="inlineStr">
+      <c r="A6" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="26" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n">
+      <c r="C6" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="C6" s="26" t="inlineStr">
+      <c r="D6" s="26" t="inlineStr">
         <is>
           <t>Chofer vehiculos ligeros</t>
         </is>
       </c>
-      <c r="D6" s="27" t="inlineStr">
+      <c r="E6" s="27" t="inlineStr">
         <is>
           <t>VIII</t>
         </is>
       </c>
-      <c r="E6" s="28" t="n">
+      <c r="F6" s="28" t="n">
         <v>4402</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="29" t="inlineStr">
+      <c r="A7" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
       </c>
-      <c r="B7" s="30" t="n">
+      <c r="C7" s="30" t="n">
         <v>25</v>
       </c>
-      <c r="C7" s="29" t="inlineStr">
+      <c r="D7" s="29" t="inlineStr">
         <is>
           <t>Secretaria</t>
         </is>
       </c>
-      <c r="D7" s="31" t="inlineStr">
+      <c r="E7" s="31" t="inlineStr">
         <is>
           <t>XI</t>
         </is>
       </c>
-      <c r="E7" s="32" t="n">
+      <c r="F7" s="32" t="n">
         <v>5343</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="26" t="inlineStr">
+      <c r="A8" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="26" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n">
+      <c r="C8" s="7" t="n">
         <v>26</v>
       </c>
-      <c r="C8" s="26" t="inlineStr">
+      <c r="D8" s="26" t="inlineStr">
         <is>
           <t>Asesor Juridico</t>
         </is>
       </c>
-      <c r="D8" s="27" t="inlineStr">
+      <c r="E8" s="27" t="inlineStr">
         <is>
           <t>XIV</t>
         </is>
       </c>
-      <c r="E8" s="28" t="n">
+      <c r="F8" s="28" t="n">
         <v>6668</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="29" t="inlineStr">
+      <c r="A9" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="29" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
       </c>
-      <c r="B9" s="30" t="n">
+      <c r="C9" s="30" t="n">
         <v>27</v>
       </c>
-      <c r="C9" s="29" t="inlineStr">
+      <c r="D9" s="29" t="inlineStr">
         <is>
           <t>Especialista en Informatica y comunic.</t>
         </is>
       </c>
-      <c r="D9" s="31" t="inlineStr">
+      <c r="E9" s="31" t="inlineStr">
         <is>
           <t>XIV</t>
         </is>
       </c>
-      <c r="E9" s="32" t="n">
+      <c r="F9" s="32" t="n">
         <v>6668</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="26" t="inlineStr">
+      <c r="A10" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="26" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
       </c>
-      <c r="B10" s="7" t="n">
+      <c r="C10" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="C10" s="26" t="inlineStr">
+      <c r="D10" s="26" t="inlineStr">
         <is>
           <t>Auditor Adjunto</t>
         </is>
       </c>
-      <c r="D10" s="27" t="inlineStr">
+      <c r="E10" s="27" t="inlineStr">
         <is>
           <t>XIV</t>
         </is>
       </c>
-      <c r="E10" s="28" t="n">
+      <c r="F10" s="28" t="n">
         <v>6668</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="29" t="inlineStr">
+      <c r="A11" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="29" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
       </c>
-      <c r="B11" s="30" t="n">
+      <c r="C11" s="30" t="n">
         <v>29</v>
       </c>
-      <c r="C11" s="29" t="inlineStr">
+      <c r="D11" s="29" t="inlineStr">
         <is>
           <t>Especialista Gestion Documental</t>
         </is>
       </c>
-      <c r="D11" s="31" t="inlineStr">
+      <c r="E11" s="31" t="inlineStr">
         <is>
           <t>XIV</t>
         </is>
       </c>
-      <c r="E11" s="32" t="n">
+      <c r="F11" s="32" t="n">
         <v>6668</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="26" t="inlineStr">
+      <c r="A12" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="26" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
       </c>
-      <c r="B12" s="7" t="n">
+      <c r="C12" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="C12" s="26" t="inlineStr">
+      <c r="D12" s="26" t="inlineStr">
         <is>
           <t>Encargado de Actividades Generales</t>
         </is>
       </c>
-      <c r="D12" s="27" t="inlineStr">
+      <c r="E12" s="27" t="inlineStr">
         <is>
           <t>XI</t>
         </is>
       </c>
-      <c r="E12" s="28" t="n">
+      <c r="F12" s="28" t="n">
         <v>5343</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="29" t="inlineStr">
+      <c r="A13" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="29" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
       </c>
-      <c r="B13" s="30" t="n">
+      <c r="C13" s="30" t="n">
         <v>31</v>
       </c>
-      <c r="C13" s="29" t="inlineStr">
+      <c r="D13" s="29" t="inlineStr">
         <is>
           <t>Encargado de Recepción y Pizarra Telefonica</t>
         </is>
       </c>
-      <c r="D13" s="31" t="inlineStr">
+      <c r="E13" s="31" t="inlineStr">
         <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="E13" s="32" t="n">
+      <c r="F13" s="32" t="n">
         <v>3918</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="26" t="inlineStr">
+      <c r="A14" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="26" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
       </c>
-      <c r="B14" s="7" t="n">
+      <c r="C14" s="7" t="n">
         <v>32</v>
       </c>
-      <c r="C14" s="26" t="inlineStr">
+      <c r="D14" s="26" t="inlineStr">
         <is>
           <t>Auxiliar General de Servicios</t>
         </is>
       </c>
-      <c r="D14" s="27" t="inlineStr">
+      <c r="E14" s="27" t="inlineStr">
         <is>
           <t>VII</t>
         </is>
       </c>
-      <c r="E14" s="28" t="n">
+      <c r="F14" s="28" t="n">
         <v>4153</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="29" t="inlineStr">
+      <c r="A15" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="29" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
       </c>
-      <c r="B15" s="30" t="n">
+      <c r="C15" s="30" t="n">
         <v>33</v>
       </c>
-      <c r="C15" s="29" t="inlineStr">
+      <c r="D15" s="29" t="inlineStr">
         <is>
           <t>Operario de mantenimientos y servicio tecnicos</t>
         </is>
       </c>
-      <c r="D15" s="31" t="inlineStr">
+      <c r="E15" s="31" t="inlineStr">
         <is>
           <t>VII</t>
         </is>
       </c>
-      <c r="E15" s="32" t="n">
+      <c r="F15" s="32" t="n">
         <v>4153</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="26" t="inlineStr">
+      <c r="A16" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="26" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
       </c>
-      <c r="B16" s="7" t="n">
+      <c r="C16" s="7" t="n">
         <v>34</v>
       </c>
-      <c r="C16" s="26" t="inlineStr">
+      <c r="D16" s="26" t="inlineStr">
         <is>
           <t>Oficial Operativo Centro Direcc.</t>
         </is>
       </c>
-      <c r="D16" s="27" t="inlineStr">
+      <c r="E16" s="27" t="inlineStr">
         <is>
           <t>XI</t>
         </is>
       </c>
-      <c r="E16" s="28" t="n">
+      <c r="F16" s="28" t="n">
         <v>5343</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="29" t="inlineStr">
+      <c r="A17" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="29" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
       </c>
-      <c r="B17" s="30" t="n">
+      <c r="C17" s="30" t="n">
         <v>36</v>
       </c>
-      <c r="C17" s="29" t="inlineStr">
+      <c r="D17" s="29" t="inlineStr">
         <is>
           <t>Jefe Dpto. Seg. Defensa y Proteccion</t>
         </is>
       </c>
-      <c r="D17" s="31" t="inlineStr">
+      <c r="E17" s="31" t="inlineStr">
         <is>
           <t>XV</t>
         </is>
       </c>
-      <c r="E17" s="32" t="n">
+      <c r="F17" s="32" t="n">
         <v>7201</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="26" t="inlineStr">
+      <c r="A18" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="26" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
       </c>
-      <c r="B18" s="7" t="n">
+      <c r="C18" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="C18" s="26" t="inlineStr">
+      <c r="D18" s="26" t="inlineStr">
         <is>
           <t>Agentes de Seguridad y Protección</t>
         </is>
       </c>
-      <c r="D18" s="27" t="inlineStr">
+      <c r="E18" s="27" t="inlineStr">
         <is>
           <t>VIII</t>
         </is>
       </c>
-      <c r="E18" s="28" t="n">
+      <c r="F18" s="28" t="n">
         <v>4402</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="29" t="inlineStr">
+      <c r="A19" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="29" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
       </c>
-      <c r="B19" s="30" t="n">
+      <c r="C19" s="30" t="n">
         <v>39</v>
       </c>
-      <c r="C19" s="29" t="inlineStr">
+      <c r="D19" s="29" t="inlineStr">
         <is>
           <t>Director Contable Financiero</t>
         </is>
       </c>
-      <c r="D19" s="31" t="inlineStr">
+      <c r="E19" s="31" t="inlineStr">
         <is>
           <t>XVI</t>
         </is>
       </c>
-      <c r="E19" s="32" t="n">
+      <c r="F19" s="32" t="n">
         <v>7777</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="26" t="inlineStr">
+      <c r="A20" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="26" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
       </c>
-      <c r="B20" s="7" t="n">
+      <c r="C20" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="C20" s="26" t="inlineStr">
+      <c r="D20" s="26" t="inlineStr">
         <is>
           <t>Tecnico en Gestión Económica</t>
         </is>
       </c>
-      <c r="D20" s="27" t="inlineStr">
+      <c r="E20" s="27" t="inlineStr">
         <is>
           <t>XII</t>
         </is>
       </c>
-      <c r="E20" s="28" t="n">
+      <c r="F20" s="28" t="n">
         <v>5770</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="29" t="inlineStr">
+      <c r="A21" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="29" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
       </c>
-      <c r="B21" s="30" t="n">
+      <c r="C21" s="30" t="n">
         <v>41</v>
       </c>
-      <c r="C21" s="29" t="inlineStr">
+      <c r="D21" s="29" t="inlineStr">
         <is>
           <t>Especialista en Gestion Económico</t>
         </is>
       </c>
-      <c r="D21" s="31" t="inlineStr">
+      <c r="E21" s="31" t="inlineStr">
         <is>
           <t>XIV</t>
         </is>
       </c>
-      <c r="E21" s="32" t="n">
+      <c r="F21" s="32" t="n">
         <v>6668</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="26" t="inlineStr">
+      <c r="A22" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="26" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
       </c>
-      <c r="B22" s="7" t="n">
+      <c r="C22" s="7" t="n">
         <v>43</v>
       </c>
-      <c r="C22" s="26" t="inlineStr">
+      <c r="D22" s="26" t="inlineStr">
         <is>
           <t>Director de Capital Humano y Perfeccionamiento Empresarial</t>
         </is>
       </c>
-      <c r="D22" s="27" t="inlineStr">
+      <c r="E22" s="27" t="inlineStr">
         <is>
           <t>XVI</t>
         </is>
       </c>
-      <c r="E22" s="28" t="n">
+      <c r="F22" s="28" t="n">
         <v>7777</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="29" t="inlineStr">
+      <c r="A23" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="29" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
       </c>
-      <c r="B23" s="30" t="n">
+      <c r="C23" s="30" t="n">
         <v>44</v>
       </c>
-      <c r="C23" s="29" t="inlineStr">
+      <c r="D23" s="29" t="inlineStr">
         <is>
           <t>Especialista en Gestion de Capital  Humanos</t>
         </is>
       </c>
-      <c r="D23" s="31" t="inlineStr">
+      <c r="E23" s="31" t="inlineStr">
         <is>
           <t>XIV</t>
         </is>
       </c>
-      <c r="E23" s="32" t="n">
+      <c r="F23" s="32" t="n">
         <v>6668</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="26" t="inlineStr">
+      <c r="A24" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="26" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
       </c>
-      <c r="B24" s="7" t="n">
+      <c r="C24" s="7" t="n">
         <v>46</v>
       </c>
-      <c r="C24" s="26" t="inlineStr">
+      <c r="D24" s="26" t="inlineStr">
         <is>
           <t>Director de Operaciones y Calidad</t>
         </is>
       </c>
-      <c r="D24" s="27" t="inlineStr">
+      <c r="E24" s="27" t="inlineStr">
         <is>
           <t>XVI</t>
         </is>
       </c>
-      <c r="E24" s="28" t="n">
+      <c r="F24" s="28" t="n">
         <v>7777</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="29" t="inlineStr">
+      <c r="A25" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="29" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
       </c>
-      <c r="B25" s="30" t="n">
+      <c r="C25" s="30" t="n">
         <v>47</v>
       </c>
-      <c r="C25" s="29" t="inlineStr">
+      <c r="D25" s="29" t="inlineStr">
         <is>
           <t>Especialista de Calidad</t>
         </is>
       </c>
-      <c r="D25" s="31" t="inlineStr">
+      <c r="E25" s="31" t="inlineStr">
         <is>
           <t>XIV</t>
         </is>
       </c>
-      <c r="E25" s="32" t="n">
+      <c r="F25" s="32" t="n">
         <v>6668</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="26" t="inlineStr">
+      <c r="A26" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="26" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
       </c>
-      <c r="B26" s="7" t="n">
+      <c r="C26" s="7" t="n">
         <v>48</v>
       </c>
-      <c r="C26" s="26" t="inlineStr">
+      <c r="D26" s="26" t="inlineStr">
         <is>
           <t>Espècialista Recreación y Animacion</t>
         </is>
       </c>
-      <c r="D26" s="27" t="inlineStr">
+      <c r="E26" s="27" t="inlineStr">
         <is>
           <t>XIV</t>
         </is>
       </c>
-      <c r="E26" s="28" t="n">
+      <c r="F26" s="28" t="n">
         <v>6668</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="29" t="inlineStr">
+      <c r="A27" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="29" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
       </c>
-      <c r="B27" s="30" t="n">
+      <c r="C27" s="30" t="n">
         <v>49</v>
       </c>
-      <c r="C27" s="29" t="inlineStr">
+      <c r="D27" s="29" t="inlineStr">
         <is>
           <t>Especialista en Alimentos y Bebidas</t>
         </is>
       </c>
-      <c r="D27" s="31" t="inlineStr">
+      <c r="E27" s="31" t="inlineStr">
         <is>
           <t>XIV</t>
         </is>
       </c>
-      <c r="E27" s="32" t="n">
+      <c r="F27" s="32" t="n">
         <v>6668</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="26" t="inlineStr">
+      <c r="A28" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="26" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
       </c>
-      <c r="B28" s="7" t="n">
+      <c r="C28" s="7" t="n">
         <v>51</v>
       </c>
-      <c r="C28" s="26" t="inlineStr">
+      <c r="D28" s="26" t="inlineStr">
         <is>
           <t>Director Comercial</t>
         </is>
       </c>
-      <c r="D28" s="27" t="inlineStr">
+      <c r="E28" s="27" t="inlineStr">
         <is>
           <t>XV</t>
         </is>
       </c>
-      <c r="E28" s="28" t="n">
+      <c r="F28" s="28" t="n">
         <v>7777</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="29" t="inlineStr">
+      <c r="A29" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="29" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
       </c>
-      <c r="B29" s="30" t="n">
+      <c r="C29" s="30" t="n">
         <v>52</v>
       </c>
-      <c r="C29" s="29" t="inlineStr">
+      <c r="D29" s="29" t="inlineStr">
         <is>
           <t>Especialista  en Comercialización del Producto Turístico</t>
         </is>
       </c>
-      <c r="D29" s="31" t="inlineStr">
+      <c r="E29" s="31" t="inlineStr">
         <is>
           <t>XIV</t>
         </is>
       </c>
-      <c r="E29" s="32" t="n">
+      <c r="F29" s="32" t="n">
         <v>6668</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="26" t="inlineStr">
+      <c r="A30" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="26" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
       </c>
-      <c r="B30" s="7" t="n">
+      <c r="C30" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="C30" s="26" t="inlineStr">
+      <c r="D30" s="26" t="inlineStr">
         <is>
           <t>Promotor de Ventas e Información turistica</t>
         </is>
       </c>
-      <c r="D30" s="27" t="inlineStr">
+      <c r="E30" s="27" t="inlineStr">
         <is>
           <t>IX</t>
         </is>
       </c>
-      <c r="E30" s="28" t="n">
+      <c r="F30" s="28" t="n">
         <v>4666</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="29" t="inlineStr">
+      <c r="A31" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="29" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
       </c>
-      <c r="B31" s="30" t="n">
+      <c r="C31" s="30" t="n">
         <v>55</v>
       </c>
-      <c r="C31" s="29" t="inlineStr">
+      <c r="D31" s="29" t="inlineStr">
         <is>
           <t>Director de Inversiones,Logistica y Servicios Tecnicos</t>
         </is>
       </c>
-      <c r="D31" s="31" t="inlineStr">
+      <c r="E31" s="31" t="inlineStr">
         <is>
           <t>XVI</t>
         </is>
       </c>
-      <c r="E31" s="32" t="n">
+      <c r="F31" s="32" t="n">
         <v>7777</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="26" t="inlineStr">
+      <c r="A32" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="26" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
       </c>
-      <c r="B32" s="7" t="n">
+      <c r="C32" s="7" t="n">
         <v>56</v>
       </c>
-      <c r="C32" s="26" t="inlineStr">
+      <c r="D32" s="26" t="inlineStr">
         <is>
           <t>Tecnico  de Transporte Automotor</t>
         </is>
       </c>
-      <c r="D32" s="27" t="inlineStr">
+      <c r="E32" s="27" t="inlineStr">
         <is>
           <t>XII</t>
         </is>
       </c>
-      <c r="E32" s="28" t="n">
+      <c r="F32" s="28" t="n">
         <v>5770</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="29" t="inlineStr">
+      <c r="A33" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="29" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
       </c>
-      <c r="B33" s="30" t="n">
+      <c r="C33" s="30" t="n">
         <v>57</v>
       </c>
-      <c r="C33" s="29" t="inlineStr">
+      <c r="D33" s="29" t="inlineStr">
         <is>
           <t>Especialista B en Ahorro y Uso Racional de la Energía</t>
         </is>
       </c>
-      <c r="D33" s="31" t="inlineStr">
+      <c r="E33" s="31" t="inlineStr">
         <is>
           <t>XIV</t>
         </is>
       </c>
-      <c r="E33" s="32" t="n">
+      <c r="F33" s="32" t="n">
         <v>6668</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="26" t="inlineStr">
+      <c r="A34" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="26" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
       </c>
-      <c r="B34" s="7" t="n">
+      <c r="C34" s="7" t="n">
         <v>58</v>
       </c>
-      <c r="C34" s="26" t="inlineStr">
+      <c r="D34" s="26" t="inlineStr">
         <is>
           <t>Chofer  Vehiculos de Carga</t>
         </is>
       </c>
-      <c r="D34" s="27" t="inlineStr">
+      <c r="E34" s="27" t="inlineStr">
         <is>
           <t>IX</t>
         </is>
       </c>
-      <c r="E34" s="28" t="n">
+      <c r="F34" s="28" t="n">
         <v>4666</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="29" t="inlineStr">
+      <c r="A35" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="29" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
       </c>
-      <c r="B35" s="30" t="n">
+      <c r="C35" s="30" t="n">
         <v>59</v>
       </c>
-      <c r="C35" s="29" t="inlineStr">
+      <c r="D35" s="29" t="inlineStr">
         <is>
           <t>Comprador</t>
         </is>
       </c>
-      <c r="D35" s="31" t="inlineStr">
+      <c r="E35" s="31" t="inlineStr">
         <is>
           <t>XI</t>
         </is>
       </c>
-      <c r="E35" s="32" t="n">
+      <c r="F35" s="32" t="n">
         <v>5343</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="26" t="inlineStr">
+      <c r="A36" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="26" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
       </c>
-      <c r="B36" s="7" t="n">
+      <c r="C36" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="C36" s="26" t="inlineStr">
+      <c r="D36" s="26" t="inlineStr">
         <is>
           <t>Encargado de Almacén</t>
         </is>
       </c>
-      <c r="D36" s="27" t="inlineStr">
+      <c r="E36" s="27" t="inlineStr">
         <is>
           <t>VIII</t>
         </is>
       </c>
-      <c r="E36" s="28" t="n">
+      <c r="F36" s="28" t="n">
         <v>4402</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="29" t="inlineStr">
+      <c r="A37" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="29" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
       </c>
-      <c r="B37" s="30" t="n">
+      <c r="C37" s="30" t="n">
         <v>61</v>
       </c>
-      <c r="C37" s="29" t="inlineStr">
+      <c r="D37" s="29" t="inlineStr">
         <is>
           <t>Dependiente de  Almacén</t>
         </is>
       </c>
-      <c r="D37" s="31" t="inlineStr">
+      <c r="E37" s="31" t="inlineStr">
         <is>
           <t>VII</t>
         </is>
       </c>
-      <c r="E37" s="32" t="n">
+      <c r="F37" s="32" t="n">
         <v>4153</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="26" t="inlineStr">
+      <c r="A38" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="26" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
       </c>
-      <c r="B38" s="7" t="n">
+      <c r="C38" s="7" t="n">
         <v>63</v>
       </c>
-      <c r="C38" s="26" t="inlineStr">
+      <c r="D38" s="26" t="inlineStr">
         <is>
           <t>Espec. en Desarr. De programa Turist. Inversiones</t>
         </is>
       </c>
-      <c r="D38" s="27" t="inlineStr">
+      <c r="E38" s="27" t="inlineStr">
         <is>
           <t>XIV</t>
         </is>
       </c>
-      <c r="E38" s="28" t="n">
+      <c r="F38" s="28" t="n">
         <v>6668</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="29" t="inlineStr">
+      <c r="A39" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="29" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
       </c>
-      <c r="B39" s="30" t="n">
+      <c r="C39" s="30" t="n">
         <v>64</v>
       </c>
-      <c r="C39" s="29" t="inlineStr">
+      <c r="D39" s="29" t="inlineStr">
         <is>
           <t>Especialista en obras de Mantenimiento</t>
         </is>
       </c>
-      <c r="D39" s="31" t="inlineStr">
+      <c r="E39" s="31" t="inlineStr">
         <is>
           <t>XIV</t>
         </is>
       </c>
-      <c r="E39" s="32" t="n">
+      <c r="F39" s="32" t="n">
         <v>6668</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="26" t="inlineStr">
+      <c r="A40" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="26" t="inlineStr">
         <is>
           <t>P-2 Dos Hermanas</t>
         </is>
       </c>
-      <c r="B40" s="7" t="n">
+      <c r="C40" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="C40" s="26" t="inlineStr">
+      <c r="D40" s="26" t="inlineStr">
         <is>
           <t>Director de las Instalaciones y/o los Complejos</t>
         </is>
       </c>
-      <c r="D40" s="27" t="inlineStr">
+      <c r="E40" s="27" t="inlineStr">
         <is>
           <t>XV</t>
         </is>
       </c>
-      <c r="E40" s="28" t="n">
+      <c r="F40" s="28" t="n">
         <v>7201</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="29" t="inlineStr">
+      <c r="A41" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="29" t="inlineStr">
         <is>
           <t>P-2 Dos Hermanas</t>
         </is>
       </c>
-      <c r="B41" s="30" t="n">
+      <c r="C41" s="30" t="n">
         <v>24</v>
       </c>
-      <c r="C41" s="29" t="inlineStr">
+      <c r="D41" s="29" t="inlineStr">
         <is>
           <t>Subdirector Asis. de Serv y Calidad</t>
         </is>
       </c>
-      <c r="D41" s="31" t="inlineStr">
+      <c r="E41" s="31" t="inlineStr">
         <is>
           <t>XIV</t>
         </is>
       </c>
-      <c r="E41" s="32" t="n">
+      <c r="F41" s="32" t="n">
         <v>6668</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="26" t="inlineStr">
+      <c r="A42" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="26" t="inlineStr">
         <is>
           <t>P-2 Dos Hermanas</t>
         </is>
       </c>
-      <c r="B42" s="7" t="n">
+      <c r="C42" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="C42" s="26" t="inlineStr">
+      <c r="D42" s="26" t="inlineStr">
         <is>
           <t>Subdirector Asistente de   Control  Interno.</t>
         </is>
       </c>
-      <c r="D42" s="27" t="inlineStr">
+      <c r="E42" s="27" t="inlineStr">
         <is>
           <t>XIV</t>
         </is>
       </c>
-      <c r="E42" s="28" t="n">
+      <c r="F42" s="28" t="n">
         <v>6668</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="29" t="inlineStr">
+      <c r="A43" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="29" t="inlineStr">
         <is>
           <t>P-2 Dos Hermanas</t>
         </is>
       </c>
-      <c r="B43" s="30" t="n">
+      <c r="C43" s="30" t="n">
         <v>26</v>
       </c>
-      <c r="C43" s="29" t="inlineStr">
+      <c r="D43" s="29" t="inlineStr">
         <is>
           <t>Técnico  en Gestión Capital  Humanos</t>
         </is>
       </c>
-      <c r="D43" s="31" t="inlineStr">
+      <c r="E43" s="31" t="inlineStr">
         <is>
           <t>XI</t>
         </is>
       </c>
-      <c r="E43" s="32" t="n">
+      <c r="F43" s="32" t="n">
         <v>5343</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="26" t="inlineStr">
+      <c r="A44" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="26" t="inlineStr">
         <is>
           <t>P-2 Dos Hermanas</t>
         </is>
       </c>
-      <c r="B44" s="7" t="n">
+      <c r="C44" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="C44" s="26" t="inlineStr">
+      <c r="D44" s="26" t="inlineStr">
         <is>
           <t>Especialista en Gestion Económico  (EP)</t>
         </is>
       </c>
-      <c r="D44" s="27" t="inlineStr">
+      <c r="E44" s="27" t="inlineStr">
         <is>
           <t>XIV</t>
         </is>
       </c>
-      <c r="E44" s="28" t="n">
+      <c r="F44" s="28" t="n">
         <v>6668</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="29" t="inlineStr">
+      <c r="A45" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="29" t="inlineStr">
         <is>
           <t>P-2 Dos Hermanas</t>
         </is>
       </c>
-      <c r="B45" s="30" t="n">
+      <c r="C45" s="30" t="n">
         <v>29</v>
       </c>
-      <c r="C45" s="29" t="inlineStr">
+      <c r="D45" s="29" t="inlineStr">
         <is>
           <t>Técnico Gestión Económica</t>
         </is>
       </c>
-      <c r="D45" s="31" t="inlineStr">
+      <c r="E45" s="31" t="inlineStr">
         <is>
           <t>XI</t>
         </is>
       </c>
-      <c r="E45" s="32" t="n">
+      <c r="F45" s="32" t="n">
         <v>5343</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="26" t="inlineStr">
+      <c r="A46" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="26" t="inlineStr">
         <is>
           <t>P-2 Dos Hermanas</t>
         </is>
       </c>
-      <c r="B46" s="7" t="n">
+      <c r="C46" s="7" t="n">
         <v>31</v>
       </c>
-      <c r="C46" s="26" t="inlineStr">
+      <c r="D46" s="26" t="inlineStr">
         <is>
           <t>Dependiente  Gastronomico</t>
         </is>
       </c>
-      <c r="D46" s="27" t="inlineStr">
+      <c r="E46" s="27" t="inlineStr">
         <is>
           <t>IX</t>
         </is>
       </c>
-      <c r="E46" s="28" t="n">
+      <c r="F46" s="28" t="n">
         <v>4666</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="29" t="inlineStr">
+      <c r="A47" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="29" t="inlineStr">
         <is>
           <t>P-2 Dos Hermanas</t>
         </is>
       </c>
-      <c r="B47" s="30" t="n">
+      <c r="C47" s="30" t="n">
         <v>32</v>
       </c>
-      <c r="C47" s="29" t="inlineStr">
+      <c r="D47" s="29" t="inlineStr">
         <is>
           <t>Maestro de Cocina</t>
         </is>
       </c>
-      <c r="D47" s="31" t="inlineStr">
+      <c r="E47" s="31" t="inlineStr">
         <is>
           <t>XI</t>
         </is>
       </c>
-      <c r="E47" s="32" t="n">
+      <c r="F47" s="32" t="n">
         <v>5343</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="26" t="inlineStr">
+      <c r="A48" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="26" t="inlineStr">
         <is>
           <t>P-2 Dos Hermanas</t>
         </is>
       </c>
-      <c r="B48" s="7" t="n">
+      <c r="C48" s="7" t="n">
         <v>33</v>
       </c>
-      <c r="C48" s="26" t="inlineStr">
+      <c r="D48" s="26" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="D48" s="27" t="inlineStr">
+      <c r="E48" s="27" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E48" s="28" t="n">
+      <c r="F48" s="28" t="n">
         <v>4993</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="29" t="inlineStr">
+      <c r="A49" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="29" t="inlineStr">
         <is>
           <t>P-2 Dos Hermanas</t>
         </is>
       </c>
-      <c r="B49" s="30" t="n">
+      <c r="C49" s="30" t="n">
         <v>34</v>
       </c>
-      <c r="C49" s="29" t="inlineStr">
+      <c r="D49" s="29" t="inlineStr">
         <is>
           <t>Elaborador de Alimentos</t>
         </is>
       </c>
-      <c r="D49" s="31" t="inlineStr">
+      <c r="E49" s="31" t="inlineStr">
         <is>
           <t>IX</t>
         </is>
       </c>
-      <c r="E49" s="32" t="n">
+      <c r="F49" s="32" t="n">
         <v>4666</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="26" t="inlineStr">
+      <c r="A50" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="26" t="inlineStr">
         <is>
           <t>P-2 Dos Hermanas</t>
         </is>
       </c>
-      <c r="B50" s="7" t="n">
+      <c r="C50" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="C50" s="26" t="inlineStr">
+      <c r="D50" s="26" t="inlineStr">
         <is>
           <t>Recepcionista Hotelero</t>
         </is>
       </c>
-      <c r="D50" s="27" t="inlineStr">
+      <c r="E50" s="27" t="inlineStr">
         <is>
           <t>IX</t>
         </is>
       </c>
-      <c r="E50" s="28" t="n">
+      <c r="F50" s="28" t="n">
         <v>4666</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="29" t="inlineStr">
+      <c r="A51" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="29" t="inlineStr">
         <is>
           <t>P-2 Dos Hermanas</t>
         </is>
       </c>
-      <c r="B51" s="30" t="n">
+      <c r="C51" s="30" t="n">
         <v>36</v>
       </c>
-      <c r="C51" s="29" t="inlineStr">
+      <c r="D51" s="29" t="inlineStr">
         <is>
           <t>Camarera de Habitaciones</t>
         </is>
       </c>
-      <c r="D51" s="31" t="inlineStr">
+      <c r="E51" s="31" t="inlineStr">
         <is>
           <t>IX</t>
         </is>
       </c>
-      <c r="E51" s="32" t="n">
+      <c r="F51" s="32" t="n">
         <v>4666</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="26" t="inlineStr">
+      <c r="A52" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="26" t="inlineStr">
         <is>
           <t>P-2 Dos Hermanas</t>
         </is>
       </c>
-      <c r="B52" s="7" t="n">
+      <c r="C52" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="C52" s="26" t="inlineStr">
+      <c r="D52" s="26" t="inlineStr">
         <is>
           <t>Camarera de Habitaciones JB</t>
         </is>
       </c>
-      <c r="D52" s="27" t="inlineStr">
+      <c r="E52" s="27" t="inlineStr">
         <is>
           <t>XII</t>
         </is>
       </c>
-      <c r="E52" s="28" t="n">
+      <c r="F52" s="28" t="n">
         <v>5770</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="29" t="inlineStr">
+      <c r="A53" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="29" t="inlineStr">
         <is>
           <t>P-2 Dos Hermanas</t>
         </is>
       </c>
-      <c r="B53" s="30" t="n">
+      <c r="C53" s="30" t="n">
         <v>38</v>
       </c>
-      <c r="C53" s="29" t="inlineStr">
+      <c r="D53" s="29" t="inlineStr">
         <is>
           <t>Técnico de Recreacion y Animación JB</t>
         </is>
       </c>
-      <c r="D53" s="31" t="inlineStr">
+      <c r="E53" s="31" t="inlineStr">
         <is>
           <t>XII</t>
         </is>
       </c>
-      <c r="E53" s="32" t="n">
+      <c r="F53" s="32" t="n">
         <v>5770</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="26" t="inlineStr">
+      <c r="A54" s="5" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="26" t="inlineStr">
         <is>
           <t>P-2 Dos Hermanas</t>
         </is>
       </c>
-      <c r="B54" s="7" t="n">
+      <c r="C54" s="7" t="n">
         <v>39</v>
       </c>
-      <c r="C54" s="26" t="inlineStr">
+      <c r="D54" s="26" t="inlineStr">
         <is>
           <t>Técnico de Recreacion y Animación</t>
         </is>
       </c>
-      <c r="D54" s="27" t="inlineStr">
+      <c r="E54" s="27" t="inlineStr">
         <is>
           <t>IX</t>
         </is>
       </c>
-      <c r="E54" s="28" t="n">
+      <c r="F54" s="28" t="n">
         <v>4666</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="29" t="inlineStr">
+      <c r="A55" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="29" t="inlineStr">
         <is>
           <t>P-2 Dos Hermanas</t>
         </is>
       </c>
-      <c r="B55" s="30" t="n">
+      <c r="C55" s="30" t="n">
         <v>41</v>
       </c>
-      <c r="C55" s="29" t="inlineStr">
+      <c r="D55" s="29" t="inlineStr">
         <is>
           <t>Encargado de Almacén</t>
         </is>
       </c>
-      <c r="D55" s="31" t="inlineStr">
+      <c r="E55" s="31" t="inlineStr">
         <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="E55" s="32" t="n">
+      <c r="F55" s="32" t="n">
         <v>3918</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="26" t="inlineStr">
+      <c r="A56" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="26" t="inlineStr">
         <is>
           <t>P-2 Dos Hermanas</t>
         </is>
       </c>
-      <c r="B56" s="7" t="n">
+      <c r="C56" s="7" t="n">
         <v>42</v>
       </c>
-      <c r="C56" s="26" t="inlineStr">
+      <c r="D56" s="26" t="inlineStr">
         <is>
           <t>Operario de MantenT. Y Serv. Tecnicos</t>
         </is>
       </c>
-      <c r="D56" s="27" t="inlineStr">
+      <c r="E56" s="27" t="inlineStr">
         <is>
           <t>VII</t>
         </is>
       </c>
-      <c r="E56" s="28" t="n">
+      <c r="F56" s="28" t="n">
         <v>4153</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="29" t="inlineStr">
+      <c r="A57" s="5" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="29" t="inlineStr">
         <is>
           <t>P-2 Dos Hermanas</t>
         </is>
       </c>
-      <c r="B57" s="30" t="n">
+      <c r="C57" s="30" t="n">
         <v>43</v>
       </c>
-      <c r="C57" s="29" t="inlineStr">
+      <c r="D57" s="29" t="inlineStr">
         <is>
           <t>Operario de MantenT. Y Serv. Tecnico  JB</t>
         </is>
       </c>
-      <c r="D57" s="31" t="inlineStr">
+      <c r="E57" s="31" t="inlineStr">
         <is>
           <t>XII</t>
         </is>
       </c>
-      <c r="E57" s="32" t="n">
+      <c r="F57" s="32" t="n">
         <v>5770</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="26" t="inlineStr">
+      <c r="A58" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="26" t="inlineStr">
         <is>
           <t>P-2 Dos Hermanas</t>
         </is>
       </c>
-      <c r="B58" s="7" t="n">
+      <c r="C58" s="7" t="n">
         <v>44</v>
       </c>
-      <c r="C58" s="26" t="inlineStr">
+      <c r="D58" s="26" t="inlineStr">
         <is>
           <t>Chofer vehiculos de carga</t>
         </is>
       </c>
-      <c r="D58" s="27" t="inlineStr">
+      <c r="E58" s="27" t="inlineStr">
         <is>
           <t>IX</t>
         </is>
       </c>
-      <c r="E58" s="28" t="n">
+      <c r="F58" s="28" t="n">
         <v>4666</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="29" t="inlineStr">
+      <c r="A59" s="5" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="29" t="inlineStr">
         <is>
           <t>P-2 Dos Hermanas</t>
         </is>
       </c>
-      <c r="B59" s="30" t="n">
+      <c r="C59" s="30" t="n">
         <v>45</v>
       </c>
-      <c r="C59" s="29" t="inlineStr">
+      <c r="D59" s="29" t="inlineStr">
         <is>
           <t>Operario LABORES AGROPECUARIAS Y Jardineria</t>
         </is>
       </c>
-      <c r="D59" s="31" t="inlineStr">
+      <c r="E59" s="31" t="inlineStr">
         <is>
           <t>VIII</t>
         </is>
       </c>
-      <c r="E59" s="32" t="n">
+      <c r="F59" s="32" t="n">
         <v>4402</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="26" t="inlineStr">
+      <c r="A60" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="26" t="inlineStr">
         <is>
           <t>P-2 Dos Hermanas</t>
         </is>
       </c>
-      <c r="B60" s="7" t="n">
+      <c r="C60" s="7" t="n">
         <v>47</v>
       </c>
-      <c r="C60" s="26" t="inlineStr">
+      <c r="D60" s="26" t="inlineStr">
         <is>
           <t>Jefes de Grupo de Seguridad Interna</t>
         </is>
       </c>
-      <c r="D60" s="27" t="inlineStr">
+      <c r="E60" s="27" t="inlineStr">
         <is>
           <t>XII</t>
         </is>
       </c>
-      <c r="E60" s="28" t="n">
+      <c r="F60" s="28" t="n">
         <v>5770</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="29" t="inlineStr">
+      <c r="A61" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="29" t="inlineStr">
         <is>
           <t>P-2 Dos Hermanas</t>
         </is>
       </c>
-      <c r="B61" s="30" t="n">
+      <c r="C61" s="30" t="n">
         <v>48</v>
       </c>
-      <c r="C61" s="29" t="inlineStr">
+      <c r="D61" s="29" t="inlineStr">
         <is>
           <t>Agente Seguridad y Protección</t>
         </is>
       </c>
-      <c r="D61" s="31" t="inlineStr">
+      <c r="E61" s="31" t="inlineStr">
         <is>
           <t>VIII</t>
         </is>
       </c>
-      <c r="E61" s="32" t="n">
+      <c r="F61" s="32" t="n">
         <v>4402</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="26" t="inlineStr">
+      <c r="A62" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="26" t="inlineStr">
         <is>
           <t>Laguna Grande</t>
         </is>
       </c>
-      <c r="B62" s="7" t="n">
+      <c r="C62" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="C62" s="26" t="inlineStr">
+      <c r="D62" s="26" t="inlineStr">
         <is>
           <t>Director de las Instalaciones y/o los Complejos</t>
         </is>
       </c>
-      <c r="D62" s="27" t="inlineStr">
+      <c r="E62" s="27" t="inlineStr">
         <is>
           <t>XV</t>
         </is>
       </c>
-      <c r="E62" s="28" t="n">
+      <c r="F62" s="28" t="n">
         <v>7201</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="29" t="inlineStr">
+      <c r="A63" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="29" t="inlineStr">
         <is>
           <t>Laguna Grande</t>
         </is>
       </c>
-      <c r="B63" s="30" t="n">
+      <c r="C63" s="30" t="n">
         <v>25</v>
       </c>
-      <c r="C63" s="29" t="inlineStr">
+      <c r="D63" s="29" t="inlineStr">
         <is>
           <t>Sub Director Asistente</t>
         </is>
       </c>
-      <c r="D63" s="31" t="inlineStr">
+      <c r="E63" s="31" t="inlineStr">
         <is>
           <t>XIV</t>
         </is>
       </c>
-      <c r="E63" s="32" t="n">
+      <c r="F63" s="32" t="n">
         <v>6668</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="26" t="inlineStr">
+      <c r="A64" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="26" t="inlineStr">
         <is>
           <t>Laguna Grande</t>
         </is>
       </c>
-      <c r="B64" s="7" t="n">
+      <c r="C64" s="7" t="n">
         <v>26</v>
       </c>
-      <c r="C64" s="26" t="inlineStr">
+      <c r="D64" s="26" t="inlineStr">
         <is>
           <t>Tecnico  en Gestión de Capital Humanos</t>
         </is>
       </c>
-      <c r="D64" s="27" t="inlineStr">
+      <c r="E64" s="27" t="inlineStr">
         <is>
           <t>XI</t>
         </is>
       </c>
-      <c r="E64" s="28" t="n">
+      <c r="F64" s="28" t="n">
         <v>5343</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="29" t="inlineStr">
+      <c r="A65" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="29" t="inlineStr">
         <is>
           <t>Laguna Grande</t>
         </is>
       </c>
-      <c r="B65" s="30" t="n">
+      <c r="C65" s="30" t="n">
         <v>27</v>
       </c>
-      <c r="C65" s="29" t="inlineStr">
+      <c r="D65" s="29" t="inlineStr">
         <is>
           <t>Tecnico de Recreacion y Animacion</t>
         </is>
       </c>
-      <c r="D65" s="31" t="inlineStr">
+      <c r="E65" s="31" t="inlineStr">
         <is>
           <t>IX</t>
         </is>
       </c>
-      <c r="E65" s="32" t="n">
+      <c r="F65" s="32" t="n">
         <v>4666</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="26" t="inlineStr">
+      <c r="A66" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="26" t="inlineStr">
         <is>
           <t>Laguna Grande</t>
         </is>
       </c>
-      <c r="B66" s="7" t="n">
+      <c r="C66" s="7" t="n">
         <v>29</v>
       </c>
-      <c r="C66" s="26" t="inlineStr">
+      <c r="D66" s="26" t="inlineStr">
         <is>
           <t>Especialista en Gestion   Económica</t>
         </is>
       </c>
-      <c r="D66" s="27" t="inlineStr">
+      <c r="E66" s="27" t="inlineStr">
         <is>
           <t>XIII</t>
         </is>
       </c>
-      <c r="E66" s="28" t="n">
+      <c r="F66" s="28" t="n">
         <v>6174</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="29" t="inlineStr">
+      <c r="A67" s="5" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="29" t="inlineStr">
         <is>
           <t>Laguna Grande</t>
         </is>
       </c>
-      <c r="B67" s="30" t="n">
+      <c r="C67" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="C67" s="29" t="inlineStr">
+      <c r="D67" s="29" t="inlineStr">
         <is>
           <t>Técnico  en Gestión Económica</t>
         </is>
       </c>
-      <c r="D67" s="31" t="inlineStr">
+      <c r="E67" s="31" t="inlineStr">
         <is>
           <t>XI</t>
         </is>
       </c>
-      <c r="E67" s="32" t="n">
+      <c r="F67" s="32" t="n">
         <v>5343</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="26" t="inlineStr">
+      <c r="A68" s="5" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="26" t="inlineStr">
         <is>
           <t>Laguna Grande</t>
         </is>
       </c>
-      <c r="B68" s="7" t="n">
+      <c r="C68" s="7" t="n">
         <v>32</v>
       </c>
-      <c r="C68" s="26" t="inlineStr">
+      <c r="D68" s="26" t="inlineStr">
         <is>
           <t>Dependiente Gastronomico</t>
         </is>
       </c>
-      <c r="D68" s="27" t="inlineStr">
+      <c r="E68" s="27" t="inlineStr">
         <is>
           <t>IX</t>
         </is>
       </c>
-      <c r="E68" s="28" t="n">
+      <c r="F68" s="28" t="n">
         <v>4666</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="29" t="inlineStr">
+      <c r="A69" s="5" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="29" t="inlineStr">
         <is>
           <t>Laguna Grande</t>
         </is>
       </c>
-      <c r="B69" s="30" t="n">
+      <c r="C69" s="30" t="n">
         <v>33</v>
       </c>
-      <c r="C69" s="29" t="inlineStr">
+      <c r="D69" s="29" t="inlineStr">
         <is>
           <t>Nivel Medio</t>
         </is>
       </c>
-      <c r="D69" s="31" t="inlineStr">
+      <c r="E69" s="31" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E69" s="32" t="n">
+      <c r="F69" s="32" t="n">
         <v>4993</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="26" t="inlineStr">
+      <c r="A70" s="5" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="26" t="inlineStr">
         <is>
           <t>Laguna Grande</t>
         </is>
       </c>
-      <c r="B70" s="7" t="n">
+      <c r="C70" s="7" t="n">
         <v>34</v>
       </c>
-      <c r="C70" s="26" t="inlineStr">
+      <c r="D70" s="26" t="inlineStr">
         <is>
           <t>Ayudante de Cocina</t>
         </is>
       </c>
-      <c r="D70" s="27" t="inlineStr">
+      <c r="E70" s="27" t="inlineStr">
         <is>
           <t>VIII</t>
         </is>
       </c>
-      <c r="E70" s="28" t="n">
+      <c r="F70" s="28" t="n">
         <v>4402</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="29" t="inlineStr">
+      <c r="A71" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="29" t="inlineStr">
         <is>
           <t>Laguna Grande</t>
         </is>
       </c>
-      <c r="B71" s="30" t="n">
+      <c r="C71" s="30" t="n">
         <v>36</v>
       </c>
-      <c r="C71" s="29" t="inlineStr">
+      <c r="D71" s="29" t="inlineStr">
         <is>
           <t>Recepcionista Hotelero</t>
         </is>
       </c>
-      <c r="D71" s="31" t="inlineStr">
+      <c r="E71" s="31" t="inlineStr">
         <is>
           <t>IX</t>
         </is>
       </c>
-      <c r="E71" s="32" t="n">
+      <c r="F71" s="32" t="n">
         <v>4666</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="26" t="inlineStr">
+      <c r="A72" s="5" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="26" t="inlineStr">
         <is>
           <t>Laguna Grande</t>
         </is>
       </c>
-      <c r="B72" s="7" t="n">
+      <c r="C72" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="C72" s="26" t="inlineStr">
+      <c r="D72" s="26" t="inlineStr">
         <is>
           <t>Camarera de Habitaciones</t>
         </is>
       </c>
-      <c r="D72" s="27" t="inlineStr">
+      <c r="E72" s="27" t="inlineStr">
         <is>
           <t>IX</t>
         </is>
       </c>
-      <c r="E72" s="28" t="n">
+      <c r="F72" s="28" t="n">
         <v>4666</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="29" t="inlineStr">
+      <c r="A73" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="29" t="inlineStr">
         <is>
           <t>Laguna Grande</t>
         </is>
       </c>
-      <c r="B73" s="30" t="n">
+      <c r="C73" s="30" t="n">
         <v>38</v>
       </c>
-      <c r="C73" s="29" t="inlineStr">
+      <c r="D73" s="29" t="inlineStr">
         <is>
           <t>Nivel Medio Superior</t>
         </is>
       </c>
-      <c r="D73" s="31" t="inlineStr">
+      <c r="E73" s="31" t="inlineStr">
         <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="E73" s="32" t="n">
+      <c r="F73" s="32" t="n">
         <v>3918</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="26" t="inlineStr">
+      <c r="A74" s="5" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="26" t="inlineStr">
         <is>
           <t>Laguna Grande</t>
         </is>
       </c>
-      <c r="B74" s="7" t="n">
+      <c r="C74" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="C74" s="26" t="inlineStr">
+      <c r="D74" s="26" t="inlineStr">
         <is>
           <t>Encargado de Almacèn</t>
         </is>
       </c>
-      <c r="D74" s="27" t="inlineStr">
+      <c r="E74" s="27" t="inlineStr">
         <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="E74" s="28" t="n">
+      <c r="F74" s="28" t="n">
         <v>3918</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="29" t="inlineStr">
+      <c r="A75" s="5" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="29" t="inlineStr">
         <is>
           <t>Laguna Grande</t>
         </is>
       </c>
-      <c r="B75" s="30" t="n">
+      <c r="C75" s="30" t="n">
         <v>41</v>
       </c>
-      <c r="C75" s="29" t="inlineStr">
+      <c r="D75" s="29" t="inlineStr">
         <is>
           <t>Operario de Mantenimiento Y SERV. TECNICOS</t>
         </is>
       </c>
-      <c r="D75" s="31" t="inlineStr">
+      <c r="E75" s="31" t="inlineStr">
         <is>
           <t>VII</t>
         </is>
       </c>
-      <c r="E75" s="32" t="n">
+      <c r="F75" s="32" t="n">
         <v>4153</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="26" t="inlineStr">
+      <c r="A76" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="26" t="inlineStr">
         <is>
           <t>Laguna Grande</t>
         </is>
       </c>
-      <c r="B76" s="7" t="n">
+      <c r="C76" s="7" t="n">
         <v>42</v>
       </c>
-      <c r="C76" s="26" t="inlineStr">
+      <c r="D76" s="26" t="inlineStr">
         <is>
           <t>Chofer Vehiculos carga</t>
         </is>
       </c>
-      <c r="D76" s="27" t="inlineStr">
+      <c r="E76" s="27" t="inlineStr">
         <is>
           <t>IX</t>
         </is>
       </c>
-      <c r="E76" s="28" t="n">
+      <c r="F76" s="28" t="n">
         <v>4666</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="29" t="inlineStr">
+      <c r="A77" s="5" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="29" t="inlineStr">
         <is>
           <t>Laguna Grande</t>
         </is>
       </c>
-      <c r="B77" s="30" t="n">
+      <c r="C77" s="30" t="n">
         <v>44</v>
       </c>
-      <c r="C77" s="29" t="inlineStr">
+      <c r="D77" s="29" t="inlineStr">
         <is>
           <t>Jefe Grupo Seg. Interna</t>
         </is>
       </c>
-      <c r="D77" s="31" t="inlineStr">
+      <c r="E77" s="31" t="inlineStr">
         <is>
           <t>XII</t>
         </is>
       </c>
-      <c r="E77" s="32" t="n">
+      <c r="F77" s="32" t="n">
         <v>5770</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="26" t="inlineStr">
+      <c r="A78" s="5" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="26" t="inlineStr">
         <is>
           <t>Laguna Grande</t>
         </is>
       </c>
-      <c r="B78" s="7" t="n">
+      <c r="C78" s="7" t="n">
         <v>45</v>
       </c>
-      <c r="C78" s="26" t="inlineStr">
+      <c r="D78" s="26" t="inlineStr">
         <is>
           <t>Agente de Seguridad y Protección</t>
         </is>
       </c>
-      <c r="D78" s="27" t="inlineStr">
+      <c r="E78" s="27" t="inlineStr">
         <is>
           <t>VIII</t>
         </is>
       </c>
-      <c r="E78" s="28" t="n">
+      <c r="F78" s="28" t="n">
         <v>4402</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="29" t="inlineStr">
+      <c r="A79" s="5" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="29" t="inlineStr">
         <is>
           <t>P-2  Aguas Claras</t>
         </is>
       </c>
-      <c r="B79" s="30" t="n">
+      <c r="C79" s="30" t="n">
         <v>19</v>
       </c>
-      <c r="C79" s="29" t="inlineStr">
+      <c r="D79" s="29" t="inlineStr">
         <is>
           <t>Director de las Instalaciones y/o los Complejos</t>
         </is>
       </c>
-      <c r="D79" s="31" t="inlineStr">
+      <c r="E79" s="31" t="inlineStr">
         <is>
           <t>XV</t>
         </is>
       </c>
-      <c r="E79" s="32" t="n">
+      <c r="F79" s="32" t="n">
         <v>7201</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="26" t="inlineStr">
+      <c r="A80" s="5" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="26" t="inlineStr">
         <is>
           <t>P-2  Aguas Claras</t>
         </is>
       </c>
-      <c r="B80" s="7" t="n">
+      <c r="C80" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="C80" s="26" t="inlineStr">
+      <c r="D80" s="26" t="inlineStr">
         <is>
           <t>Sub Director Asistente</t>
         </is>
       </c>
-      <c r="D80" s="27" t="inlineStr">
+      <c r="E80" s="27" t="inlineStr">
         <is>
           <t>XIV</t>
         </is>
       </c>
-      <c r="E80" s="28" t="n">
+      <c r="F80" s="28" t="n">
         <v>6668</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="29" t="inlineStr">
+      <c r="A81" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="29" t="inlineStr">
         <is>
           <t>P-2  Aguas Claras</t>
         </is>
       </c>
-      <c r="B81" s="30" t="n">
+      <c r="C81" s="30" t="n">
         <v>21</v>
       </c>
-      <c r="C81" s="29" t="inlineStr">
+      <c r="D81" s="29" t="inlineStr">
         <is>
           <t>Especialista en Gestion de Capital Humanos</t>
         </is>
       </c>
-      <c r="D81" s="31" t="inlineStr">
+      <c r="E81" s="31" t="inlineStr">
         <is>
           <t>XIII</t>
         </is>
       </c>
-      <c r="E81" s="32" t="n">
+      <c r="F81" s="32" t="n">
         <v>6174</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="26" t="inlineStr">
+      <c r="A82" s="5" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="26" t="inlineStr">
         <is>
           <t>P-2  Aguas Claras</t>
         </is>
       </c>
-      <c r="B82" s="7" t="n">
+      <c r="C82" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="C82" s="26" t="inlineStr">
+      <c r="D82" s="26" t="inlineStr">
         <is>
           <t>Especialista en Gestion Economica (EP)</t>
         </is>
       </c>
-      <c r="D82" s="27" t="inlineStr">
+      <c r="E82" s="27" t="inlineStr">
         <is>
           <t>XIV</t>
         </is>
       </c>
-      <c r="E82" s="28" t="n">
+      <c r="F82" s="28" t="n">
         <v>6668</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="29" t="inlineStr">
+      <c r="A83" s="5" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="29" t="inlineStr">
         <is>
           <t>P-2  Aguas Claras</t>
         </is>
       </c>
-      <c r="B83" s="30" t="n">
+      <c r="C83" s="30" t="n">
         <v>24</v>
       </c>
-      <c r="C83" s="29" t="inlineStr">
+      <c r="D83" s="29" t="inlineStr">
         <is>
           <t>Tècnico  en Gestiòn Econòmica</t>
         </is>
       </c>
-      <c r="D83" s="31" t="inlineStr">
+      <c r="E83" s="31" t="inlineStr">
         <is>
           <t>XI</t>
         </is>
       </c>
-      <c r="E83" s="32" t="n">
+      <c r="F83" s="32" t="n">
         <v>5343</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="26" t="inlineStr">
+      <c r="A84" s="5" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="26" t="inlineStr">
         <is>
           <t>P-2  Aguas Claras</t>
         </is>
       </c>
-      <c r="B84" s="7" t="n">
+      <c r="C84" s="7" t="n">
         <v>26</v>
       </c>
-      <c r="C84" s="26" t="inlineStr">
+      <c r="D84" s="26" t="inlineStr">
         <is>
           <t>Capitàn de SALÓN</t>
         </is>
       </c>
-      <c r="D84" s="27" t="inlineStr">
+      <c r="E84" s="27" t="inlineStr">
         <is>
           <t>XI</t>
         </is>
       </c>
-      <c r="E84" s="28" t="n">
+      <c r="F84" s="28" t="n">
         <v>5343</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="29" t="inlineStr">
+      <c r="A85" s="5" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="29" t="inlineStr">
         <is>
           <t>P-2  Aguas Claras</t>
         </is>
       </c>
-      <c r="B85" s="30" t="n">
+      <c r="C85" s="30" t="n">
         <v>27</v>
       </c>
-      <c r="C85" s="29" t="inlineStr">
+      <c r="D85" s="29" t="inlineStr">
         <is>
           <t>Dependiente  GastronomicoJB</t>
         </is>
       </c>
-      <c r="D85" s="31" t="inlineStr">
+      <c r="E85" s="31" t="inlineStr">
         <is>
           <t>XII</t>
         </is>
       </c>
-      <c r="E85" s="32" t="n">
+      <c r="F85" s="32" t="n">
         <v>5770</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="26" t="inlineStr">
+      <c r="A86" s="5" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="26" t="inlineStr">
         <is>
           <t>P-2  Aguas Claras</t>
         </is>
       </c>
-      <c r="B86" s="7" t="n">
+      <c r="C86" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="C86" s="26" t="inlineStr">
+      <c r="D86" s="26" t="inlineStr">
         <is>
           <t>Dependiente  Gastronomico</t>
         </is>
       </c>
-      <c r="D86" s="27" t="inlineStr">
+      <c r="E86" s="27" t="inlineStr">
         <is>
           <t>IX</t>
         </is>
       </c>
-      <c r="E86" s="28" t="n">
+      <c r="F86" s="28" t="n">
         <v>4666</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="29" t="inlineStr">
+      <c r="A87" s="5" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="29" t="inlineStr">
         <is>
           <t>P-2  Aguas Claras</t>
         </is>
       </c>
-      <c r="B87" s="30" t="n">
+      <c r="C87" s="30" t="n">
         <v>29</v>
       </c>
-      <c r="C87" s="29" t="inlineStr">
+      <c r="D87" s="29" t="inlineStr">
         <is>
           <t>Panadero Dulcero</t>
         </is>
       </c>
-      <c r="D87" s="31" t="inlineStr">
+      <c r="E87" s="31" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E87" s="32" t="n">
+      <c r="F87" s="32" t="n">
         <v>4993</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="26" t="inlineStr">
+      <c r="A88" s="5" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="26" t="inlineStr">
         <is>
           <t>P-2  Aguas Claras</t>
         </is>
       </c>
-      <c r="B88" s="7" t="n">
+      <c r="C88" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="C88" s="26" t="inlineStr">
+      <c r="D88" s="26" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="D88" s="27" t="inlineStr">
+      <c r="E88" s="27" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E88" s="28" t="n">
+      <c r="F88" s="28" t="n">
         <v>4993</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="29" t="inlineStr">
+      <c r="A89" s="5" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="29" t="inlineStr">
         <is>
           <t>P-2  Aguas Claras</t>
         </is>
       </c>
-      <c r="B89" s="30" t="n">
+      <c r="C89" s="30" t="n">
         <v>31</v>
       </c>
-      <c r="C89" s="29" t="inlineStr">
+      <c r="D89" s="29" t="inlineStr">
         <is>
           <t>Ayudante  de Cocina</t>
         </is>
       </c>
-      <c r="D89" s="31" t="inlineStr">
+      <c r="E89" s="31" t="inlineStr">
         <is>
           <t>VIII</t>
         </is>
       </c>
-      <c r="E89" s="32" t="n">
+      <c r="F89" s="32" t="n">
         <v>4402</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="26" t="inlineStr">
+      <c r="A90" s="5" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="26" t="inlineStr">
         <is>
           <t>P-2  Aguas Claras</t>
         </is>
       </c>
-      <c r="B90" s="7" t="n">
+      <c r="C90" s="7" t="n">
         <v>33</v>
       </c>
-      <c r="C90" s="26" t="inlineStr">
+      <c r="D90" s="26" t="inlineStr">
         <is>
           <t>Recepcionista Hotelero JB</t>
         </is>
       </c>
-      <c r="D90" s="27" t="inlineStr">
+      <c r="E90" s="27" t="inlineStr">
         <is>
           <t>XII</t>
         </is>
       </c>
-      <c r="E90" s="28" t="n">
+      <c r="F90" s="28" t="n">
         <v>5770</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="29" t="inlineStr">
+      <c r="A91" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="29" t="inlineStr">
         <is>
           <t>P-2  Aguas Claras</t>
         </is>
       </c>
-      <c r="B91" s="30" t="n">
+      <c r="C91" s="30" t="n">
         <v>34</v>
       </c>
-      <c r="C91" s="29" t="inlineStr">
+      <c r="D91" s="29" t="inlineStr">
         <is>
           <t>Recepcionista Hotelero</t>
         </is>
       </c>
-      <c r="D91" s="31" t="inlineStr">
+      <c r="E91" s="31" t="inlineStr">
         <is>
           <t>IX</t>
         </is>
       </c>
-      <c r="E91" s="32" t="n">
+      <c r="F91" s="32" t="n">
         <v>4666</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="26" t="inlineStr">
+      <c r="A92" s="5" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="26" t="inlineStr">
         <is>
           <t>P-2  Aguas Claras</t>
         </is>
       </c>
-      <c r="B92" s="7" t="n">
+      <c r="C92" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="C92" s="26" t="inlineStr">
+      <c r="D92" s="26" t="inlineStr">
         <is>
           <t>Camarera de Habitaciones JB</t>
         </is>
       </c>
-      <c r="D92" s="27" t="inlineStr">
+      <c r="E92" s="27" t="inlineStr">
         <is>
           <t>XII</t>
         </is>
       </c>
-      <c r="E92" s="28" t="n">
+      <c r="F92" s="28" t="n">
         <v>5770</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="29" t="inlineStr">
+      <c r="A93" s="5" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="29" t="inlineStr">
         <is>
           <t>P-2  Aguas Claras</t>
         </is>
       </c>
-      <c r="B93" s="30" t="n">
+      <c r="C93" s="30" t="n">
         <v>36</v>
       </c>
-      <c r="C93" s="29" t="inlineStr">
+      <c r="D93" s="29" t="inlineStr">
         <is>
           <t>Camarera de Habitaciones</t>
         </is>
       </c>
-      <c r="D93" s="31" t="inlineStr">
+      <c r="E93" s="31" t="inlineStr">
         <is>
           <t>IX</t>
         </is>
       </c>
-      <c r="E93" s="32" t="n">
+      <c r="F93" s="32" t="n">
         <v>4666</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="26" t="inlineStr">
+      <c r="A94" s="5" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="26" t="inlineStr">
         <is>
           <t>P-2  Aguas Claras</t>
         </is>
       </c>
-      <c r="B94" s="7" t="n">
+      <c r="C94" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="C94" s="26" t="inlineStr">
+      <c r="D94" s="26" t="inlineStr">
         <is>
           <t>Limpiadora de Areas Publicas para Centros Turisticos</t>
         </is>
       </c>
-      <c r="D94" s="27" t="inlineStr">
+      <c r="E94" s="27" t="inlineStr">
         <is>
           <t>VII</t>
         </is>
       </c>
-      <c r="E94" s="28" t="n">
+      <c r="F94" s="28" t="n">
         <v>4153</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="29" t="inlineStr">
+      <c r="A95" s="5" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="29" t="inlineStr">
         <is>
           <t>P-2  Aguas Claras</t>
         </is>
       </c>
-      <c r="B95" s="30" t="n">
+      <c r="C95" s="30" t="n">
         <v>39</v>
       </c>
-      <c r="C95" s="29" t="inlineStr">
+      <c r="D95" s="29" t="inlineStr">
         <is>
           <t>Tècnico en  Recreación y Animación</t>
         </is>
       </c>
-      <c r="D95" s="31" t="inlineStr">
+      <c r="E95" s="31" t="inlineStr">
         <is>
           <t>IX</t>
         </is>
       </c>
-      <c r="E95" s="32" t="n">
+      <c r="F95" s="32" t="n">
         <v>4666</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="26" t="inlineStr">
+      <c r="A96" s="5" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="26" t="inlineStr">
         <is>
           <t>P-2  Aguas Claras</t>
         </is>
       </c>
-      <c r="B96" s="7" t="n">
+      <c r="C96" s="7" t="n">
         <v>41</v>
       </c>
-      <c r="C96" s="26" t="inlineStr">
+      <c r="D96" s="26" t="inlineStr">
         <is>
           <t>Operario de Mant. Y serv. Tecn.</t>
         </is>
       </c>
-      <c r="D96" s="27" t="inlineStr">
+      <c r="E96" s="27" t="inlineStr">
         <is>
           <t>VII</t>
         </is>
       </c>
-      <c r="E96" s="28" t="n">
+      <c r="F96" s="28" t="n">
         <v>4153</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="29" t="inlineStr">
+      <c r="A97" s="5" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="29" t="inlineStr">
         <is>
           <t>P-2  Aguas Claras</t>
         </is>
       </c>
-      <c r="B97" s="30" t="n">
+      <c r="C97" s="30" t="n">
         <v>42</v>
       </c>
-      <c r="C97" s="29" t="inlineStr">
+      <c r="D97" s="29" t="inlineStr">
         <is>
           <t>Encargado de Almacèn</t>
         </is>
       </c>
-      <c r="D97" s="31" t="inlineStr">
+      <c r="E97" s="31" t="inlineStr">
         <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="E97" s="32" t="n">
+      <c r="F97" s="32" t="n">
         <v>3918</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="26" t="inlineStr">
+      <c r="A98" s="5" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="26" t="inlineStr">
         <is>
           <t>P-2  Aguas Claras</t>
         </is>
       </c>
-      <c r="B98" s="7" t="n">
+      <c r="C98" s="7" t="n">
         <v>44</v>
       </c>
-      <c r="C98" s="26" t="inlineStr">
+      <c r="D98" s="26" t="inlineStr">
         <is>
           <t>Jefes de Grupo de Seguridad Interna</t>
         </is>
       </c>
-      <c r="D98" s="27" t="inlineStr">
+      <c r="E98" s="27" t="inlineStr">
         <is>
           <t>XII</t>
         </is>
       </c>
-      <c r="E98" s="28" t="n">
+      <c r="F98" s="28" t="n">
         <v>5570</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="29" t="inlineStr">
+      <c r="A99" s="5" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="29" t="inlineStr">
         <is>
           <t>P-2  Aguas Claras</t>
         </is>
       </c>
-      <c r="B99" s="30" t="n">
+      <c r="C99" s="30" t="n">
         <v>45</v>
       </c>
-      <c r="C99" s="29" t="inlineStr">
+      <c r="D99" s="29" t="inlineStr">
         <is>
           <t>Agente de Seguridad y Protecciòn</t>
         </is>
       </c>
-      <c r="D99" s="31" t="inlineStr">
+      <c r="E99" s="31" t="inlineStr">
         <is>
           <t>VIII</t>
         </is>
       </c>
-      <c r="E99" s="32" t="n">
+      <c r="F99" s="32" t="n">
         <v>4402</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="26" t="inlineStr">
+      <c r="A100" s="5" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="26" t="inlineStr">
         <is>
           <t>P-2 CUEVA LOS PORTALES</t>
         </is>
       </c>
-      <c r="B100" s="7" t="n">
+      <c r="C100" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="C100" s="26" t="inlineStr">
+      <c r="D100" s="26" t="inlineStr">
         <is>
           <t>Director de las Instalaciones y/o los Complejos</t>
         </is>
       </c>
-      <c r="D100" s="27" t="inlineStr">
+      <c r="E100" s="27" t="inlineStr">
         <is>
           <t>XV</t>
         </is>
       </c>
-      <c r="E100" s="28" t="n">
+      <c r="F100" s="28" t="n">
         <v>7201</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="29" t="inlineStr">
+      <c r="A101" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" s="29" t="inlineStr">
         <is>
           <t>P-2 CUEVA LOS PORTALES</t>
         </is>
       </c>
-      <c r="B101" s="30" t="n">
+      <c r="C101" s="30" t="n">
         <v>26</v>
       </c>
-      <c r="C101" s="29" t="inlineStr">
+      <c r="D101" s="29" t="inlineStr">
         <is>
           <t>Sub Dtor Asistente Servicios y Calidad</t>
         </is>
       </c>
-      <c r="D101" s="31" t="inlineStr">
+      <c r="E101" s="31" t="inlineStr">
         <is>
           <t>XIV</t>
         </is>
       </c>
-      <c r="E101" s="32" t="n">
+      <c r="F101" s="32" t="n">
         <v>6668</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="26" t="inlineStr">
+      <c r="A102" s="5" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="26" t="inlineStr">
         <is>
           <t>P-2 CUEVA LOS PORTALES</t>
         </is>
       </c>
-      <c r="B102" s="7" t="n">
+      <c r="C102" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="C102" s="26" t="inlineStr">
+      <c r="D102" s="26" t="inlineStr">
         <is>
           <t>Chofer vehiculos ligeros</t>
         </is>
       </c>
-      <c r="D102" s="27" t="inlineStr">
+      <c r="E102" s="27" t="inlineStr">
         <is>
           <t>VIII</t>
         </is>
       </c>
-      <c r="E102" s="28" t="n">
+      <c r="F102" s="28" t="n">
         <v>4402</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="29" t="inlineStr">
+      <c r="A103" s="5" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" s="29" t="inlineStr">
         <is>
           <t>P-2 CUEVA LOS PORTALES</t>
         </is>
       </c>
-      <c r="B103" s="30" t="n">
+      <c r="C103" s="30" t="n">
         <v>28</v>
       </c>
-      <c r="C103" s="29" t="inlineStr">
+      <c r="D103" s="29" t="inlineStr">
         <is>
           <t>Tecnico  en Gestion de Capital  Humanos</t>
         </is>
       </c>
-      <c r="D103" s="31" t="inlineStr">
+      <c r="E103" s="31" t="inlineStr">
         <is>
           <t>XI</t>
         </is>
       </c>
-      <c r="E103" s="32" t="n">
+      <c r="F103" s="32" t="n">
         <v>5343</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="26" t="inlineStr">
+      <c r="A104" s="5" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" s="26" t="inlineStr">
         <is>
           <t>P-2 CUEVA LOS PORTALES</t>
         </is>
       </c>
-      <c r="B104" s="7" t="n">
+      <c r="C104" s="7" t="n">
         <v>29</v>
       </c>
-      <c r="C104" s="26" t="inlineStr">
+      <c r="D104" s="26" t="inlineStr">
         <is>
           <t>Operario labores agropec. Y jardineria</t>
         </is>
       </c>
-      <c r="D104" s="27" t="inlineStr">
+      <c r="E104" s="27" t="inlineStr">
         <is>
           <t>VIII</t>
         </is>
       </c>
-      <c r="E104" s="28" t="n">
+      <c r="F104" s="28" t="n">
         <v>4402</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="29" t="inlineStr">
+      <c r="A105" s="5" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="29" t="inlineStr">
         <is>
           <t>P-2 CUEVA LOS PORTALES</t>
         </is>
       </c>
-      <c r="B105" s="30" t="n">
+      <c r="C105" s="30" t="n">
         <v>31</v>
       </c>
-      <c r="C105" s="29" t="inlineStr">
+      <c r="D105" s="29" t="inlineStr">
         <is>
           <t>Técnico en Gestión Económica</t>
         </is>
       </c>
-      <c r="D105" s="31" t="inlineStr">
+      <c r="E105" s="31" t="inlineStr">
         <is>
           <t>XI</t>
         </is>
       </c>
-      <c r="E105" s="32" t="n">
+      <c r="F105" s="32" t="n">
         <v>5343</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="26" t="inlineStr">
+      <c r="A106" s="5" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="26" t="inlineStr">
         <is>
           <t>P-2 CUEVA LOS PORTALES</t>
         </is>
       </c>
-      <c r="B106" s="7" t="n">
+      <c r="C106" s="7" t="n">
         <v>33</v>
       </c>
-      <c r="C106" s="26" t="inlineStr">
+      <c r="D106" s="26" t="inlineStr">
         <is>
           <t>Dependiente  GastronomIco</t>
         </is>
       </c>
-      <c r="D106" s="27" t="inlineStr">
+      <c r="E106" s="27" t="inlineStr">
         <is>
           <t>IX</t>
         </is>
       </c>
-      <c r="E106" s="28" t="n">
+      <c r="F106" s="28" t="n">
         <v>4666</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="29" t="inlineStr">
+      <c r="A107" s="5" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="29" t="inlineStr">
         <is>
           <t>P-2 CUEVA LOS PORTALES</t>
         </is>
       </c>
-      <c r="B107" s="30" t="n">
+      <c r="C107" s="30" t="n">
         <v>34</v>
       </c>
-      <c r="C107" s="29" t="inlineStr">
+      <c r="D107" s="29" t="inlineStr">
         <is>
           <t>Nivel Medio Superior</t>
         </is>
       </c>
-      <c r="D107" s="31" t="inlineStr">
+      <c r="E107" s="31" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E107" s="32" t="n">
+      <c r="F107" s="32" t="n">
         <v>4993</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="26" t="inlineStr">
+      <c r="A108" s="5" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="26" t="inlineStr">
         <is>
           <t>P-2 CUEVA LOS PORTALES</t>
         </is>
       </c>
-      <c r="B108" s="7" t="n">
+      <c r="C108" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="C108" s="26" t="inlineStr">
+      <c r="D108" s="26" t="inlineStr">
         <is>
           <t>Elaborador de Alimentos</t>
         </is>
       </c>
-      <c r="D108" s="27" t="inlineStr">
+      <c r="E108" s="27" t="inlineStr">
         <is>
           <t>IX</t>
         </is>
       </c>
-      <c r="E108" s="28" t="n">
+      <c r="F108" s="28" t="n">
         <v>4666</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="29" t="inlineStr">
+      <c r="A109" s="5" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="29" t="inlineStr">
         <is>
           <t>P-2 CUEVA LOS PORTALES</t>
         </is>
       </c>
-      <c r="B109" s="30" t="n">
+      <c r="C109" s="30" t="n">
         <v>37</v>
       </c>
-      <c r="C109" s="29" t="inlineStr">
+      <c r="D109" s="29" t="inlineStr">
         <is>
           <t>Recepcionista Hotelero</t>
         </is>
       </c>
-      <c r="D109" s="31" t="inlineStr">
+      <c r="E109" s="31" t="inlineStr">
         <is>
           <t>IX</t>
         </is>
       </c>
-      <c r="E109" s="32" t="n">
+      <c r="F109" s="32" t="n">
         <v>4666</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="26" t="inlineStr">
+      <c r="A110" s="5" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="26" t="inlineStr">
         <is>
           <t>P-2 CUEVA LOS PORTALES</t>
         </is>
       </c>
-      <c r="B110" s="7" t="n">
+      <c r="C110" s="7" t="n">
         <v>38</v>
       </c>
-      <c r="C110" s="26" t="inlineStr">
+      <c r="D110" s="26" t="inlineStr">
         <is>
           <t>Camarera de Habitaciones</t>
         </is>
       </c>
-      <c r="D110" s="27" t="inlineStr">
+      <c r="E110" s="27" t="inlineStr">
         <is>
           <t>IX</t>
         </is>
       </c>
-      <c r="E110" s="28" t="n">
+      <c r="F110" s="28" t="n">
         <v>4666</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="29" t="inlineStr">
+      <c r="A111" s="5" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="29" t="inlineStr">
         <is>
           <t>P-2 CUEVA LOS PORTALES</t>
         </is>
       </c>
-      <c r="B111" s="30" t="n">
+      <c r="C111" s="30" t="n">
         <v>39</v>
       </c>
-      <c r="C111" s="29" t="inlineStr">
+      <c r="D111" s="29" t="inlineStr">
         <is>
           <t>Técnico en Recreación y animación</t>
         </is>
       </c>
-      <c r="D111" s="31" t="inlineStr">
+      <c r="E111" s="31" t="inlineStr">
         <is>
           <t>IX</t>
         </is>
       </c>
-      <c r="E111" s="32" t="n">
+      <c r="F111" s="32" t="n">
         <v>4666</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="26" t="inlineStr">
+      <c r="A112" s="5" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" s="26" t="inlineStr">
         <is>
           <t>P-2 CUEVA LOS PORTALES</t>
         </is>
       </c>
-      <c r="B112" s="7" t="n">
+      <c r="C112" s="7" t="n">
         <v>41</v>
       </c>
-      <c r="C112" s="26" t="inlineStr">
+      <c r="D112" s="26" t="inlineStr">
         <is>
           <t>Encargado de Almacén</t>
         </is>
       </c>
-      <c r="D112" s="27" t="inlineStr">
+      <c r="E112" s="27" t="inlineStr">
         <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="E112" s="28" t="n">
+      <c r="F112" s="28" t="n">
         <v>3918</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="29" t="inlineStr">
+      <c r="A113" s="5" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="29" t="inlineStr">
         <is>
           <t>P-2 CUEVA LOS PORTALES</t>
         </is>
       </c>
-      <c r="B113" s="30" t="n">
+      <c r="C113" s="30" t="n">
         <v>42</v>
       </c>
-      <c r="C113" s="29" t="inlineStr">
+      <c r="D113" s="29" t="inlineStr">
         <is>
           <t>Operario de Mante. Y Serv. Tecn.</t>
         </is>
       </c>
-      <c r="D113" s="31" t="inlineStr">
+      <c r="E113" s="31" t="inlineStr">
         <is>
           <t>VII</t>
         </is>
       </c>
-      <c r="E113" s="32" t="n">
+      <c r="F113" s="32" t="n">
         <v>4153</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="26" t="inlineStr">
+      <c r="A114" s="5" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" s="26" t="inlineStr">
         <is>
           <t>P-2 CUEVA LOS PORTALES</t>
         </is>
       </c>
-      <c r="B114" s="7" t="n">
+      <c r="C114" s="7" t="n">
         <v>43</v>
       </c>
-      <c r="C114" s="26" t="inlineStr">
+      <c r="D114" s="26" t="inlineStr">
         <is>
           <t>Chofer vehiculos de carga</t>
         </is>
       </c>
-      <c r="D114" s="27" t="inlineStr">
+      <c r="E114" s="27" t="inlineStr">
         <is>
           <t>IX</t>
         </is>
       </c>
-      <c r="E114" s="28" t="n">
+      <c r="F114" s="28" t="n">
         <v>4666</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="29" t="inlineStr">
+      <c r="A115" s="5" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" s="29" t="inlineStr">
         <is>
           <t>P-2 CUEVA LOS PORTALES</t>
         </is>
       </c>
-      <c r="B115" s="30" t="n">
+      <c r="C115" s="30" t="n">
         <v>45</v>
       </c>
-      <c r="C115" s="29" t="inlineStr">
+      <c r="D115" s="29" t="inlineStr">
         <is>
           <t>Agente de Seguridad y Protección</t>
         </is>
       </c>
-      <c r="D115" s="31" t="inlineStr">
+      <c r="E115" s="31" t="inlineStr">
         <is>
           <t>VIII</t>
         </is>
       </c>
-      <c r="E115" s="32" t="n">
+      <c r="F115" s="32" t="n">
         <v>4402</v>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="26" t="inlineStr">
+      <c r="A116" s="5" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" s="26" t="inlineStr">
         <is>
           <t>P-2 SALTO LOS PORTALES</t>
         </is>
       </c>
-      <c r="B116" s="7" t="n">
+      <c r="C116" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="C116" s="26" t="inlineStr">
+      <c r="D116" s="26" t="inlineStr">
         <is>
           <t>Director de las Instalaciones y/o los Complejos</t>
         </is>
       </c>
-      <c r="D116" s="27" t="inlineStr">
+      <c r="E116" s="27" t="inlineStr">
         <is>
           <t>XIV</t>
         </is>
       </c>
-      <c r="E116" s="28" t="n">
+      <c r="F116" s="28" t="n">
         <v>6668</v>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="29" t="inlineStr">
+      <c r="A117" s="5" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" s="29" t="inlineStr">
         <is>
           <t>P-2 SALTO LOS PORTALES</t>
         </is>
       </c>
-      <c r="B117" s="30" t="n">
+      <c r="C117" s="30" t="n">
         <v>23</v>
       </c>
-      <c r="C117" s="29" t="inlineStr">
+      <c r="D117" s="29" t="inlineStr">
         <is>
           <t>Subdirector Asistente</t>
         </is>
       </c>
-      <c r="D117" s="31" t="inlineStr">
+      <c r="E117" s="31" t="inlineStr">
         <is>
           <t>XIII</t>
         </is>
       </c>
-      <c r="E117" s="32" t="n">
+      <c r="F117" s="32" t="n">
         <v>6174</v>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="26" t="inlineStr">
+      <c r="A118" s="5" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" s="26" t="inlineStr">
         <is>
           <t>P-2 SALTO LOS PORTALES</t>
         </is>
       </c>
-      <c r="B118" s="7" t="n">
+      <c r="C118" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="C118" s="26" t="inlineStr">
+      <c r="D118" s="26" t="inlineStr">
         <is>
           <t>Técnico  en Gestion de Capital   Humanos</t>
         </is>
       </c>
-      <c r="D118" s="27" t="inlineStr">
+      <c r="E118" s="27" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E118" s="28" t="n">
+      <c r="F118" s="28" t="n">
         <v>4993</v>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="29" t="inlineStr">
+      <c r="A119" s="5" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" s="29" t="inlineStr">
         <is>
           <t>P-2 SALTO LOS PORTALES</t>
         </is>
       </c>
-      <c r="B119" s="30" t="n">
+      <c r="C119" s="30" t="n">
         <v>26</v>
       </c>
-      <c r="C119" s="29" t="inlineStr">
+      <c r="D119" s="29" t="inlineStr">
         <is>
           <t>Especialista en Gestion  Economico.</t>
         </is>
       </c>
-      <c r="D119" s="31" t="inlineStr">
+      <c r="E119" s="31" t="inlineStr">
         <is>
           <t>XII</t>
         </is>
       </c>
-      <c r="E119" s="32" t="n">
+      <c r="F119" s="32" t="n">
         <v>5770</v>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="26" t="inlineStr">
+      <c r="A120" s="5" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" s="26" t="inlineStr">
         <is>
           <t>P-2 SALTO LOS PORTALES</t>
         </is>
       </c>
-      <c r="B120" s="7" t="n">
+      <c r="C120" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="C120" s="26" t="inlineStr">
+      <c r="D120" s="26" t="inlineStr">
         <is>
           <t>Tec. Gest. Economica(Cajero)</t>
         </is>
       </c>
-      <c r="D120" s="27" t="inlineStr">
+      <c r="E120" s="27" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E120" s="28" t="n">
+      <c r="F120" s="28" t="n">
         <v>4993</v>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="29" t="inlineStr">
+      <c r="A121" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" s="29" t="inlineStr">
         <is>
           <t>P-2 SALTO LOS PORTALES</t>
         </is>
       </c>
-      <c r="B121" s="30" t="n">
+      <c r="C121" s="30" t="n">
         <v>29</v>
       </c>
-      <c r="C121" s="29" t="inlineStr">
+      <c r="D121" s="29" t="inlineStr">
         <is>
           <t>Jefe de Brigada de los Servicios</t>
         </is>
       </c>
-      <c r="D121" s="31" t="inlineStr">
+      <c r="E121" s="31" t="inlineStr">
         <is>
           <t>XI</t>
         </is>
       </c>
-      <c r="E121" s="32" t="n">
+      <c r="F121" s="32" t="n">
         <v>5343</v>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="26" t="inlineStr">
+      <c r="A122" s="5" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" s="26" t="inlineStr">
         <is>
           <t>P-2 SALTO LOS PORTALES</t>
         </is>
       </c>
-      <c r="B122" s="7" t="n">
+      <c r="C122" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="C122" s="26" t="inlineStr">
+      <c r="D122" s="26" t="inlineStr">
         <is>
           <t>Dependiente Gastronómico</t>
         </is>
       </c>
-      <c r="D122" s="27" t="inlineStr">
+      <c r="E122" s="27" t="inlineStr">
         <is>
           <t>VIII</t>
         </is>
       </c>
-      <c r="E122" s="28" t="n">
+      <c r="F122" s="28" t="n">
         <v>4402</v>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="29" t="inlineStr">
+      <c r="A123" s="5" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" s="29" t="inlineStr">
         <is>
           <t>P-2 SALTO LOS PORTALES</t>
         </is>
       </c>
-      <c r="B123" s="30" t="n">
+      <c r="C123" s="30" t="n">
         <v>31</v>
       </c>
-      <c r="C123" s="29" t="inlineStr">
+      <c r="D123" s="29" t="inlineStr">
         <is>
           <t>Nivel Medio Superior</t>
         </is>
       </c>
-      <c r="D123" s="31" t="inlineStr">
+      <c r="E123" s="31" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E123" s="32" t="n">
+      <c r="F123" s="32" t="n">
         <v>4993</v>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="26" t="inlineStr">
+      <c r="A124" s="5" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" s="26" t="inlineStr">
         <is>
           <t>P-2 SALTO LOS PORTALES</t>
         </is>
       </c>
-      <c r="B124" s="7" t="n">
+      <c r="C124" s="7" t="n">
         <v>32</v>
       </c>
-      <c r="C124" s="26" t="inlineStr">
+      <c r="D124" s="26" t="inlineStr">
         <is>
           <t>Nivel Medio</t>
         </is>
       </c>
-      <c r="D124" s="27" t="inlineStr">
+      <c r="E124" s="27" t="inlineStr">
         <is>
           <t>IX</t>
         </is>
       </c>
-      <c r="E124" s="28" t="n">
+      <c r="F124" s="28" t="n">
         <v>4666</v>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="29" t="inlineStr">
+      <c r="A125" s="5" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" s="29" t="inlineStr">
         <is>
           <t>P-2 SALTO LOS PORTALES</t>
         </is>
       </c>
-      <c r="B125" s="30" t="n">
+      <c r="C125" s="30" t="n">
         <v>33</v>
       </c>
-      <c r="C125" s="29" t="inlineStr">
+      <c r="D125" s="29" t="inlineStr">
         <is>
           <t>Elaborador de Alimentos</t>
         </is>
       </c>
-      <c r="D125" s="31" t="inlineStr">
+      <c r="E125" s="31" t="inlineStr">
         <is>
           <t>VIII</t>
         </is>
       </c>
-      <c r="E125" s="32" t="n">
+      <c r="F125" s="32" t="n">
         <v>4402</v>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="26" t="inlineStr">
+      <c r="A126" s="5" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" s="26" t="inlineStr">
         <is>
           <t>P-2 SALTO LOS PORTALES</t>
         </is>
       </c>
-      <c r="B126" s="7" t="n">
+      <c r="C126" s="7" t="n">
         <v>34</v>
       </c>
-      <c r="C126" s="26" t="inlineStr">
+      <c r="D126" s="26" t="inlineStr">
         <is>
           <t>Ayudante de Cocina</t>
         </is>
       </c>
-      <c r="D126" s="27" t="inlineStr">
+      <c r="E126" s="27" t="inlineStr">
         <is>
           <t>VII</t>
         </is>
       </c>
-      <c r="E126" s="28" t="n">
+      <c r="F126" s="28" t="n">
         <v>4153</v>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="29" t="inlineStr">
+      <c r="A127" s="5" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" s="29" t="inlineStr">
         <is>
           <t>P-2 SALTO LOS PORTALES</t>
         </is>
       </c>
-      <c r="B127" s="30" t="n">
+      <c r="C127" s="30" t="n">
         <v>36</v>
       </c>
-      <c r="C127" s="29" t="inlineStr">
+      <c r="D127" s="29" t="inlineStr">
         <is>
           <t>Recepcionista Hotelero</t>
         </is>
       </c>
-      <c r="D127" s="31" t="inlineStr">
+      <c r="E127" s="31" t="inlineStr">
         <is>
           <t>VIII</t>
         </is>
       </c>
-      <c r="E127" s="32" t="n">
+      <c r="F127" s="32" t="n">
         <v>4402</v>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="26" t="inlineStr">
+      <c r="A128" s="5" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" s="26" t="inlineStr">
         <is>
           <t>P-2 SALTO LOS PORTALES</t>
         </is>
       </c>
-      <c r="B128" s="7" t="n">
+      <c r="C128" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="C128" s="26" t="inlineStr">
+      <c r="D128" s="26" t="inlineStr">
         <is>
           <t>Camarera de Habitaciones</t>
         </is>
       </c>
-      <c r="D128" s="27" t="inlineStr">
+      <c r="E128" s="27" t="inlineStr">
         <is>
           <t>VIII</t>
         </is>
       </c>
-      <c r="E128" s="28" t="n">
+      <c r="F128" s="28" t="n">
         <v>4402</v>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="29" t="inlineStr">
+      <c r="A129" s="5" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" s="29" t="inlineStr">
         <is>
           <t>P-2 SALTO LOS PORTALES</t>
         </is>
       </c>
-      <c r="B129" s="30" t="n">
+      <c r="C129" s="30" t="n">
         <v>38</v>
       </c>
-      <c r="C129" s="29" t="inlineStr">
+      <c r="D129" s="29" t="inlineStr">
         <is>
           <t>Técnico en Recreación y Animación</t>
         </is>
       </c>
-      <c r="D129" s="31" t="inlineStr">
+      <c r="E129" s="31" t="inlineStr">
         <is>
           <t>VIII</t>
         </is>
       </c>
-      <c r="E129" s="32" t="n">
+      <c r="F129" s="32" t="n">
         <v>4402</v>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="26" t="inlineStr">
+      <c r="A130" s="5" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" s="26" t="inlineStr">
         <is>
           <t>P-2 SALTO LOS PORTALES</t>
         </is>
       </c>
-      <c r="B130" s="7" t="n">
+      <c r="C130" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="C130" s="26" t="inlineStr">
+      <c r="D130" s="26" t="inlineStr">
         <is>
           <t>Encargado de Almacén</t>
         </is>
       </c>
-      <c r="D130" s="27" t="inlineStr">
+      <c r="E130" s="27" t="inlineStr">
         <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="E130" s="28" t="n">
+      <c r="F130" s="28" t="n">
         <v>3918</v>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="29" t="inlineStr">
+      <c r="A131" s="5" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" s="29" t="inlineStr">
         <is>
           <t>P-2 SALTO LOS PORTALES</t>
         </is>
       </c>
-      <c r="B131" s="30" t="n">
+      <c r="C131" s="30" t="n">
         <v>41</v>
       </c>
-      <c r="C131" s="29" t="inlineStr">
+      <c r="D131" s="29" t="inlineStr">
         <is>
           <t>Chofer vehiculos de carga</t>
         </is>
       </c>
-      <c r="D131" s="31" t="inlineStr">
+      <c r="E131" s="31" t="inlineStr">
         <is>
           <t>VIII</t>
         </is>
       </c>
-      <c r="E131" s="32" t="n">
+      <c r="F131" s="32" t="n">
         <v>4402</v>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="26" t="inlineStr">
+      <c r="A132" s="5" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" s="26" t="inlineStr">
         <is>
           <t>P-2 SALTO LOS PORTALES</t>
         </is>
       </c>
-      <c r="B132" s="7" t="n">
+      <c r="C132" s="7" t="n">
         <v>42</v>
       </c>
-      <c r="C132" s="26" t="inlineStr">
+      <c r="D132" s="26" t="inlineStr">
         <is>
           <t>Operario de Mant. Y SERV. Tecnicos</t>
         </is>
       </c>
-      <c r="D132" s="27" t="inlineStr">
+      <c r="E132" s="27" t="inlineStr">
         <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="E132" s="28" t="n">
+      <c r="F132" s="28" t="n">
         <v>3918</v>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="29" t="inlineStr">
+      <c r="A133" s="5" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" s="29" t="inlineStr">
         <is>
           <t>P-2 SALTO LOS PORTALES</t>
         </is>
       </c>
-      <c r="B133" s="30" t="n">
+      <c r="C133" s="30" t="n">
         <v>44</v>
       </c>
-      <c r="C133" s="29" t="inlineStr">
+      <c r="D133" s="29" t="inlineStr">
         <is>
           <t>Jefe de Grupo de Seguridad Interna</t>
         </is>
       </c>
-      <c r="D133" s="31" t="inlineStr">
+      <c r="E133" s="31" t="inlineStr">
         <is>
           <t>XI</t>
         </is>
       </c>
-      <c r="E133" s="32" t="n">
+      <c r="F133" s="32" t="n">
         <v>5343</v>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="26" t="inlineStr">
+      <c r="A134" s="5" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" s="26" t="inlineStr">
         <is>
           <t>P-2 SALTO LOS PORTALES</t>
         </is>
       </c>
-      <c r="B134" s="7" t="n">
+      <c r="C134" s="7" t="n">
         <v>45</v>
       </c>
-      <c r="C134" s="26" t="inlineStr">
+      <c r="D134" s="26" t="inlineStr">
         <is>
           <t>Agente de Seguridad  y Protección</t>
         </is>
       </c>
-      <c r="D134" s="27" t="inlineStr">
+      <c r="E134" s="27" t="inlineStr">
         <is>
           <t>VII</t>
         </is>
       </c>
-      <c r="E134" s="28" t="n">
+      <c r="F134" s="28" t="n">
         <v>4153</v>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="29" t="inlineStr">
+      <c r="A135" s="5" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" s="29" t="inlineStr">
         <is>
           <t>P-2 EL COPEY</t>
         </is>
       </c>
-      <c r="B135" s="30" t="n">
+      <c r="C135" s="30" t="n">
         <v>24</v>
       </c>
-      <c r="C135" s="29" t="inlineStr">
+      <c r="D135" s="29" t="inlineStr">
         <is>
           <t>Director de las Instalaciones y/o los Complejos</t>
         </is>
       </c>
-      <c r="D135" s="31" t="inlineStr">
+      <c r="E135" s="31" t="inlineStr">
         <is>
           <t>XIII</t>
         </is>
       </c>
-      <c r="E135" s="32" t="n">
+      <c r="F135" s="32" t="n">
         <v>6174</v>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="26" t="inlineStr">
+      <c r="A136" s="5" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" s="26" t="inlineStr">
         <is>
           <t>P-2 EL COPEY</t>
         </is>
       </c>
-      <c r="B136" s="7" t="n">
+      <c r="C136" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="C136" s="26" t="inlineStr">
+      <c r="D136" s="26" t="inlineStr">
         <is>
           <t>Subdirector Asistente</t>
         </is>
       </c>
-      <c r="D136" s="27" t="inlineStr">
+      <c r="E136" s="27" t="inlineStr">
         <is>
           <t>XII</t>
         </is>
       </c>
-      <c r="E136" s="28" t="n">
+      <c r="F136" s="28" t="n">
         <v>5770</v>
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="29" t="inlineStr">
+      <c r="A137" s="5" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" s="29" t="inlineStr">
         <is>
           <t>P-2 EL COPEY</t>
         </is>
       </c>
-      <c r="B137" s="30" t="n">
+      <c r="C137" s="30" t="n">
         <v>26</v>
       </c>
-      <c r="C137" s="29" t="inlineStr">
+      <c r="D137" s="29" t="inlineStr">
         <is>
           <t>Sub Director Servicios</t>
         </is>
       </c>
-      <c r="D137" s="31" t="inlineStr">
+      <c r="E137" s="31" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E137" s="32" t="n">
+      <c r="F137" s="32" t="n">
         <v>4993</v>
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="26" t="inlineStr">
+      <c r="A138" s="5" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" s="26" t="inlineStr">
         <is>
           <t>P-2 EL COPEY</t>
         </is>
       </c>
-      <c r="B138" s="7" t="n">
+      <c r="C138" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="C138" s="26" t="inlineStr">
+      <c r="D138" s="26" t="inlineStr">
         <is>
           <t>Chofer vehiculos ligeros</t>
         </is>
       </c>
-      <c r="D138" s="27" t="inlineStr">
+      <c r="E138" s="27" t="inlineStr">
         <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="E138" s="28" t="n">
+      <c r="F138" s="28" t="n">
         <v>3918</v>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="29" t="inlineStr">
+      <c r="A139" s="5" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" s="29" t="inlineStr">
         <is>
           <t>P-2 EL COPEY</t>
         </is>
       </c>
-      <c r="B139" s="30" t="n">
+      <c r="C139" s="30" t="n">
         <v>28</v>
       </c>
-      <c r="C139" s="29" t="inlineStr">
+      <c r="D139" s="29" t="inlineStr">
         <is>
           <t>Tècnico en gestion de capital  Humanos</t>
         </is>
       </c>
-      <c r="D139" s="31" t="inlineStr">
+      <c r="E139" s="31" t="inlineStr">
         <is>
           <t>IX</t>
         </is>
       </c>
-      <c r="E139" s="32" t="n">
+      <c r="F139" s="32" t="n">
         <v>4666</v>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="26" t="inlineStr">
+      <c r="A140" s="5" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" s="26" t="inlineStr">
         <is>
           <t>P-2 EL COPEY</t>
         </is>
       </c>
-      <c r="B140" s="7" t="n">
+      <c r="C140" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="C140" s="26" t="inlineStr">
+      <c r="D140" s="26" t="inlineStr">
         <is>
           <t>Tecnico en Gestion Economica</t>
         </is>
       </c>
-      <c r="D140" s="27" t="inlineStr">
+      <c r="E140" s="27" t="inlineStr">
         <is>
           <t>IX</t>
         </is>
       </c>
-      <c r="E140" s="28" t="n">
+      <c r="F140" s="28" t="n">
         <v>4666</v>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="29" t="inlineStr">
+      <c r="A141" s="5" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" s="29" t="inlineStr">
         <is>
           <t>P-2 EL COPEY</t>
         </is>
       </c>
-      <c r="B141" s="30" t="n">
+      <c r="C141" s="30" t="n">
         <v>31</v>
       </c>
-      <c r="C141" s="29" t="inlineStr">
+      <c r="D141" s="29" t="inlineStr">
         <is>
           <t>Tecnico en Gestion Economica Cajero Pagador</t>
         </is>
       </c>
-      <c r="D141" s="31" t="inlineStr">
+      <c r="E141" s="31" t="inlineStr">
         <is>
           <t>IX</t>
         </is>
       </c>
-      <c r="E141" s="32" t="n">
+      <c r="F141" s="32" t="n">
         <v>4666</v>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="26" t="inlineStr">
+      <c r="A142" s="5" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" s="26" t="inlineStr">
         <is>
           <t>P-2 EL COPEY</t>
         </is>
       </c>
-      <c r="B142" s="7" t="n">
+      <c r="C142" s="7" t="n">
         <v>33</v>
       </c>
-      <c r="C142" s="26" t="inlineStr">
+      <c r="D142" s="26" t="inlineStr">
         <is>
           <t>Dependiente Gastronomico</t>
         </is>
       </c>
-      <c r="D142" s="27" t="inlineStr">
+      <c r="E142" s="27" t="inlineStr">
         <is>
           <t>VII</t>
         </is>
       </c>
-      <c r="E142" s="28" t="n">
+      <c r="F142" s="28" t="n">
         <v>4153</v>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="29" t="inlineStr">
+      <c r="A143" s="5" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" s="29" t="inlineStr">
         <is>
           <t>P-2 EL COPEY</t>
         </is>
       </c>
-      <c r="B143" s="30" t="n">
+      <c r="C143" s="30" t="n">
         <v>34</v>
       </c>
-      <c r="C143" s="29" t="inlineStr">
+      <c r="D143" s="29" t="inlineStr">
         <is>
           <t>Nivel Medio Superior</t>
         </is>
       </c>
-      <c r="D143" s="31" t="inlineStr">
+      <c r="E143" s="31" t="inlineStr">
         <is>
           <t>VIII</t>
         </is>
       </c>
-      <c r="E143" s="32" t="n">
+      <c r="F143" s="32" t="n">
         <v>4402</v>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="26" t="inlineStr">
+      <c r="A144" s="5" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" s="26" t="inlineStr">
         <is>
           <t>P-2 EL COPEY</t>
         </is>
       </c>
-      <c r="B144" s="7" t="n">
+      <c r="C144" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="C144" s="26" t="inlineStr">
+      <c r="D144" s="26" t="inlineStr">
         <is>
           <t>Elaborador de Alimentos</t>
         </is>
       </c>
-      <c r="D144" s="27" t="inlineStr">
+      <c r="E144" s="27" t="inlineStr">
         <is>
           <t>VII</t>
         </is>
       </c>
-      <c r="E144" s="28" t="n">
+      <c r="F144" s="28" t="n">
         <v>4153</v>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="29" t="inlineStr">
+      <c r="A145" s="5" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" s="29" t="inlineStr">
         <is>
           <t>P-2 EL COPEY</t>
         </is>
       </c>
-      <c r="B145" s="30" t="n">
+      <c r="C145" s="30" t="n">
         <v>37</v>
       </c>
-      <c r="C145" s="29" t="inlineStr">
+      <c r="D145" s="29" t="inlineStr">
         <is>
           <t>Recepcionista Hotelero</t>
         </is>
       </c>
-      <c r="D145" s="31" t="inlineStr">
+      <c r="E145" s="31" t="inlineStr">
         <is>
           <t>VII</t>
         </is>
       </c>
-      <c r="E145" s="32" t="n">
+      <c r="F145" s="32" t="n">
         <v>4153</v>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="26" t="inlineStr">
+      <c r="A146" s="5" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" s="26" t="inlineStr">
         <is>
           <t>P-2 EL COPEY</t>
         </is>
       </c>
-      <c r="B146" s="7" t="n">
+      <c r="C146" s="7" t="n">
         <v>38</v>
       </c>
-      <c r="C146" s="26" t="inlineStr">
+      <c r="D146" s="26" t="inlineStr">
         <is>
           <t>Camarera de Habitaciones</t>
         </is>
       </c>
-      <c r="D146" s="27" t="inlineStr">
+      <c r="E146" s="27" t="inlineStr">
         <is>
           <t>VII</t>
         </is>
       </c>
-      <c r="E146" s="28" t="n">
+      <c r="F146" s="28" t="n">
         <v>4153</v>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="29" t="inlineStr">
+      <c r="A147" s="5" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" s="29" t="inlineStr">
         <is>
           <t>P-2 EL COPEY</t>
         </is>
       </c>
-      <c r="B147" s="30" t="n">
+      <c r="C147" s="30" t="n">
         <v>40</v>
       </c>
-      <c r="C147" s="29" t="inlineStr">
+      <c r="D147" s="29" t="inlineStr">
         <is>
           <t>Tècnico de Recreación y Animación</t>
         </is>
       </c>
-      <c r="D147" s="31" t="inlineStr">
+      <c r="E147" s="31" t="inlineStr">
         <is>
           <t>VII</t>
         </is>
       </c>
-      <c r="E147" s="32" t="n">
+      <c r="F147" s="32" t="n">
         <v>4153</v>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="26" t="inlineStr">
+      <c r="A148" s="5" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" s="26" t="inlineStr">
         <is>
           <t>P-2 EL COPEY</t>
         </is>
       </c>
-      <c r="B148" s="7" t="n">
+      <c r="C148" s="7" t="n">
         <v>42</v>
       </c>
-      <c r="C148" s="26" t="inlineStr">
+      <c r="D148" s="26" t="inlineStr">
         <is>
           <t>Encargado de Almacèn</t>
         </is>
       </c>
-      <c r="D148" s="27" t="inlineStr">
+      <c r="E148" s="27" t="inlineStr">
         <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="E148" s="28" t="n">
+      <c r="F148" s="28" t="n">
         <v>3918</v>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="29" t="inlineStr">
+      <c r="A149" s="5" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" s="29" t="inlineStr">
         <is>
           <t>P-2 EL COPEY</t>
         </is>
       </c>
-      <c r="B149" s="30" t="n">
+      <c r="C149" s="30" t="n">
         <v>43</v>
       </c>
-      <c r="C149" s="29" t="inlineStr">
+      <c r="D149" s="29" t="inlineStr">
         <is>
           <t>Operario de Mant. Y Serv. Tecnicos</t>
         </is>
       </c>
-      <c r="D149" s="31" t="inlineStr">
+      <c r="E149" s="31" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="E149" s="32" t="n">
+      <c r="F149" s="32" t="n">
         <v>3696</v>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="26" t="inlineStr">
+      <c r="A150" s="5" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" s="26" t="inlineStr">
         <is>
           <t>P-2 EL COPEY</t>
         </is>
       </c>
-      <c r="B150" s="7" t="n">
+      <c r="C150" s="7" t="n">
         <v>45</v>
       </c>
-      <c r="C150" s="26" t="inlineStr">
+      <c r="D150" s="26" t="inlineStr">
         <is>
           <t>Jefe de Grupo de Seguridad Interna</t>
         </is>
       </c>
-      <c r="D150" s="27" t="inlineStr">
+      <c r="E150" s="27" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E150" s="28" t="n">
+      <c r="F150" s="28" t="n">
         <v>4993</v>
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="29" t="inlineStr">
+      <c r="A151" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" s="29" t="inlineStr">
         <is>
           <t>P-2 EL COPEY</t>
         </is>
       </c>
-      <c r="B151" s="30" t="n">
+      <c r="C151" s="30" t="n">
         <v>46</v>
       </c>
-      <c r="C151" s="29" t="inlineStr">
+      <c r="D151" s="29" t="inlineStr">
         <is>
           <t>Agente de Seguridad y Protecciòn</t>
         </is>
       </c>
-      <c r="D151" s="31" t="inlineStr">
+      <c r="E151" s="31" t="inlineStr">
         <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="E151" s="32" t="n">
+      <c r="F151" s="32" t="n">
         <v>3918</v>
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="26" t="inlineStr">
+      <c r="A152" s="5" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" s="26" t="inlineStr">
         <is>
           <t>P-2 PAJARITO</t>
         </is>
       </c>
-      <c r="B152" s="7" t="n">
+      <c r="C152" s="7" t="n">
         <v>26</v>
       </c>
-      <c r="C152" s="26" t="inlineStr">
+      <c r="D152" s="26" t="inlineStr">
         <is>
           <t>Director de las Instalaciones y/o los Complejos</t>
         </is>
       </c>
-      <c r="D152" s="27" t="inlineStr">
+      <c r="E152" s="27" t="inlineStr">
         <is>
           <t>XIII</t>
         </is>
       </c>
-      <c r="E152" s="28" t="n">
+      <c r="F152" s="28" t="n">
         <v>6174</v>
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="29" t="inlineStr">
+      <c r="A153" s="5" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" s="29" t="inlineStr">
         <is>
           <t>P-2 PAJARITO</t>
         </is>
       </c>
-      <c r="B153" s="30" t="n">
+      <c r="C153" s="30" t="n">
         <v>27</v>
       </c>
-      <c r="C153" s="29" t="inlineStr">
+      <c r="D153" s="29" t="inlineStr">
         <is>
           <t>Subdirector Asistente de Servicios y Calidad</t>
         </is>
       </c>
-      <c r="D153" s="31" t="inlineStr">
+      <c r="E153" s="31" t="inlineStr">
         <is>
           <t>XII</t>
         </is>
       </c>
-      <c r="E153" s="32" t="n">
+      <c r="F153" s="32" t="n">
         <v>5770</v>
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="26" t="inlineStr">
+      <c r="A154" s="5" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" s="26" t="inlineStr">
         <is>
           <t>P-2 PAJARITO</t>
         </is>
       </c>
-      <c r="B154" s="7" t="n">
+      <c r="C154" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="C154" s="26" t="inlineStr">
+      <c r="D154" s="26" t="inlineStr">
         <is>
           <t>Subdirector Asistente de  Control Interno</t>
         </is>
       </c>
-      <c r="D154" s="27" t="inlineStr">
+      <c r="E154" s="27" t="inlineStr">
         <is>
           <t>XII</t>
         </is>
       </c>
-      <c r="E154" s="28" t="n">
+      <c r="F154" s="28" t="n">
         <v>5770</v>
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="29" t="inlineStr">
+      <c r="A155" s="5" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" s="29" t="inlineStr">
         <is>
           <t>P-2 PAJARITO</t>
         </is>
       </c>
-      <c r="B155" s="30" t="n">
+      <c r="C155" s="30" t="n">
         <v>29</v>
       </c>
-      <c r="C155" s="29" t="inlineStr">
+      <c r="D155" s="29" t="inlineStr">
         <is>
           <t>Tecnico  en Gestion de Capital Humanos</t>
         </is>
       </c>
-      <c r="D155" s="31" t="inlineStr">
+      <c r="E155" s="31" t="inlineStr">
         <is>
           <t>IX</t>
         </is>
       </c>
-      <c r="E155" s="32" t="n">
+      <c r="F155" s="32" t="n">
         <v>4666</v>
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="26" t="inlineStr">
+      <c r="A156" s="5" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" s="26" t="inlineStr">
         <is>
           <t>P-2 PAJARITO</t>
         </is>
       </c>
-      <c r="B156" s="7" t="n">
+      <c r="C156" s="7" t="n">
         <v>31</v>
       </c>
-      <c r="C156" s="26" t="inlineStr">
+      <c r="D156" s="26" t="inlineStr">
         <is>
           <t>Técnico  en Gestión Económica</t>
         </is>
       </c>
-      <c r="D156" s="27" t="inlineStr">
+      <c r="E156" s="27" t="inlineStr">
         <is>
           <t>IX</t>
         </is>
       </c>
-      <c r="E156" s="28" t="n">
+      <c r="F156" s="28" t="n">
         <v>4666</v>
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="29" t="inlineStr">
+      <c r="A157" s="5" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" s="29" t="inlineStr">
         <is>
           <t>P-2 PAJARITO</t>
         </is>
       </c>
-      <c r="B157" s="30" t="n">
+      <c r="C157" s="30" t="n">
         <v>33</v>
       </c>
-      <c r="C157" s="29" t="inlineStr">
+      <c r="D157" s="29" t="inlineStr">
         <is>
           <t>Dependiente Gastronómico</t>
         </is>
       </c>
-      <c r="D157" s="31" t="inlineStr">
+      <c r="E157" s="31" t="inlineStr">
         <is>
           <t>VII</t>
         </is>
       </c>
-      <c r="E157" s="32" t="n">
+      <c r="F157" s="32" t="n">
         <v>4153</v>
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="26" t="inlineStr">
+      <c r="A158" s="5" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" s="26" t="inlineStr">
         <is>
           <t>P-2 PAJARITO</t>
         </is>
       </c>
-      <c r="B158" s="7" t="n">
+      <c r="C158" s="7" t="n">
         <v>34</v>
       </c>
-      <c r="C158" s="26" t="inlineStr">
+      <c r="D158" s="26" t="inlineStr">
         <is>
           <t>Nivel Medio Superior</t>
         </is>
       </c>
-      <c r="D158" s="27" t="inlineStr">
+      <c r="E158" s="27" t="inlineStr">
         <is>
           <t>VIII</t>
         </is>
       </c>
-      <c r="E158" s="28" t="n">
+      <c r="F158" s="28" t="n">
         <v>4402</v>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="29" t="inlineStr">
+      <c r="A159" s="5" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" s="29" t="inlineStr">
         <is>
           <t>P-2 PAJARITO</t>
         </is>
       </c>
-      <c r="B159" s="30" t="n">
+      <c r="C159" s="30" t="n">
         <v>35</v>
       </c>
-      <c r="C159" s="29" t="inlineStr">
+      <c r="D159" s="29" t="inlineStr">
         <is>
           <t>Elaborador de Alimentos</t>
         </is>
       </c>
-      <c r="D159" s="31" t="inlineStr">
+      <c r="E159" s="31" t="inlineStr">
         <is>
           <t>VII</t>
         </is>
       </c>
-      <c r="E159" s="32" t="n">
+      <c r="F159" s="32" t="n">
         <v>4153</v>
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="26" t="inlineStr">
+      <c r="A160" s="5" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" s="26" t="inlineStr">
         <is>
           <t>P-2 PAJARITO</t>
         </is>
       </c>
-      <c r="B160" s="7" t="n">
+      <c r="C160" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="C160" s="26" t="inlineStr">
+      <c r="D160" s="26" t="inlineStr">
         <is>
           <t>Recepcionista Hotelero</t>
         </is>
       </c>
-      <c r="D160" s="27" t="inlineStr">
+      <c r="E160" s="27" t="inlineStr">
         <is>
           <t>VII</t>
         </is>
       </c>
-      <c r="E160" s="28" t="n">
+      <c r="F160" s="28" t="n">
         <v>4153</v>
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="29" t="inlineStr">
+      <c r="A161" s="5" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" s="29" t="inlineStr">
         <is>
           <t>P-2 PAJARITO</t>
         </is>
       </c>
-      <c r="B161" s="30" t="n">
+      <c r="C161" s="30" t="n">
         <v>38</v>
       </c>
-      <c r="C161" s="29" t="inlineStr">
+      <c r="D161" s="29" t="inlineStr">
         <is>
           <t>Camarera de Habitaciones</t>
         </is>
       </c>
-      <c r="D161" s="31" t="inlineStr">
+      <c r="E161" s="31" t="inlineStr">
         <is>
           <t>VII</t>
         </is>
       </c>
-      <c r="E161" s="32" t="n">
+      <c r="F161" s="32" t="n">
         <v>4153</v>
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="26" t="inlineStr">
+      <c r="A162" s="5" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" s="26" t="inlineStr">
         <is>
           <t>P-2 PAJARITO</t>
         </is>
       </c>
-      <c r="B162" s="7" t="n">
+      <c r="C162" s="7" t="n">
         <v>39</v>
       </c>
-      <c r="C162" s="26" t="inlineStr">
+      <c r="D162" s="26" t="inlineStr">
         <is>
           <t>Técnico  en Recreación y Animación</t>
         </is>
       </c>
-      <c r="D162" s="27" t="inlineStr">
+      <c r="E162" s="27" t="inlineStr">
         <is>
           <t>VII</t>
         </is>
       </c>
-      <c r="E162" s="28" t="n">
+      <c r="F162" s="28" t="n">
         <v>4153</v>
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="29" t="inlineStr">
+      <c r="A163" s="5" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" s="29" t="inlineStr">
         <is>
           <t>P-2 PAJARITO</t>
         </is>
       </c>
-      <c r="B163" s="30" t="n">
+      <c r="C163" s="30" t="n">
         <v>41</v>
       </c>
-      <c r="C163" s="29" t="inlineStr">
+      <c r="D163" s="29" t="inlineStr">
         <is>
           <t>Encargado de Almacén</t>
         </is>
       </c>
-      <c r="D163" s="31" t="inlineStr">
+      <c r="E163" s="31" t="inlineStr">
         <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="E163" s="32" t="n">
+      <c r="F163" s="32" t="n">
         <v>3918</v>
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="26" t="inlineStr">
+      <c r="A164" s="5" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" s="26" t="inlineStr">
         <is>
           <t>P-2 PAJARITO</t>
         </is>
       </c>
-      <c r="B164" s="7" t="n">
+      <c r="C164" s="7" t="n">
         <v>42</v>
       </c>
-      <c r="C164" s="26" t="inlineStr">
+      <c r="D164" s="26" t="inlineStr">
         <is>
           <t>Operario de Mant. Y SERV. TEC.</t>
         </is>
       </c>
-      <c r="D164" s="27" t="inlineStr">
+      <c r="E164" s="27" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="E164" s="28" t="n">
+      <c r="F164" s="28" t="n">
         <v>3696</v>
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="29" t="inlineStr">
+      <c r="A165" s="5" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" s="29" t="inlineStr">
         <is>
           <t>P-2 PAJARITO</t>
         </is>
       </c>
-      <c r="B165" s="30" t="n">
+      <c r="C165" s="30" t="n">
         <v>44</v>
       </c>
-      <c r="C165" s="29" t="inlineStr">
+      <c r="D165" s="29" t="inlineStr">
         <is>
           <t>Agente de Seguridad y Proteccion</t>
         </is>
       </c>
-      <c r="D165" s="31" t="inlineStr">
+      <c r="E165" s="31" t="inlineStr">
         <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="E165" s="32" t="n">
+      <c r="F165" s="32" t="n">
         <v>3918</v>
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="26" t="inlineStr">
+      <c r="A166" s="5" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" s="26" t="inlineStr">
         <is>
           <t>Boca de Galafre</t>
         </is>
       </c>
-      <c r="B166" s="7" t="n">
+      <c r="C166" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="C166" s="26" t="inlineStr">
+      <c r="D166" s="26" t="inlineStr">
         <is>
           <t>Director de las Instalaciones y/o los Complejos</t>
         </is>
       </c>
-      <c r="D166" s="27" t="inlineStr">
+      <c r="E166" s="27" t="inlineStr">
         <is>
           <t>XIII</t>
         </is>
       </c>
-      <c r="E166" s="28" t="n">
+      <c r="F166" s="28" t="n">
         <v>6174</v>
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="29" t="inlineStr">
+      <c r="A167" s="5" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" s="29" t="inlineStr">
         <is>
           <t>Boca de Galafre</t>
         </is>
       </c>
-      <c r="B167" s="30" t="n">
+      <c r="C167" s="30" t="n">
         <v>25</v>
       </c>
-      <c r="C167" s="29" t="inlineStr">
+      <c r="D167" s="29" t="inlineStr">
         <is>
           <t>Subdirector Asistente</t>
         </is>
       </c>
-      <c r="D167" s="31" t="inlineStr">
+      <c r="E167" s="31" t="inlineStr">
         <is>
           <t>XII</t>
         </is>
       </c>
-      <c r="E167" s="32" t="n">
+      <c r="F167" s="32" t="n">
         <v>5770</v>
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="26" t="inlineStr">
+      <c r="A168" s="5" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" s="26" t="inlineStr">
         <is>
           <t>Boca de Galafre</t>
         </is>
       </c>
-      <c r="B168" s="7" t="n">
+      <c r="C168" s="7" t="n">
         <v>26</v>
       </c>
-      <c r="C168" s="26" t="inlineStr">
+      <c r="D168" s="26" t="inlineStr">
         <is>
           <t>Jefe de Brigada de los Servicios</t>
         </is>
       </c>
-      <c r="D168" s="27" t="inlineStr">
+      <c r="E168" s="27" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E168" s="28" t="n">
+      <c r="F168" s="28" t="n">
         <v>4993</v>
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="29" t="inlineStr">
+      <c r="A169" s="5" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" s="29" t="inlineStr">
         <is>
           <t>Boca de Galafre</t>
         </is>
       </c>
-      <c r="B169" s="30" t="n">
+      <c r="C169" s="30" t="n">
         <v>27</v>
       </c>
-      <c r="C169" s="29" t="inlineStr">
+      <c r="D169" s="29" t="inlineStr">
         <is>
           <t>Chofer Vehiculos Ligeros</t>
         </is>
       </c>
-      <c r="D169" s="31" t="inlineStr">
+      <c r="E169" s="31" t="inlineStr">
         <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="E169" s="32" t="n">
+      <c r="F169" s="32" t="n">
         <v>3918</v>
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="26" t="inlineStr">
+      <c r="A170" s="5" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" s="26" t="inlineStr">
         <is>
           <t>Boca de Galafre</t>
         </is>
       </c>
-      <c r="B170" s="7" t="n">
+      <c r="C170" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="C170" s="26" t="inlineStr">
+      <c r="D170" s="26" t="inlineStr">
         <is>
           <t>Tecnico  en Gestion de Capital Humanos</t>
         </is>
       </c>
-      <c r="D170" s="27" t="inlineStr">
+      <c r="E170" s="27" t="inlineStr">
         <is>
           <t>IX</t>
         </is>
       </c>
-      <c r="E170" s="28" t="n">
+      <c r="F170" s="28" t="n">
         <v>4666</v>
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="29" t="inlineStr">
+      <c r="A171" s="5" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" s="29" t="inlineStr">
         <is>
           <t>Boca de Galafre</t>
         </is>
       </c>
-      <c r="B171" s="30" t="n">
+      <c r="C171" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="C171" s="29" t="inlineStr">
+      <c r="D171" s="29" t="inlineStr">
         <is>
           <t>Especialista en Gestion  Economica</t>
         </is>
       </c>
-      <c r="D171" s="31" t="inlineStr">
+      <c r="E171" s="31" t="inlineStr">
         <is>
           <t>XI</t>
         </is>
       </c>
-      <c r="E171" s="32" t="n">
+      <c r="F171" s="32" t="n">
         <v>5343</v>
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="26" t="inlineStr">
+      <c r="A172" s="5" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" s="26" t="inlineStr">
         <is>
           <t>Boca de Galafre</t>
         </is>
       </c>
-      <c r="B172" s="7" t="n">
+      <c r="C172" s="7" t="n">
         <v>31</v>
       </c>
-      <c r="C172" s="26" t="inlineStr">
+      <c r="D172" s="26" t="inlineStr">
         <is>
           <t>Técnico  en Gestión Económica</t>
         </is>
       </c>
-      <c r="D172" s="27" t="inlineStr">
+      <c r="E172" s="27" t="inlineStr">
         <is>
           <t>IX</t>
         </is>
       </c>
-      <c r="E172" s="28" t="n">
+      <c r="F172" s="28" t="n">
         <v>4666</v>
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="29" t="inlineStr">
+      <c r="A173" s="5" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" s="29" t="inlineStr">
         <is>
           <t>Boca de Galafre</t>
         </is>
       </c>
-      <c r="B173" s="30" t="n">
+      <c r="C173" s="30" t="n">
         <v>33</v>
       </c>
-      <c r="C173" s="29" t="inlineStr">
+      <c r="D173" s="29" t="inlineStr">
         <is>
           <t>Dependiente Gastronomico</t>
         </is>
       </c>
-      <c r="D173" s="31" t="inlineStr">
+      <c r="E173" s="31" t="inlineStr">
         <is>
           <t>VII</t>
         </is>
       </c>
-      <c r="E173" s="32" t="n">
+      <c r="F173" s="32" t="n">
         <v>4153</v>
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="26" t="inlineStr">
+      <c r="A174" s="5" t="n">
+        <v>173</v>
+      </c>
+      <c r="B174" s="26" t="inlineStr">
         <is>
           <t>Boca de Galafre</t>
         </is>
       </c>
-      <c r="B174" s="7" t="n">
+      <c r="C174" s="7" t="n">
         <v>34</v>
       </c>
-      <c r="C174" s="26" t="inlineStr">
+      <c r="D174" s="26" t="inlineStr">
         <is>
           <t>Nivel Medio Superior</t>
         </is>
       </c>
-      <c r="D174" s="27" t="inlineStr">
+      <c r="E174" s="27" t="inlineStr">
         <is>
           <t>VIII</t>
         </is>
       </c>
-      <c r="E174" s="28" t="n">
+      <c r="F174" s="28" t="n">
         <v>4402</v>
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="29" t="inlineStr">
+      <c r="A175" s="5" t="n">
+        <v>174</v>
+      </c>
+      <c r="B175" s="29" t="inlineStr">
         <is>
           <t>Boca de Galafre</t>
         </is>
       </c>
-      <c r="B175" s="30" t="n">
+      <c r="C175" s="30" t="n">
         <v>35</v>
       </c>
-      <c r="C175" s="29" t="inlineStr">
+      <c r="D175" s="29" t="inlineStr">
         <is>
           <t>Elaborador de Alimentos</t>
         </is>
       </c>
-      <c r="D175" s="31" t="inlineStr">
+      <c r="E175" s="31" t="inlineStr">
         <is>
           <t>VII</t>
         </is>
       </c>
-      <c r="E175" s="32" t="n">
+      <c r="F175" s="32" t="n">
         <v>4153</v>
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="26" t="inlineStr">
+      <c r="A176" s="5" t="n">
+        <v>175</v>
+      </c>
+      <c r="B176" s="26" t="inlineStr">
         <is>
           <t>Boca de Galafre</t>
         </is>
       </c>
-      <c r="B176" s="7" t="n">
+      <c r="C176" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="C176" s="26" t="inlineStr">
+      <c r="D176" s="26" t="inlineStr">
         <is>
           <t>Recepcionista Hotelero</t>
         </is>
       </c>
-      <c r="D176" s="27" t="inlineStr">
+      <c r="E176" s="27" t="inlineStr">
         <is>
           <t>VII</t>
         </is>
       </c>
-      <c r="E176" s="28" t="n">
+      <c r="F176" s="28" t="n">
         <v>4153</v>
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="29" t="inlineStr">
+      <c r="A177" s="5" t="n">
+        <v>176</v>
+      </c>
+      <c r="B177" s="29" t="inlineStr">
         <is>
           <t>Boca de Galafre</t>
         </is>
       </c>
-      <c r="B177" s="30" t="n">
+      <c r="C177" s="30" t="n">
         <v>38</v>
       </c>
-      <c r="C177" s="29" t="inlineStr">
+      <c r="D177" s="29" t="inlineStr">
         <is>
           <t>Camarera de Habitaciones</t>
         </is>
       </c>
-      <c r="D177" s="31" t="inlineStr">
+      <c r="E177" s="31" t="inlineStr">
         <is>
           <t>VII</t>
         </is>
       </c>
-      <c r="E177" s="32" t="n">
+      <c r="F177" s="32" t="n">
         <v>4153</v>
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="26" t="inlineStr">
+      <c r="A178" s="5" t="n">
+        <v>177</v>
+      </c>
+      <c r="B178" s="26" t="inlineStr">
         <is>
           <t>Boca de Galafre</t>
         </is>
       </c>
-      <c r="B178" s="7" t="n">
+      <c r="C178" s="7" t="n">
         <v>39</v>
       </c>
-      <c r="C178" s="26" t="inlineStr">
+      <c r="D178" s="26" t="inlineStr">
         <is>
           <t>Auxiliar General de  Servicios</t>
         </is>
       </c>
-      <c r="D178" s="27" t="inlineStr">
+      <c r="E178" s="27" t="inlineStr">
         <is>
           <t>IV</t>
         </is>
       </c>
-      <c r="E178" s="28" t="n">
+      <c r="F178" s="28" t="n">
         <v>3487</v>
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="29" t="inlineStr">
+      <c r="A179" s="5" t="n">
+        <v>178</v>
+      </c>
+      <c r="B179" s="29" t="inlineStr">
         <is>
           <t>Boca de Galafre</t>
         </is>
       </c>
-      <c r="B179" s="30" t="n">
+      <c r="C179" s="30" t="n">
         <v>40</v>
       </c>
-      <c r="C179" s="29" t="inlineStr">
+      <c r="D179" s="29" t="inlineStr">
         <is>
           <t>Técnico en Recreación y Animación JB</t>
         </is>
       </c>
-      <c r="D179" s="31" t="inlineStr">
+      <c r="E179" s="31" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E179" s="32" t="n">
+      <c r="F179" s="32" t="n">
         <v>4993</v>
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="26" t="inlineStr">
+      <c r="A180" s="5" t="n">
+        <v>179</v>
+      </c>
+      <c r="B180" s="26" t="inlineStr">
         <is>
           <t>Boca de Galafre</t>
         </is>
       </c>
-      <c r="B180" s="7" t="n">
+      <c r="C180" s="7" t="n">
         <v>41</v>
       </c>
-      <c r="C180" s="26" t="inlineStr">
+      <c r="D180" s="26" t="inlineStr">
         <is>
           <t>Técnico en Recreación y Animación</t>
         </is>
       </c>
-      <c r="D180" s="27" t="inlineStr">
+      <c r="E180" s="27" t="inlineStr">
         <is>
           <t>VII</t>
         </is>
       </c>
-      <c r="E180" s="28" t="n">
+      <c r="F180" s="28" t="n">
         <v>4153</v>
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="29" t="inlineStr">
+      <c r="A181" s="5" t="n">
+        <v>180</v>
+      </c>
+      <c r="B181" s="29" t="inlineStr">
         <is>
           <t>Boca de Galafre</t>
         </is>
       </c>
-      <c r="B181" s="30" t="n">
+      <c r="C181" s="30" t="n">
         <v>43</v>
       </c>
-      <c r="C181" s="29" t="inlineStr">
+      <c r="D181" s="29" t="inlineStr">
         <is>
           <t>Encargado de Almacén</t>
         </is>
       </c>
-      <c r="D181" s="31" t="inlineStr">
+      <c r="E181" s="31" t="inlineStr">
         <is>
           <t>VII</t>
         </is>
       </c>
-      <c r="E181" s="32" t="n">
+      <c r="F181" s="32" t="n">
         <v>4153</v>
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="26" t="inlineStr">
+      <c r="A182" s="5" t="n">
+        <v>181</v>
+      </c>
+      <c r="B182" s="26" t="inlineStr">
         <is>
           <t>Boca de Galafre</t>
         </is>
       </c>
-      <c r="B182" s="7" t="n">
+      <c r="C182" s="7" t="n">
         <v>44</v>
       </c>
-      <c r="C182" s="26" t="inlineStr">
+      <c r="D182" s="26" t="inlineStr">
         <is>
           <t>Operario de Mant. Y Serv, Tec.</t>
         </is>
       </c>
-      <c r="D182" s="27" t="inlineStr">
+      <c r="E182" s="27" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="E182" s="28" t="n">
+      <c r="F182" s="28" t="n">
         <v>3696</v>
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="29" t="inlineStr">
+      <c r="A183" s="5" t="n">
+        <v>182</v>
+      </c>
+      <c r="B183" s="29" t="inlineStr">
         <is>
           <t>Boca de Galafre</t>
         </is>
       </c>
-      <c r="B183" s="30" t="n">
+      <c r="C183" s="30" t="n">
         <v>46</v>
       </c>
-      <c r="C183" s="29" t="inlineStr">
+      <c r="D183" s="29" t="inlineStr">
         <is>
           <t>Jefes de Grupo de Seguridad Interna</t>
         </is>
       </c>
-      <c r="D183" s="31" t="inlineStr">
+      <c r="E183" s="31" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E183" s="32" t="n">
+      <c r="F183" s="32" t="n">
         <v>4993</v>
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="26" t="inlineStr">
+      <c r="A184" s="5" t="n">
+        <v>183</v>
+      </c>
+      <c r="B184" s="26" t="inlineStr">
         <is>
           <t>Boca de Galafre</t>
         </is>
       </c>
-      <c r="B184" s="7" t="n">
+      <c r="C184" s="7" t="n">
         <v>47</v>
       </c>
-      <c r="C184" s="26" t="inlineStr">
+      <c r="D184" s="26" t="inlineStr">
         <is>
           <t>Agente de Seguridad y Protección</t>
         </is>
       </c>
-      <c r="D184" s="27" t="inlineStr">
+      <c r="E184" s="27" t="inlineStr">
         <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="E184" s="28" t="n">
+      <c r="F184" s="28" t="n">
         <v>3918</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E184"/>
+  <autoFilter ref="A1:F184"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7053,7 +7608,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-28T22:03:38+00:00</t>
+          <t>2026-10-28T22:18:57+00:00</t>
         </is>
       </c>
     </row>
@@ -7229,16 +7784,16 @@
       </c>
       <c r="E10" s="42" t="inlineStr">
         <is>
-          <t>c41ad5dfcdabc308705d391cca7309377ba1dd7ec855c06bfe49b28a32c272e8</t>
+          <t>259b3e28b7d715fe7fb2cd0eaea0f440fd0df3a48199cf306ba89c5902f42d9b</t>
         </is>
       </c>
       <c r="F10" s="42" t="inlineStr">
         <is>
-          <t>c41ad5dfcdabc308705d391cca7309377ba1dd7ec855c06bfe49b28a32c272e8</t>
+          <t>259b3e28b7d715fe7fb2cd0eaea0f440fd0df3a48199cf306ba89c5902f42d9b</t>
         </is>
       </c>
       <c r="G10" s="39" t="n">
-        <v>37562</v>
+        <v>38904</v>
       </c>
     </row>
     <row r="11">
@@ -7264,16 +7819,16 @@
       </c>
       <c r="E11" s="42" t="inlineStr">
         <is>
-          <t>ee25477b30fad036b861ebc1f46f21922de217576a95200ed27b836a0d6421de</t>
+          <t>d3d445fe400ce174942b4dad8f2ff5b1d96d05e0a53580b851a8428439aea6e7</t>
         </is>
       </c>
       <c r="F11" s="42" t="inlineStr">
         <is>
-          <t>ee25477b30fad036b861ebc1f46f21922de217576a95200ed27b836a0d6421de</t>
+          <t>d3d445fe400ce174942b4dad8f2ff5b1d96d05e0a53580b851a8428439aea6e7</t>
         </is>
       </c>
       <c r="G11" s="39" t="n">
-        <v>51698</v>
+        <v>54531</v>
       </c>
     </row>
     <row r="12">

--- a/TES/Salariales/Nueva Escala 3210/Escala_Salarial_3210_Nueva.xlsx
+++ b/TES/Salariales/Nueva Escala 3210/Escala_Salarial_3210_Nueva.xlsx
@@ -7608,7 +7608,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-28T22:18:57+00:00</t>
+          <t>2026-10-28T22:40:37+00:00</t>
         </is>
       </c>
     </row>
@@ -7784,16 +7784,16 @@
       </c>
       <c r="E10" s="42" t="inlineStr">
         <is>
-          <t>259b3e28b7d715fe7fb2cd0eaea0f440fd0df3a48199cf306ba89c5902f42d9b</t>
+          <t>7ab5a4346d21ac5bb85389c006f81741a9afc03ea4f3058cf17ab24ea2f45a13</t>
         </is>
       </c>
       <c r="F10" s="42" t="inlineStr">
         <is>
-          <t>259b3e28b7d715fe7fb2cd0eaea0f440fd0df3a48199cf306ba89c5902f42d9b</t>
+          <t>7ab5a4346d21ac5bb85389c006f81741a9afc03ea4f3058cf17ab24ea2f45a13</t>
         </is>
       </c>
       <c r="G10" s="39" t="n">
-        <v>38904</v>
+        <v>43005</v>
       </c>
     </row>
     <row r="11">
@@ -7819,16 +7819,16 @@
       </c>
       <c r="E11" s="42" t="inlineStr">
         <is>
-          <t>d3d445fe400ce174942b4dad8f2ff5b1d96d05e0a53580b851a8428439aea6e7</t>
+          <t>b0a794ad3c4c6e5e6c204d808480d50725c2afd2b471808f32dde14d51940515</t>
         </is>
       </c>
       <c r="F11" s="42" t="inlineStr">
         <is>
-          <t>d3d445fe400ce174942b4dad8f2ff5b1d96d05e0a53580b851a8428439aea6e7</t>
+          <t>b0a794ad3c4c6e5e6c204d808480d50725c2afd2b471808f32dde14d51940515</t>
         </is>
       </c>
       <c r="G11" s="39" t="n">
-        <v>54531</v>
+        <v>56412</v>
       </c>
     </row>
     <row r="12">

--- a/TES/Salariales/Nueva Escala 3210/Escala_Salarial_3210_Nueva.xlsx
+++ b/TES/Salariales/Nueva Escala 3210/Escala_Salarial_3210_Nueva.xlsx
@@ -7608,7 +7608,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-28T22:40:37+00:00</t>
+          <t>2026-10-28T22:47:29+00:00</t>
         </is>
       </c>
     </row>
@@ -7819,16 +7819,16 @@
       </c>
       <c r="E11" s="42" t="inlineStr">
         <is>
-          <t>b0a794ad3c4c6e5e6c204d808480d50725c2afd2b471808f32dde14d51940515</t>
+          <t>247abb24916ab26d432365a991e389986e62dff1e658156c817145354cd84b03</t>
         </is>
       </c>
       <c r="F11" s="42" t="inlineStr">
         <is>
-          <t>b0a794ad3c4c6e5e6c204d808480d50725c2afd2b471808f32dde14d51940515</t>
+          <t>247abb24916ab26d432365a991e389986e62dff1e658156c817145354cd84b03</t>
         </is>
       </c>
       <c r="G11" s="39" t="n">
-        <v>56412</v>
+        <v>56637</v>
       </c>
     </row>
     <row r="12">

--- a/TES/Salariales/Nueva Escala 3210/Escala_Salarial_3210_Nueva.xlsx
+++ b/TES/Salariales/Nueva Escala 3210/Escala_Salarial_3210_Nueva.xlsx
@@ -15,9 +15,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Detalle Plantilla 87'!$A$1:$F$184</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Trazabilidad SHA-256'!$A$6:$G$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Trazabilidad SHA-256'!$A$6:$G$13</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Trazabilidad SHA-256'!$1:$6</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Trazabilidad SHA-256'!$A$1:$G$12</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Trazabilidad SHA-256'!$A$1:$G$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -398,8 +398,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ManifiestoSHA256" displayName="ManifiestoSHA256" ref="A6:G12" headerRowCount="1">
-  <autoFilter ref="A6:G12"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ManifiestoSHA256" displayName="ManifiestoSHA256" ref="A6:G13" headerRowCount="1">
+  <autoFilter ref="A6:G13"/>
   <tableColumns count="7">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fuente"/>
@@ -726,7 +726,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generado el 28/10/2026. La columna G se alimenta del archivo “propuesta de plantilla por la resolucion 87.xls”. Montos en pesos cubanos (CUP).</t>
+          <t>Generado el 29/10/2026. La columna G se alimenta del archivo “propuesta de plantilla por la resolucion 87.xls”. Montos en pesos cubanos (CUP).</t>
         </is>
       </c>
     </row>
@@ -1852,7 +1852,7 @@
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="19" t="inlineStr">
         <is>
-          <t>NOTAS: Grupo XII: valores encontrados -&gt; $5,770.00 (15 ocurrencias), $5,570.00 (1 ocurrencias). Se adopta $5,770.00 por ser el mayoritario. / Grupo XV: valores encontrados -&gt; $7,201.00 (5 ocurrencias), $7,777.00 (1 ocurrencias). Se adopta $7,201.00 por ser el mayoritario.</t>
+          <t>NOTAS: sin anomalías.</t>
         </is>
       </c>
     </row>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="F28" s="28" t="n">
-        <v>7777</v>
+        <v>7201</v>
       </c>
     </row>
     <row r="29">
@@ -5197,7 +5197,7 @@
         </is>
       </c>
       <c r="F98" s="28" t="n">
-        <v>5570</v>
+        <v>5770</v>
       </c>
     </row>
     <row r="99">
@@ -7448,7 +7448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -7516,25 +7516,11 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="34" t="inlineStr">
-        <is>
-          <t>• Grupo XII: valores encontrados -&gt; $5,770.00 (15 ocurrencias), $5,570.00 (1 ocurrencias). Se adopta $5,770.00 por ser el mayoritario.</t>
-        </is>
-      </c>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="34" t="inlineStr"/>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="34" t="inlineStr">
-        <is>
-          <t>• Grupo XV: valores encontrados -&gt; $7,201.00 (5 ocurrencias), $7,777.00 (1 ocurrencias). Se adopta $7,201.00 por ser el mayoritario.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="34" t="inlineStr"/>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="34" t="inlineStr">
         <is>
           <t>LENGUAJE DE PROGRAMACIÓN UTILIZADO: Python 3 — librerías xlrd (lectura del .xls heredado), openpyxl (Excel con fórmulas/estilos) y fpdf2 (PDF). Es la opción más adecuada porque lee formatos legacy, permite auditoría registro a registro, se re-ejecuta sin intervención manual y genera ambos formatos de salida con un único código mantenible.</t>
         </is>
@@ -7551,7 +7537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -7608,7 +7594,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-28T22:47:29+00:00</t>
+          <t>2026-10-29T00:52:01+00:00</t>
         </is>
       </c>
     </row>
@@ -7679,12 +7665,12 @@
       </c>
       <c r="E7" s="42" t="inlineStr">
         <is>
-          <t>02399d1abf33cb821829df57f146e9011488ed86a11e539c664a2114c7b8b6cc</t>
+          <t>5542e23b705462738e66a82ed1aec8d60727c6d1352438266e620878ab63e473</t>
         </is>
       </c>
       <c r="F7" s="42" t="inlineStr">
         <is>
-          <t>02399d1abf33cb821829df57f146e9011488ed86a11e539c664a2114c7b8b6cc</t>
+          <t>5542e23b705462738e66a82ed1aec8d60727c6d1352438266e620878ab63e473</t>
         </is>
       </c>
       <c r="G7" s="39" t="n">
@@ -7784,16 +7770,16 @@
       </c>
       <c r="E10" s="42" t="inlineStr">
         <is>
-          <t>7ab5a4346d21ac5bb85389c006f81741a9afc03ea4f3058cf17ab24ea2f45a13</t>
+          <t>11da9e812e996110373df74759d9eb17c49a7fce58fa00e5d7c4c24b1d05adbf</t>
         </is>
       </c>
       <c r="F10" s="42" t="inlineStr">
         <is>
-          <t>7ab5a4346d21ac5bb85389c006f81741a9afc03ea4f3058cf17ab24ea2f45a13</t>
+          <t>11da9e812e996110373df74759d9eb17c49a7fce58fa00e5d7c4c24b1d05adbf</t>
         </is>
       </c>
       <c r="G10" s="39" t="n">
-        <v>43005</v>
+        <v>43127</v>
       </c>
     </row>
     <row r="11">
@@ -7819,16 +7805,16 @@
       </c>
       <c r="E11" s="42" t="inlineStr">
         <is>
-          <t>247abb24916ab26d432365a991e389986e62dff1e658156c817145354cd84b03</t>
+          <t>749b33588504192a5ccf2d062bcb689e7498f75547c355918252216bcec97ef1</t>
         </is>
       </c>
       <c r="F11" s="42" t="inlineStr">
         <is>
-          <t>247abb24916ab26d432365a991e389986e62dff1e658156c817145354cd84b03</t>
+          <t>749b33588504192a5ccf2d062bcb689e7498f75547c355918252216bcec97ef1</t>
         </is>
       </c>
       <c r="G11" s="39" t="n">
-        <v>56637</v>
+        <v>75282</v>
       </c>
     </row>
     <row r="12">
@@ -7866,8 +7852,43 @@
         <v>865</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="39" t="inlineStr">
+        <is>
+          <t>verificador_paquete</t>
+        </is>
+      </c>
+      <c r="B13" s="40" t="inlineStr">
+        <is>
+          <t>Verificador offline de paquetes de exportación</t>
+        </is>
+      </c>
+      <c r="C13" s="40" t="inlineStr">
+        <is>
+          <t>tools/verificar_paquete_exportacion.py</t>
+        </is>
+      </c>
+      <c r="D13" s="41" t="inlineStr">
+        <is>
+          <t>VERIFICADA</t>
+        </is>
+      </c>
+      <c r="E13" s="42" t="inlineStr">
+        <is>
+          <t>0633c843d086b003c6ebaffafdd2c88abd2b463bcf912c80c0ba9a607ec5cbdb</t>
+        </is>
+      </c>
+      <c r="F13" s="42" t="inlineStr">
+        <is>
+          <t>0633c843d086b003c6ebaffafdd2c88abd2b463bcf912c80c0ba9a607ec5cbdb</t>
+        </is>
+      </c>
+      <c r="G13" s="39" t="n">
+        <v>8341</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A6:G12"/>
+  <autoFilter ref="A6:G13"/>
   <mergeCells count="2">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A5:G5"/>

--- a/TES/Salariales/Nueva Escala 3210/Escala_Salarial_3210_Nueva.xlsx
+++ b/TES/Salariales/Nueva Escala 3210/Escala_Salarial_3210_Nueva.xlsx
@@ -15,9 +15,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Detalle Plantilla 87'!$A$1:$F$184</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Trazabilidad SHA-256'!$A$6:$G$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Trazabilidad SHA-256'!$A$6:$G$14</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Trazabilidad SHA-256'!$1:$6</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Trazabilidad SHA-256'!$A$1:$G$13</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Trazabilidad SHA-256'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -25,10 +25,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
-    <numFmt numFmtId="166" formatCode="0.0000"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="&quot;$ &quot;#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
   <fonts count="15">
     <font>
@@ -197,7 +196,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -220,7 +219,7 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -235,19 +234,19 @@
     <xf numFmtId="164" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -262,25 +261,19 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -290,9 +283,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -398,8 +388,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ManifiestoSHA256" displayName="ManifiestoSHA256" ref="A6:G13" headerRowCount="1">
-  <autoFilter ref="A6:G13"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ManifiestoSHA256" displayName="ManifiestoSHA256" ref="A6:G14" headerRowCount="1">
+  <autoFilter ref="A6:G14"/>
   <tableColumns count="7">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Fuente"/>
@@ -719,7 +709,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NUEVA ESCALA SALARIAL — SALARIO MÍNIMO $3,210.00 (Res. 14/2026 y 15/2026, GOC-2026-O60)</t>
+          <t>NUEVA ESCALA SALARIAL — SALARIO MÍNIMO $ 3,210.00 (Res. 14/2026 y 15/2026, GOC-2026-O60)</t>
         </is>
       </c>
     </row>
@@ -1902,7 +1892,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Nueva escala (mínimo $3,210.00)</t>
+          <t>Nueva escala (mínimo $ 3,210.00)</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -1948,11 +1938,11 @@
       <c r="B4" s="21" t="n">
         <v>2200</v>
       </c>
-      <c r="C4" s="24">
+      <c r="C4" s="22">
         <f>D4*C3</f>
         <v/>
       </c>
-      <c r="D4" s="25">
+      <c r="D4" s="24">
         <f>B4/B3</f>
         <v/>
       </c>
@@ -1970,11 +1960,11 @@
       <c r="B5" s="21" t="n">
         <v>2300</v>
       </c>
-      <c r="C5" s="24">
+      <c r="C5" s="22">
         <f>D5*C4</f>
         <v/>
       </c>
-      <c r="D5" s="25">
+      <c r="D5" s="24">
         <f>B5/B4</f>
         <v/>
       </c>
@@ -1992,11 +1982,11 @@
       <c r="B6" s="21" t="n">
         <v>2420</v>
       </c>
-      <c r="C6" s="24">
+      <c r="C6" s="22">
         <f>D6*C5</f>
         <v/>
       </c>
-      <c r="D6" s="25">
+      <c r="D6" s="24">
         <f>B6/B5</f>
         <v/>
       </c>
@@ -2014,11 +2004,11 @@
       <c r="B7" s="21" t="n">
         <v>2540</v>
       </c>
-      <c r="C7" s="24">
+      <c r="C7" s="22">
         <f>D7*C6</f>
         <v/>
       </c>
-      <c r="D7" s="25">
+      <c r="D7" s="24">
         <f>B7/B6</f>
         <v/>
       </c>
@@ -2036,11 +2026,11 @@
       <c r="B8" s="21" t="n">
         <v>2660</v>
       </c>
-      <c r="C8" s="24">
+      <c r="C8" s="22">
         <f>D8*C7</f>
         <v/>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="24">
         <f>B8/B7</f>
         <v/>
       </c>
@@ -2058,11 +2048,11 @@
       <c r="B9" s="21" t="n">
         <v>2810</v>
       </c>
-      <c r="C9" s="24">
+      <c r="C9" s="22">
         <f>D9*C8</f>
         <v/>
       </c>
-      <c r="D9" s="25">
+      <c r="D9" s="24">
         <f>B9/B8</f>
         <v/>
       </c>
@@ -2080,11 +2070,11 @@
       <c r="B10" s="21" t="n">
         <v>2960</v>
       </c>
-      <c r="C10" s="24">
+      <c r="C10" s="22">
         <f>D10*C9</f>
         <v/>
       </c>
-      <c r="D10" s="25">
+      <c r="D10" s="24">
         <f>B10/B9</f>
         <v/>
       </c>
@@ -2102,11 +2092,11 @@
       <c r="B11" s="21" t="n">
         <v>3110</v>
       </c>
-      <c r="C11" s="24">
+      <c r="C11" s="22">
         <f>D11*C10</f>
         <v/>
       </c>
-      <c r="D11" s="25">
+      <c r="D11" s="24">
         <f>B11/B10</f>
         <v/>
       </c>
@@ -2124,11 +2114,11 @@
       <c r="B12" s="21" t="n">
         <v>3260</v>
       </c>
-      <c r="C12" s="24">
+      <c r="C12" s="22">
         <f>D12*C11</f>
         <v/>
       </c>
-      <c r="D12" s="25">
+      <c r="D12" s="24">
         <f>B12/B11</f>
         <v/>
       </c>
@@ -2146,11 +2136,11 @@
       <c r="B13" s="21" t="n">
         <v>3410</v>
       </c>
-      <c r="C13" s="24">
+      <c r="C13" s="22">
         <f>D13*C12</f>
         <v/>
       </c>
-      <c r="D13" s="25">
+      <c r="D13" s="24">
         <f>B13/B12</f>
         <v/>
       </c>
@@ -2168,11 +2158,11 @@
       <c r="B14" s="21" t="n">
         <v>3610</v>
       </c>
-      <c r="C14" s="24">
+      <c r="C14" s="22">
         <f>D14*C13</f>
         <v/>
       </c>
-      <c r="D14" s="25">
+      <c r="D14" s="24">
         <f>B14/B13</f>
         <v/>
       </c>
@@ -2190,11 +2180,11 @@
       <c r="B15" s="21" t="n">
         <v>3810</v>
       </c>
-      <c r="C15" s="24">
+      <c r="C15" s="22">
         <f>D15*C14</f>
         <v/>
       </c>
-      <c r="D15" s="25">
+      <c r="D15" s="24">
         <f>B15/B14</f>
         <v/>
       </c>
@@ -2212,11 +2202,11 @@
       <c r="B16" s="21" t="n">
         <v>4010</v>
       </c>
-      <c r="C16" s="24">
+      <c r="C16" s="22">
         <f>D16*C15</f>
         <v/>
       </c>
-      <c r="D16" s="25">
+      <c r="D16" s="24">
         <f>B16/B15</f>
         <v/>
       </c>
@@ -2234,11 +2224,11 @@
       <c r="B17" s="21" t="n">
         <v>4210</v>
       </c>
-      <c r="C17" s="24">
+      <c r="C17" s="22">
         <f>D17*C16</f>
         <v/>
       </c>
-      <c r="D17" s="25">
+      <c r="D17" s="24">
         <f>B17/B16</f>
         <v/>
       </c>
@@ -2256,11 +2246,11 @@
       <c r="B18" s="21" t="n">
         <v>4410</v>
       </c>
-      <c r="C18" s="24">
+      <c r="C18" s="22">
         <f>D18*C17</f>
         <v/>
       </c>
-      <c r="D18" s="25">
+      <c r="D18" s="24">
         <f>B18/B17</f>
         <v/>
       </c>
@@ -2278,11 +2268,11 @@
       <c r="B19" s="21" t="n">
         <v>4610</v>
       </c>
-      <c r="C19" s="24">
+      <c r="C19" s="22">
         <f>D19*C18</f>
         <v/>
       </c>
-      <c r="D19" s="25">
+      <c r="D19" s="24">
         <f>B19/B18</f>
         <v/>
       </c>
@@ -2300,11 +2290,11 @@
       <c r="B20" s="21" t="n">
         <v>4810</v>
       </c>
-      <c r="C20" s="24">
+      <c r="C20" s="22">
         <f>D20*C19</f>
         <v/>
       </c>
-      <c r="D20" s="25">
+      <c r="D20" s="24">
         <f>B20/B19</f>
         <v/>
       </c>
@@ -2322,11 +2312,11 @@
       <c r="B21" s="21" t="n">
         <v>5060</v>
       </c>
-      <c r="C21" s="24">
+      <c r="C21" s="22">
         <f>D21*C20</f>
         <v/>
       </c>
-      <c r="D21" s="25">
+      <c r="D21" s="24">
         <f>B21/B20</f>
         <v/>
       </c>
@@ -2344,11 +2334,11 @@
       <c r="B22" s="21" t="n">
         <v>5310</v>
       </c>
-      <c r="C22" s="24">
+      <c r="C22" s="22">
         <f>D22*C21</f>
         <v/>
       </c>
-      <c r="D22" s="25">
+      <c r="D22" s="24">
         <f>B22/B21</f>
         <v/>
       </c>
@@ -2366,11 +2356,11 @@
       <c r="B23" s="21" t="n">
         <v>5560</v>
       </c>
-      <c r="C23" s="24">
+      <c r="C23" s="22">
         <f>D23*C22</f>
         <v/>
       </c>
-      <c r="D23" s="25">
+      <c r="D23" s="24">
         <f>B23/B22</f>
         <v/>
       </c>
@@ -2388,11 +2378,11 @@
       <c r="B24" s="21" t="n">
         <v>5810</v>
       </c>
-      <c r="C24" s="24">
+      <c r="C24" s="22">
         <f>D24*C23</f>
         <v/>
       </c>
-      <c r="D24" s="25">
+      <c r="D24" s="24">
         <f>B24/B23</f>
         <v/>
       </c>
@@ -2410,11 +2400,11 @@
       <c r="B25" s="21" t="n">
         <v>6060</v>
       </c>
-      <c r="C25" s="24">
+      <c r="C25" s="22">
         <f>D25*C24</f>
         <v/>
       </c>
-      <c r="D25" s="25">
+      <c r="D25" s="24">
         <f>B25/B24</f>
         <v/>
       </c>
@@ -2432,11 +2422,11 @@
       <c r="B26" s="21" t="n">
         <v>6310</v>
       </c>
-      <c r="C26" s="24">
+      <c r="C26" s="22">
         <f>D26*C25</f>
         <v/>
       </c>
-      <c r="D26" s="25">
+      <c r="D26" s="24">
         <f>B26/B25</f>
         <v/>
       </c>
@@ -2454,11 +2444,11 @@
       <c r="B27" s="21" t="n">
         <v>6610</v>
       </c>
-      <c r="C27" s="24">
+      <c r="C27" s="22">
         <f>D27*C26</f>
         <v/>
       </c>
-      <c r="D27" s="25">
+      <c r="D27" s="24">
         <f>B27/B26</f>
         <v/>
       </c>
@@ -2476,11 +2466,11 @@
       <c r="B28" s="21" t="n">
         <v>6960</v>
       </c>
-      <c r="C28" s="24">
+      <c r="C28" s="22">
         <f>D28*C27</f>
         <v/>
       </c>
-      <c r="D28" s="25">
+      <c r="D28" s="24">
         <f>B28/B27</f>
         <v/>
       </c>
@@ -2498,11 +2488,11 @@
       <c r="B29" s="21" t="n">
         <v>7310</v>
       </c>
-      <c r="C29" s="24">
+      <c r="C29" s="22">
         <f>D29*C28</f>
         <v/>
       </c>
-      <c r="D29" s="25">
+      <c r="D29" s="24">
         <f>B29/B28</f>
         <v/>
       </c>
@@ -2520,11 +2510,11 @@
       <c r="B30" s="21" t="n">
         <v>7660</v>
       </c>
-      <c r="C30" s="24">
+      <c r="C30" s="22">
         <f>D30*C29</f>
         <v/>
       </c>
-      <c r="D30" s="25">
+      <c r="D30" s="24">
         <f>B30/B29</f>
         <v/>
       </c>
@@ -2542,11 +2532,11 @@
       <c r="B31" s="21" t="n">
         <v>8010</v>
       </c>
-      <c r="C31" s="24">
+      <c r="C31" s="22">
         <f>D31*C30</f>
         <v/>
       </c>
-      <c r="D31" s="25">
+      <c r="D31" s="24">
         <f>B31/B30</f>
         <v/>
       </c>
@@ -2564,11 +2554,11 @@
       <c r="B32" s="21" t="n">
         <v>8510</v>
       </c>
-      <c r="C32" s="24">
+      <c r="C32" s="22">
         <f>D32*C31</f>
         <v/>
       </c>
-      <c r="D32" s="25">
+      <c r="D32" s="24">
         <f>B32/B31</f>
         <v/>
       </c>
@@ -2586,11 +2576,11 @@
       <c r="B33" s="21" t="n">
         <v>9010</v>
       </c>
-      <c r="C33" s="24">
+      <c r="C33" s="22">
         <f>D33*C32</f>
         <v/>
       </c>
-      <c r="D33" s="25">
+      <c r="D33" s="24">
         <f>B33/B32</f>
         <v/>
       </c>
@@ -2608,11 +2598,11 @@
       <c r="B34" s="21" t="n">
         <v>9510</v>
       </c>
-      <c r="C34" s="24">
+      <c r="C34" s="22">
         <f>D34*C33</f>
         <v/>
       </c>
-      <c r="D34" s="25">
+      <c r="D34" s="24">
         <f>B34/B33</f>
         <v/>
       </c>
@@ -2682,7 +2672,7 @@
       <c r="A2" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="26" t="inlineStr">
+      <c r="B2" s="25" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
@@ -2690,17 +2680,17 @@
       <c r="C2" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="D2" s="26" t="inlineStr">
+      <c r="D2" s="25" t="inlineStr">
         <is>
           <t>Director</t>
         </is>
       </c>
-      <c r="E2" s="27" t="inlineStr">
+      <c r="E2" s="26" t="inlineStr">
         <is>
           <t>XVIII</t>
         </is>
       </c>
-      <c r="F2" s="28" t="n">
+      <c r="F2" s="6" t="n">
         <v>9072</v>
       </c>
     </row>
@@ -2708,25 +2698,25 @@
       <c r="A3" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="29" t="inlineStr">
+      <c r="B3" s="27" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
       </c>
-      <c r="C3" s="30" t="n">
+      <c r="C3" s="28" t="n">
         <v>21</v>
       </c>
-      <c r="D3" s="29" t="inlineStr">
+      <c r="D3" s="27" t="inlineStr">
         <is>
           <t>Director Adjunto</t>
         </is>
       </c>
-      <c r="E3" s="31" t="inlineStr">
+      <c r="E3" s="29" t="inlineStr">
         <is>
           <t>XVII</t>
         </is>
       </c>
-      <c r="F3" s="32" t="n">
+      <c r="F3" s="12" t="n">
         <v>8400</v>
       </c>
     </row>
@@ -2734,7 +2724,7 @@
       <c r="A4" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="26" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
@@ -2742,17 +2732,17 @@
       <c r="C4" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="D4" s="26" t="inlineStr">
+      <c r="D4" s="25" t="inlineStr">
         <is>
           <t>Especialista  en Cuadro</t>
         </is>
       </c>
-      <c r="E4" s="27" t="inlineStr">
+      <c r="E4" s="26" t="inlineStr">
         <is>
           <t>XIV</t>
         </is>
       </c>
-      <c r="F4" s="28" t="n">
+      <c r="F4" s="6" t="n">
         <v>6668</v>
       </c>
     </row>
@@ -2760,25 +2750,25 @@
       <c r="A5" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="29" t="inlineStr">
+      <c r="B5" s="27" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
       </c>
-      <c r="C5" s="30" t="n">
+      <c r="C5" s="28" t="n">
         <v>23</v>
       </c>
-      <c r="D5" s="29" t="inlineStr">
+      <c r="D5" s="27" t="inlineStr">
         <is>
           <t>Inspector  Sup. del Servicio Turistico</t>
         </is>
       </c>
-      <c r="E5" s="31" t="inlineStr">
+      <c r="E5" s="29" t="inlineStr">
         <is>
           <t>XIV</t>
         </is>
       </c>
-      <c r="F5" s="32" t="n">
+      <c r="F5" s="12" t="n">
         <v>6668</v>
       </c>
     </row>
@@ -2786,7 +2776,7 @@
       <c r="A6" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="26" t="inlineStr">
+      <c r="B6" s="25" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
@@ -2794,17 +2784,17 @@
       <c r="C6" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="D6" s="26" t="inlineStr">
+      <c r="D6" s="25" t="inlineStr">
         <is>
           <t>Chofer vehiculos ligeros</t>
         </is>
       </c>
-      <c r="E6" s="27" t="inlineStr">
+      <c r="E6" s="26" t="inlineStr">
         <is>
           <t>VIII</t>
         </is>
       </c>
-      <c r="F6" s="28" t="n">
+      <c r="F6" s="6" t="n">
         <v>4402</v>
       </c>
     </row>
@@ -2812,25 +2802,25 @@
       <c r="A7" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="29" t="inlineStr">
+      <c r="B7" s="27" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
       </c>
-      <c r="C7" s="30" t="n">
+      <c r="C7" s="28" t="n">
         <v>25</v>
       </c>
-      <c r="D7" s="29" t="inlineStr">
+      <c r="D7" s="27" t="inlineStr">
         <is>
           <t>Secretaria</t>
         </is>
       </c>
-      <c r="E7" s="31" t="inlineStr">
+      <c r="E7" s="29" t="inlineStr">
         <is>
           <t>XI</t>
         </is>
       </c>
-      <c r="F7" s="32" t="n">
+      <c r="F7" s="12" t="n">
         <v>5343</v>
       </c>
     </row>
@@ -2838,7 +2828,7 @@
       <c r="A8" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
@@ -2846,17 +2836,17 @@
       <c r="C8" s="7" t="n">
         <v>26</v>
       </c>
-      <c r="D8" s="26" t="inlineStr">
+      <c r="D8" s="25" t="inlineStr">
         <is>
           <t>Asesor Juridico</t>
         </is>
       </c>
-      <c r="E8" s="27" t="inlineStr">
+      <c r="E8" s="26" t="inlineStr">
         <is>
           <t>XIV</t>
         </is>
       </c>
-      <c r="F8" s="28" t="n">
+      <c r="F8" s="6" t="n">
         <v>6668</v>
       </c>
     </row>
@@ -2864,25 +2854,25 @@
       <c r="A9" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="29" t="inlineStr">
+      <c r="B9" s="27" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
       </c>
-      <c r="C9" s="30" t="n">
+      <c r="C9" s="28" t="n">
         <v>27</v>
       </c>
-      <c r="D9" s="29" t="inlineStr">
+      <c r="D9" s="27" t="inlineStr">
         <is>
           <t>Especialista en Informatica y comunic.</t>
         </is>
       </c>
-      <c r="E9" s="31" t="inlineStr">
+      <c r="E9" s="29" t="inlineStr">
         <is>
           <t>XIV</t>
         </is>
       </c>
-      <c r="F9" s="32" t="n">
+      <c r="F9" s="12" t="n">
         <v>6668</v>
       </c>
     </row>
@@ -2890,7 +2880,7 @@
       <c r="A10" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="26" t="inlineStr">
+      <c r="B10" s="25" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
@@ -2898,17 +2888,17 @@
       <c r="C10" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="D10" s="26" t="inlineStr">
+      <c r="D10" s="25" t="inlineStr">
         <is>
           <t>Auditor Adjunto</t>
         </is>
       </c>
-      <c r="E10" s="27" t="inlineStr">
+      <c r="E10" s="26" t="inlineStr">
         <is>
           <t>XIV</t>
         </is>
       </c>
-      <c r="F10" s="28" t="n">
+      <c r="F10" s="6" t="n">
         <v>6668</v>
       </c>
     </row>
@@ -2916,25 +2906,25 @@
       <c r="A11" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="29" t="inlineStr">
+      <c r="B11" s="27" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
       </c>
-      <c r="C11" s="30" t="n">
+      <c r="C11" s="28" t="n">
         <v>29</v>
       </c>
-      <c r="D11" s="29" t="inlineStr">
+      <c r="D11" s="27" t="inlineStr">
         <is>
           <t>Especialista Gestion Documental</t>
         </is>
       </c>
-      <c r="E11" s="31" t="inlineStr">
+      <c r="E11" s="29" t="inlineStr">
         <is>
           <t>XIV</t>
         </is>
       </c>
-      <c r="F11" s="32" t="n">
+      <c r="F11" s="12" t="n">
         <v>6668</v>
       </c>
     </row>
@@ -2942,7 +2932,7 @@
       <c r="A12" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="26" t="inlineStr">
+      <c r="B12" s="25" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
@@ -2950,17 +2940,17 @@
       <c r="C12" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="D12" s="26" t="inlineStr">
+      <c r="D12" s="25" t="inlineStr">
         <is>
           <t>Encargado de Actividades Generales</t>
         </is>
       </c>
-      <c r="E12" s="27" t="inlineStr">
+      <c r="E12" s="26" t="inlineStr">
         <is>
           <t>XI</t>
         </is>
       </c>
-      <c r="F12" s="28" t="n">
+      <c r="F12" s="6" t="n">
         <v>5343</v>
       </c>
     </row>
@@ -2968,25 +2958,25 @@
       <c r="A13" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="29" t="inlineStr">
+      <c r="B13" s="27" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
       </c>
-      <c r="C13" s="30" t="n">
+      <c r="C13" s="28" t="n">
         <v>31</v>
       </c>
-      <c r="D13" s="29" t="inlineStr">
+      <c r="D13" s="27" t="inlineStr">
         <is>
           <t>Encargado de Recepción y Pizarra Telefonica</t>
         </is>
       </c>
-      <c r="E13" s="31" t="inlineStr">
+      <c r="E13" s="29" t="inlineStr">
         <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="F13" s="32" t="n">
+      <c r="F13" s="12" t="n">
         <v>3918</v>
       </c>
     </row>
@@ -2994,7 +2984,7 @@
       <c r="A14" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="26" t="inlineStr">
+      <c r="B14" s="25" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
@@ -3002,17 +2992,17 @@
       <c r="C14" s="7" t="n">
         <v>32</v>
       </c>
-      <c r="D14" s="26" t="inlineStr">
+      <c r="D14" s="25" t="inlineStr">
         <is>
           <t>Auxiliar General de Servicios</t>
         </is>
       </c>
-      <c r="E14" s="27" t="inlineStr">
+      <c r="E14" s="26" t="inlineStr">
         <is>
           <t>VII</t>
         </is>
       </c>
-      <c r="F14" s="28" t="n">
+      <c r="F14" s="6" t="n">
         <v>4153</v>
       </c>
     </row>
@@ -3020,25 +3010,25 @@
       <c r="A15" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="29" t="inlineStr">
+      <c r="B15" s="27" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
       </c>
-      <c r="C15" s="30" t="n">
+      <c r="C15" s="28" t="n">
         <v>33</v>
       </c>
-      <c r="D15" s="29" t="inlineStr">
+      <c r="D15" s="27" t="inlineStr">
         <is>
           <t>Operario de mantenimientos y servicio tecnicos</t>
         </is>
       </c>
-      <c r="E15" s="31" t="inlineStr">
+      <c r="E15" s="29" t="inlineStr">
         <is>
           <t>VII</t>
         </is>
       </c>
-      <c r="F15" s="32" t="n">
+      <c r="F15" s="12" t="n">
         <v>4153</v>
       </c>
     </row>
@@ -3046,7 +3036,7 @@
       <c r="A16" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="26" t="inlineStr">
+      <c r="B16" s="25" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
@@ -3054,17 +3044,17 @@
       <c r="C16" s="7" t="n">
         <v>34</v>
       </c>
-      <c r="D16" s="26" t="inlineStr">
+      <c r="D16" s="25" t="inlineStr">
         <is>
           <t>Oficial Operativo Centro Direcc.</t>
         </is>
       </c>
-      <c r="E16" s="27" t="inlineStr">
+      <c r="E16" s="26" t="inlineStr">
         <is>
           <t>XI</t>
         </is>
       </c>
-      <c r="F16" s="28" t="n">
+      <c r="F16" s="6" t="n">
         <v>5343</v>
       </c>
     </row>
@@ -3072,25 +3062,25 @@
       <c r="A17" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="29" t="inlineStr">
+      <c r="B17" s="27" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
       </c>
-      <c r="C17" s="30" t="n">
+      <c r="C17" s="28" t="n">
         <v>36</v>
       </c>
-      <c r="D17" s="29" t="inlineStr">
+      <c r="D17" s="27" t="inlineStr">
         <is>
           <t>Jefe Dpto. Seg. Defensa y Proteccion</t>
         </is>
       </c>
-      <c r="E17" s="31" t="inlineStr">
+      <c r="E17" s="29" t="inlineStr">
         <is>
           <t>XV</t>
         </is>
       </c>
-      <c r="F17" s="32" t="n">
+      <c r="F17" s="12" t="n">
         <v>7201</v>
       </c>
     </row>
@@ -3098,7 +3088,7 @@
       <c r="A18" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="26" t="inlineStr">
+      <c r="B18" s="25" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
@@ -3106,17 +3096,17 @@
       <c r="C18" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="D18" s="26" t="inlineStr">
+      <c r="D18" s="25" t="inlineStr">
         <is>
           <t>Agentes de Seguridad y Protección</t>
         </is>
       </c>
-      <c r="E18" s="27" t="inlineStr">
+      <c r="E18" s="26" t="inlineStr">
         <is>
           <t>VIII</t>
         </is>
       </c>
-      <c r="F18" s="28" t="n">
+      <c r="F18" s="6" t="n">
         <v>4402</v>
       </c>
     </row>
@@ -3124,25 +3114,25 @@
       <c r="A19" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="29" t="inlineStr">
+      <c r="B19" s="27" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
       </c>
-      <c r="C19" s="30" t="n">
+      <c r="C19" s="28" t="n">
         <v>39</v>
       </c>
-      <c r="D19" s="29" t="inlineStr">
+      <c r="D19" s="27" t="inlineStr">
         <is>
           <t>Director Contable Financiero</t>
         </is>
       </c>
-      <c r="E19" s="31" t="inlineStr">
+      <c r="E19" s="29" t="inlineStr">
         <is>
           <t>XVI</t>
         </is>
       </c>
-      <c r="F19" s="32" t="n">
+      <c r="F19" s="12" t="n">
         <v>7777</v>
       </c>
     </row>
@@ -3150,7 +3140,7 @@
       <c r="A20" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="26" t="inlineStr">
+      <c r="B20" s="25" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
@@ -3158,17 +3148,17 @@
       <c r="C20" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="D20" s="26" t="inlineStr">
+      <c r="D20" s="25" t="inlineStr">
         <is>
           <t>Tecnico en Gestión Económica</t>
         </is>
       </c>
-      <c r="E20" s="27" t="inlineStr">
+      <c r="E20" s="26" t="inlineStr">
         <is>
           <t>XII</t>
         </is>
       </c>
-      <c r="F20" s="28" t="n">
+      <c r="F20" s="6" t="n">
         <v>5770</v>
       </c>
     </row>
@@ -3176,25 +3166,25 @@
       <c r="A21" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="29" t="inlineStr">
+      <c r="B21" s="27" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
       </c>
-      <c r="C21" s="30" t="n">
+      <c r="C21" s="28" t="n">
         <v>41</v>
       </c>
-      <c r="D21" s="29" t="inlineStr">
+      <c r="D21" s="27" t="inlineStr">
         <is>
           <t>Especialista en Gestion Económico</t>
         </is>
       </c>
-      <c r="E21" s="31" t="inlineStr">
+      <c r="E21" s="29" t="inlineStr">
         <is>
           <t>XIV</t>
         </is>
       </c>
-      <c r="F21" s="32" t="n">
+      <c r="F21" s="12" t="n">
         <v>6668</v>
       </c>
     </row>
@@ -3202,7 +3192,7 @@
       <c r="A22" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="26" t="inlineStr">
+      <c r="B22" s="25" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
@@ -3210,17 +3200,17 @@
       <c r="C22" s="7" t="n">
         <v>43</v>
       </c>
-      <c r="D22" s="26" t="inlineStr">
+      <c r="D22" s="25" t="inlineStr">
         <is>
           <t>Director de Capital Humano y Perfeccionamiento Empresarial</t>
         </is>
       </c>
-      <c r="E22" s="27" t="inlineStr">
+      <c r="E22" s="26" t="inlineStr">
         <is>
           <t>XVI</t>
         </is>
       </c>
-      <c r="F22" s="28" t="n">
+      <c r="F22" s="6" t="n">
         <v>7777</v>
       </c>
     </row>
@@ -3228,25 +3218,25 @@
       <c r="A23" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="29" t="inlineStr">
+      <c r="B23" s="27" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
       </c>
-      <c r="C23" s="30" t="n">
+      <c r="C23" s="28" t="n">
         <v>44</v>
       </c>
-      <c r="D23" s="29" t="inlineStr">
+      <c r="D23" s="27" t="inlineStr">
         <is>
           <t>Especialista en Gestion de Capital  Humanos</t>
         </is>
       </c>
-      <c r="E23" s="31" t="inlineStr">
+      <c r="E23" s="29" t="inlineStr">
         <is>
           <t>XIV</t>
         </is>
       </c>
-      <c r="F23" s="32" t="n">
+      <c r="F23" s="12" t="n">
         <v>6668</v>
       </c>
     </row>
@@ -3254,7 +3244,7 @@
       <c r="A24" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="26" t="inlineStr">
+      <c r="B24" s="25" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
@@ -3262,17 +3252,17 @@
       <c r="C24" s="7" t="n">
         <v>46</v>
       </c>
-      <c r="D24" s="26" t="inlineStr">
+      <c r="D24" s="25" t="inlineStr">
         <is>
           <t>Director de Operaciones y Calidad</t>
         </is>
       </c>
-      <c r="E24" s="27" t="inlineStr">
+      <c r="E24" s="26" t="inlineStr">
         <is>
           <t>XVI</t>
         </is>
       </c>
-      <c r="F24" s="28" t="n">
+      <c r="F24" s="6" t="n">
         <v>7777</v>
       </c>
     </row>
@@ -3280,25 +3270,25 @@
       <c r="A25" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="29" t="inlineStr">
+      <c r="B25" s="27" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
       </c>
-      <c r="C25" s="30" t="n">
+      <c r="C25" s="28" t="n">
         <v>47</v>
       </c>
-      <c r="D25" s="29" t="inlineStr">
+      <c r="D25" s="27" t="inlineStr">
         <is>
           <t>Especialista de Calidad</t>
         </is>
       </c>
-      <c r="E25" s="31" t="inlineStr">
+      <c r="E25" s="29" t="inlineStr">
         <is>
           <t>XIV</t>
         </is>
       </c>
-      <c r="F25" s="32" t="n">
+      <c r="F25" s="12" t="n">
         <v>6668</v>
       </c>
     </row>
@@ -3306,7 +3296,7 @@
       <c r="A26" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="26" t="inlineStr">
+      <c r="B26" s="25" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
@@ -3314,17 +3304,17 @@
       <c r="C26" s="7" t="n">
         <v>48</v>
       </c>
-      <c r="D26" s="26" t="inlineStr">
+      <c r="D26" s="25" t="inlineStr">
         <is>
           <t>Espècialista Recreación y Animacion</t>
         </is>
       </c>
-      <c r="E26" s="27" t="inlineStr">
+      <c r="E26" s="26" t="inlineStr">
         <is>
           <t>XIV</t>
         </is>
       </c>
-      <c r="F26" s="28" t="n">
+      <c r="F26" s="6" t="n">
         <v>6668</v>
       </c>
     </row>
@@ -3332,25 +3322,25 @@
       <c r="A27" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="29" t="inlineStr">
+      <c r="B27" s="27" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
       </c>
-      <c r="C27" s="30" t="n">
+      <c r="C27" s="28" t="n">
         <v>49</v>
       </c>
-      <c r="D27" s="29" t="inlineStr">
+      <c r="D27" s="27" t="inlineStr">
         <is>
           <t>Especialista en Alimentos y Bebidas</t>
         </is>
       </c>
-      <c r="E27" s="31" t="inlineStr">
+      <c r="E27" s="29" t="inlineStr">
         <is>
           <t>XIV</t>
         </is>
       </c>
-      <c r="F27" s="32" t="n">
+      <c r="F27" s="12" t="n">
         <v>6668</v>
       </c>
     </row>
@@ -3358,7 +3348,7 @@
       <c r="A28" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="26" t="inlineStr">
+      <c r="B28" s="25" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
@@ -3366,17 +3356,17 @@
       <c r="C28" s="7" t="n">
         <v>51</v>
       </c>
-      <c r="D28" s="26" t="inlineStr">
+      <c r="D28" s="25" t="inlineStr">
         <is>
           <t>Director Comercial</t>
         </is>
       </c>
-      <c r="E28" s="27" t="inlineStr">
+      <c r="E28" s="26" t="inlineStr">
         <is>
           <t>XV</t>
         </is>
       </c>
-      <c r="F28" s="28" t="n">
+      <c r="F28" s="6" t="n">
         <v>7201</v>
       </c>
     </row>
@@ -3384,25 +3374,25 @@
       <c r="A29" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="29" t="inlineStr">
+      <c r="B29" s="27" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
       </c>
-      <c r="C29" s="30" t="n">
+      <c r="C29" s="28" t="n">
         <v>52</v>
       </c>
-      <c r="D29" s="29" t="inlineStr">
+      <c r="D29" s="27" t="inlineStr">
         <is>
           <t>Especialista  en Comercialización del Producto Turístico</t>
         </is>
       </c>
-      <c r="E29" s="31" t="inlineStr">
+      <c r="E29" s="29" t="inlineStr">
         <is>
           <t>XIV</t>
         </is>
       </c>
-      <c r="F29" s="32" t="n">
+      <c r="F29" s="12" t="n">
         <v>6668</v>
       </c>
     </row>
@@ -3410,7 +3400,7 @@
       <c r="A30" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="26" t="inlineStr">
+      <c r="B30" s="25" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
@@ -3418,17 +3408,17 @@
       <c r="C30" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="D30" s="26" t="inlineStr">
+      <c r="D30" s="25" t="inlineStr">
         <is>
           <t>Promotor de Ventas e Información turistica</t>
         </is>
       </c>
-      <c r="E30" s="27" t="inlineStr">
+      <c r="E30" s="26" t="inlineStr">
         <is>
           <t>IX</t>
         </is>
       </c>
-      <c r="F30" s="28" t="n">
+      <c r="F30" s="6" t="n">
         <v>4666</v>
       </c>
     </row>
@@ -3436,25 +3426,25 @@
       <c r="A31" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="29" t="inlineStr">
+      <c r="B31" s="27" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
       </c>
-      <c r="C31" s="30" t="n">
+      <c r="C31" s="28" t="n">
         <v>55</v>
       </c>
-      <c r="D31" s="29" t="inlineStr">
+      <c r="D31" s="27" t="inlineStr">
         <is>
           <t>Director de Inversiones,Logistica y Servicios Tecnicos</t>
         </is>
       </c>
-      <c r="E31" s="31" t="inlineStr">
+      <c r="E31" s="29" t="inlineStr">
         <is>
           <t>XVI</t>
         </is>
       </c>
-      <c r="F31" s="32" t="n">
+      <c r="F31" s="12" t="n">
         <v>7777</v>
       </c>
     </row>
@@ -3462,7 +3452,7 @@
       <c r="A32" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="26" t="inlineStr">
+      <c r="B32" s="25" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
@@ -3470,17 +3460,17 @@
       <c r="C32" s="7" t="n">
         <v>56</v>
       </c>
-      <c r="D32" s="26" t="inlineStr">
+      <c r="D32" s="25" t="inlineStr">
         <is>
           <t>Tecnico  de Transporte Automotor</t>
         </is>
       </c>
-      <c r="E32" s="27" t="inlineStr">
+      <c r="E32" s="26" t="inlineStr">
         <is>
           <t>XII</t>
         </is>
       </c>
-      <c r="F32" s="28" t="n">
+      <c r="F32" s="6" t="n">
         <v>5770</v>
       </c>
     </row>
@@ -3488,25 +3478,25 @@
       <c r="A33" s="5" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="29" t="inlineStr">
+      <c r="B33" s="27" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
       </c>
-      <c r="C33" s="30" t="n">
+      <c r="C33" s="28" t="n">
         <v>57</v>
       </c>
-      <c r="D33" s="29" t="inlineStr">
+      <c r="D33" s="27" t="inlineStr">
         <is>
           <t>Especialista B en Ahorro y Uso Racional de la Energía</t>
         </is>
       </c>
-      <c r="E33" s="31" t="inlineStr">
+      <c r="E33" s="29" t="inlineStr">
         <is>
           <t>XIV</t>
         </is>
       </c>
-      <c r="F33" s="32" t="n">
+      <c r="F33" s="12" t="n">
         <v>6668</v>
       </c>
     </row>
@@ -3514,7 +3504,7 @@
       <c r="A34" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="26" t="inlineStr">
+      <c r="B34" s="25" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
@@ -3522,17 +3512,17 @@
       <c r="C34" s="7" t="n">
         <v>58</v>
       </c>
-      <c r="D34" s="26" t="inlineStr">
+      <c r="D34" s="25" t="inlineStr">
         <is>
           <t>Chofer  Vehiculos de Carga</t>
         </is>
       </c>
-      <c r="E34" s="27" t="inlineStr">
+      <c r="E34" s="26" t="inlineStr">
         <is>
           <t>IX</t>
         </is>
       </c>
-      <c r="F34" s="28" t="n">
+      <c r="F34" s="6" t="n">
         <v>4666</v>
       </c>
     </row>
@@ -3540,25 +3530,25 @@
       <c r="A35" s="5" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="29" t="inlineStr">
+      <c r="B35" s="27" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
       </c>
-      <c r="C35" s="30" t="n">
+      <c r="C35" s="28" t="n">
         <v>59</v>
       </c>
-      <c r="D35" s="29" t="inlineStr">
+      <c r="D35" s="27" t="inlineStr">
         <is>
           <t>Comprador</t>
         </is>
       </c>
-      <c r="E35" s="31" t="inlineStr">
+      <c r="E35" s="29" t="inlineStr">
         <is>
           <t>XI</t>
         </is>
       </c>
-      <c r="F35" s="32" t="n">
+      <c r="F35" s="12" t="n">
         <v>5343</v>
       </c>
     </row>
@@ -3566,7 +3556,7 @@
       <c r="A36" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="26" t="inlineStr">
+      <c r="B36" s="25" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
@@ -3574,17 +3564,17 @@
       <c r="C36" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="D36" s="26" t="inlineStr">
+      <c r="D36" s="25" t="inlineStr">
         <is>
           <t>Encargado de Almacén</t>
         </is>
       </c>
-      <c r="E36" s="27" t="inlineStr">
+      <c r="E36" s="26" t="inlineStr">
         <is>
           <t>VIII</t>
         </is>
       </c>
-      <c r="F36" s="28" t="n">
+      <c r="F36" s="6" t="n">
         <v>4402</v>
       </c>
     </row>
@@ -3592,25 +3582,25 @@
       <c r="A37" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="29" t="inlineStr">
+      <c r="B37" s="27" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
       </c>
-      <c r="C37" s="30" t="n">
+      <c r="C37" s="28" t="n">
         <v>61</v>
       </c>
-      <c r="D37" s="29" t="inlineStr">
+      <c r="D37" s="27" t="inlineStr">
         <is>
           <t>Dependiente de  Almacén</t>
         </is>
       </c>
-      <c r="E37" s="31" t="inlineStr">
+      <c r="E37" s="29" t="inlineStr">
         <is>
           <t>VII</t>
         </is>
       </c>
-      <c r="F37" s="32" t="n">
+      <c r="F37" s="12" t="n">
         <v>4153</v>
       </c>
     </row>
@@ -3618,7 +3608,7 @@
       <c r="A38" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="26" t="inlineStr">
+      <c r="B38" s="25" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
@@ -3626,17 +3616,17 @@
       <c r="C38" s="7" t="n">
         <v>63</v>
       </c>
-      <c r="D38" s="26" t="inlineStr">
+      <c r="D38" s="25" t="inlineStr">
         <is>
           <t>Espec. en Desarr. De programa Turist. Inversiones</t>
         </is>
       </c>
-      <c r="E38" s="27" t="inlineStr">
+      <c r="E38" s="26" t="inlineStr">
         <is>
           <t>XIV</t>
         </is>
       </c>
-      <c r="F38" s="28" t="n">
+      <c r="F38" s="6" t="n">
         <v>6668</v>
       </c>
     </row>
@@ -3644,25 +3634,25 @@
       <c r="A39" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="29" t="inlineStr">
+      <c r="B39" s="27" t="inlineStr">
         <is>
           <t>Plantilla Emp</t>
         </is>
       </c>
-      <c r="C39" s="30" t="n">
+      <c r="C39" s="28" t="n">
         <v>64</v>
       </c>
-      <c r="D39" s="29" t="inlineStr">
+      <c r="D39" s="27" t="inlineStr">
         <is>
           <t>Especialista en obras de Mantenimiento</t>
         </is>
       </c>
-      <c r="E39" s="31" t="inlineStr">
+      <c r="E39" s="29" t="inlineStr">
         <is>
           <t>XIV</t>
         </is>
       </c>
-      <c r="F39" s="32" t="n">
+      <c r="F39" s="12" t="n">
         <v>6668</v>
       </c>
     </row>
@@ -3670,7 +3660,7 @@
       <c r="A40" s="5" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="26" t="inlineStr">
+      <c r="B40" s="25" t="inlineStr">
         <is>
           <t>P-2 Dos Hermanas</t>
         </is>
@@ -3678,17 +3668,17 @@
       <c r="C40" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="D40" s="26" t="inlineStr">
+      <c r="D40" s="25" t="inlineStr">
         <is>
           <t>Director de las Instalaciones y/o los Complejos</t>
         </is>
       </c>
-      <c r="E40" s="27" t="inlineStr">
+      <c r="E40" s="26" t="inlineStr">
         <is>
           <t>XV</t>
         </is>
       </c>
-      <c r="F40" s="28" t="n">
+      <c r="F40" s="6" t="n">
         <v>7201</v>
       </c>
     </row>
@@ -3696,25 +3686,25 @@
       <c r="A41" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="29" t="inlineStr">
+      <c r="B41" s="27" t="inlineStr">
         <is>
           <t>P-2 Dos Hermanas</t>
         </is>
       </c>
-      <c r="C41" s="30" t="n">
+      <c r="C41" s="28" t="n">
         <v>24</v>
       </c>
-      <c r="D41" s="29" t="inlineStr">
+      <c r="D41" s="27" t="inlineStr">
         <is>
           <t>Subdirector Asis. de Serv y Calidad</t>
         </is>
       </c>
-      <c r="E41" s="31" t="inlineStr">
+      <c r="E41" s="29" t="inlineStr">
         <is>
           <t>XIV</t>
         </is>
       </c>
-      <c r="F41" s="32" t="n">
+      <c r="F41" s="12" t="n">
         <v>6668</v>
       </c>
     </row>
@@ -3722,7 +3712,7 @@
       <c r="A42" s="5" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="26" t="inlineStr">
+      <c r="B42" s="25" t="inlineStr">
         <is>
           <t>P-2 Dos Hermanas</t>
         </is>
@@ -3730,17 +3720,17 @@
       <c r="C42" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="D42" s="26" t="inlineStr">
+      <c r="D42" s="25" t="inlineStr">
         <is>
           <t>Subdirector Asistente de   Control  Interno.</t>
         </is>
       </c>
-      <c r="E42" s="27" t="inlineStr">
+      <c r="E42" s="26" t="inlineStr">
         <is>
           <t>XIV</t>
         </is>
       </c>
-      <c r="F42" s="28" t="n">
+      <c r="F42" s="6" t="n">
         <v>6668</v>
       </c>
     </row>
@@ -3748,25 +3738,25 @@
       <c r="A43" s="5" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="29" t="inlineStr">
+      <c r="B43" s="27" t="inlineStr">
         <is>
           <t>P-2 Dos Hermanas</t>
         </is>
       </c>
-      <c r="C43" s="30" t="n">
+      <c r="C43" s="28" t="n">
         <v>26</v>
       </c>
-      <c r="D43" s="29" t="inlineStr">
+      <c r="D43" s="27" t="inlineStr">
         <is>
           <t>Técnico  en Gestión Capital  Humanos</t>
         </is>
       </c>
-      <c r="E43" s="31" t="inlineStr">
+      <c r="E43" s="29" t="inlineStr">
         <is>
           <t>XI</t>
         </is>
       </c>
-      <c r="F43" s="32" t="n">
+      <c r="F43" s="12" t="n">
         <v>5343</v>
       </c>
     </row>
@@ -3774,7 +3764,7 @@
       <c r="A44" s="5" t="n">
         <v>43</v>
       </c>
-      <c r="B44" s="26" t="inlineStr">
+      <c r="B44" s="25" t="inlineStr">
         <is>
           <t>P-2 Dos Hermanas</t>
         </is>
@@ -3782,17 +3772,17 @@
       <c r="C44" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="D44" s="26" t="inlineStr">
+      <c r="D44" s="25" t="inlineStr">
         <is>
           <t>Especialista en Gestion Económico  (EP)</t>
         </is>
       </c>
-      <c r="E44" s="27" t="inlineStr">
+      <c r="E44" s="26" t="inlineStr">
         <is>
           <t>XIV</t>
         </is>
       </c>
-      <c r="F44" s="28" t="n">
+      <c r="F44" s="6" t="n">
         <v>6668</v>
       </c>
     </row>
@@ -3800,25 +3790,25 @@
       <c r="A45" s="5" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="29" t="inlineStr">
+      <c r="B45" s="27" t="inlineStr">
         <is>
           <t>P-2 Dos Hermanas</t>
         </is>
       </c>
-      <c r="C45" s="30" t="n">
+      <c r="C45" s="28" t="n">
         <v>29</v>
       </c>
-      <c r="D45" s="29" t="inlineStr">
+      <c r="D45" s="27" t="inlineStr">
         <is>
           <t>Técnico Gestión Económica</t>
         </is>
       </c>
-      <c r="E45" s="31" t="inlineStr">
+      <c r="E45" s="29" t="inlineStr">
         <is>
           <t>XI</t>
         </is>
       </c>
-      <c r="F45" s="32" t="n">
+      <c r="F45" s="12" t="n">
         <v>5343</v>
       </c>
     </row>
@@ -3826,7 +3816,7 @@
       <c r="A46" s="5" t="n">
         <v>45</v>
       </c>
-      <c r="B46" s="26" t="inlineStr">
+      <c r="B46" s="25" t="inlineStr">
         <is>
           <t>P-2 Dos Hermanas</t>
         </is>
@@ -3834,17 +3824,17 @@
       <c r="C46" s="7" t="n">
         <v>31</v>
       </c>
-      <c r="D46" s="26" t="inlineStr">
+      <c r="D46" s="25" t="inlineStr">
         <is>
           <t>Dependiente  Gastronomico</t>
         </is>
       </c>
-      <c r="E46" s="27" t="inlineStr">
+      <c r="E46" s="26" t="inlineStr">
         <is>
           <t>IX</t>
         </is>
       </c>
-      <c r="F46" s="28" t="n">
+      <c r="F46" s="6" t="n">
         <v>4666</v>
       </c>
     </row>
@@ -3852,25 +3842,25 @@
       <c r="A47" s="5" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="29" t="inlineStr">
+      <c r="B47" s="27" t="inlineStr">
         <is>
           <t>P-2 Dos Hermanas</t>
         </is>
       </c>
-      <c r="C47" s="30" t="n">
+      <c r="C47" s="28" t="n">
         <v>32</v>
       </c>
-      <c r="D47" s="29" t="inlineStr">
+      <c r="D47" s="27" t="inlineStr">
         <is>
           <t>Maestro de Cocina</t>
         </is>
       </c>
-      <c r="E47" s="31" t="inlineStr">
+      <c r="E47" s="29" t="inlineStr">
         <is>
           <t>XI</t>
         </is>
       </c>
-      <c r="F47" s="32" t="n">
+      <c r="F47" s="12" t="n">
         <v>5343</v>
       </c>
     </row>
@@ -3878,7 +3868,7 @@
       <c r="A48" s="5" t="n">
         <v>47</v>
       </c>
-      <c r="B48" s="26" t="inlineStr">
+      <c r="B48" s="25" t="inlineStr">
         <is>
           <t>P-2 Dos Hermanas</t>
         </is>
@@ -3886,17 +3876,17 @@
       <c r="C48" s="7" t="n">
         <v>33</v>
       </c>
-      <c r="D48" s="26" t="inlineStr">
+      <c r="D48" s="25" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E48" s="27" t="inlineStr">
+      <c r="E48" s="26" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="F48" s="28" t="n">
+      <c r="F48" s="6" t="n">
         <v>4993</v>
       </c>
     </row>
@@ -3904,25 +3894,25 @@
       <c r="A49" s="5" t="n">
         <v>48</v>
       </c>
-      <c r="B49" s="29" t="inlineStr">
+      <c r="B49" s="27" t="inlineStr">
         <is>
           <t>P-2 Dos Hermanas</t>
         </is>
       </c>
-      <c r="C49" s="30" t="n">
+      <c r="C49" s="28" t="n">
         <v>34</v>
       </c>
-      <c r="D49" s="29" t="inlineStr">
+      <c r="D49" s="27" t="inlineStr">
         <is>
           <t>Elaborador de Alimentos</t>
         </is>
       </c>
-      <c r="E49" s="31" t="inlineStr">
+      <c r="E49" s="29" t="inlineStr">
         <is>
           <t>IX</t>
         </is>
       </c>
-      <c r="F49" s="32" t="n">
+      <c r="F49" s="12" t="n">
         <v>4666</v>
       </c>
     </row>
@@ -3930,7 +3920,7 @@
       <c r="A50" s="5" t="n">
         <v>49</v>
       </c>
-      <c r="B50" s="26" t="inlineStr">
+      <c r="B50" s="25" t="inlineStr">
         <is>
           <t>P-2 Dos Hermanas</t>
         </is>
@@ -3938,17 +3928,17 @@
       <c r="C50" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="D50" s="26" t="inlineStr">
+      <c r="D50" s="25" t="inlineStr">
         <is>
           <t>Recepcionista Hotelero</t>
         </is>
       </c>
-      <c r="E50" s="27" t="inlineStr">
+      <c r="E50" s="26" t="inlineStr">
         <is>
           <t>IX</t>
         </is>
       </c>
-      <c r="F50" s="28" t="n">
+      <c r="F50" s="6" t="n">
         <v>4666</v>
       </c>
     </row>
@@ -3956,25 +3946,25 @@
       <c r="A51" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="B51" s="29" t="inlineStr">
+      <c r="B51" s="27" t="inlineStr">
         <is>
           <t>P-2 Dos Hermanas</t>
         </is>
       </c>
-      <c r="C51" s="30" t="n">
+      <c r="C51" s="28" t="n">
         <v>36</v>
       </c>
-      <c r="D51" s="29" t="inlineStr">
+      <c r="D51" s="27" t="inlineStr">
         <is>
           <t>Camarera de Habitaciones</t>
         </is>
       </c>
-      <c r="E51" s="31" t="inlineStr">
+      <c r="E51" s="29" t="inlineStr">
         <is>
           <t>IX</t>
         </is>
       </c>
-      <c r="F51" s="32" t="n">
+      <c r="F51" s="12" t="n">
         <v>4666</v>
       </c>
     </row>
@@ -3982,7 +3972,7 @@
       <c r="A52" s="5" t="n">
         <v>51</v>
       </c>
-      <c r="B52" s="26" t="inlineStr">
+      <c r="B52" s="25" t="inlineStr">
         <is>
           <t>P-2 Dos Hermanas</t>
         </is>
@@ -3990,17 +3980,17 @@
       <c r="C52" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="D52" s="26" t="inlineStr">
+      <c r="D52" s="25" t="inlineStr">
         <is>
           <t>Camarera de Habitaciones JB</t>
         </is>
       </c>
-      <c r="E52" s="27" t="inlineStr">
+      <c r="E52" s="26" t="inlineStr">
         <is>
           <t>XII</t>
         </is>
       </c>
-      <c r="F52" s="28" t="n">
+      <c r="F52" s="6" t="n">
         <v>5770</v>
       </c>
     </row>
@@ -4008,25 +3998,25 @@
       <c r="A53" s="5" t="n">
         <v>52</v>
       </c>
-      <c r="B53" s="29" t="inlineStr">
+      <c r="B53" s="27" t="inlineStr">
         <is>
           <t>P-2 Dos Hermanas</t>
         </is>
       </c>
-      <c r="C53" s="30" t="n">
+      <c r="C53" s="28" t="n">
         <v>38</v>
       </c>
-      <c r="D53" s="29" t="inlineStr">
+      <c r="D53" s="27" t="inlineStr">
         <is>
           <t>Técnico de Recreacion y Animación JB</t>
         </is>
       </c>
-      <c r="E53" s="31" t="inlineStr">
+      <c r="E53" s="29" t="inlineStr">
         <is>
           <t>XII</t>
         </is>
       </c>
-      <c r="F53" s="32" t="n">
+      <c r="F53" s="12" t="n">
         <v>5770</v>
       </c>
     </row>
@@ -4034,7 +4024,7 @@
       <c r="A54" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="B54" s="26" t="inlineStr">
+      <c r="B54" s="25" t="inlineStr">
         <is>
           <t>P-2 Dos Hermanas</t>
         </is>
@@ -4042,17 +4032,17 @@
       <c r="C54" s="7" t="n">
         <v>39</v>
       </c>
-      <c r="D54" s="26" t="inlineStr">
+      <c r="D54" s="25" t="inlineStr">
         <is>
           <t>Técnico de Recreacion y Animación</t>
         </is>
       </c>
-      <c r="E54" s="27" t="inlineStr">
+      <c r="E54" s="26" t="inlineStr">
         <is>
           <t>IX</t>
         </is>
       </c>
-      <c r="F54" s="28" t="n">
+      <c r="F54" s="6" t="n">
         <v>4666</v>
       </c>
     </row>
@@ -4060,25 +4050,25 @@
       <c r="A55" s="5" t="n">
         <v>54</v>
       </c>
-      <c r="B55" s="29" t="inlineStr">
+      <c r="B55" s="27" t="inlineStr">
         <is>
           <t>P-2 Dos Hermanas</t>
         </is>
       </c>
-      <c r="C55" s="30" t="n">
+      <c r="C55" s="28" t="n">
         <v>41</v>
       </c>
-      <c r="D55" s="29" t="inlineStr">
+      <c r="D55" s="27" t="inlineStr">
         <is>
           <t>Encargado de Almacén</t>
         </is>
       </c>
-      <c r="E55" s="31" t="inlineStr">
+      <c r="E55" s="29" t="inlineStr">
         <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="F55" s="32" t="n">
+      <c r="F55" s="12" t="n">
         <v>3918</v>
       </c>
     </row>
@@ -4086,7 +4076,7 @@
       <c r="A56" s="5" t="n">
         <v>55</v>
       </c>
-      <c r="B56" s="26" t="inlineStr">
+      <c r="B56" s="25" t="inlineStr">
         <is>
           <t>P-2 Dos Hermanas</t>
         </is>
@@ -4094,17 +4084,17 @@
       <c r="C56" s="7" t="n">
         <v>42</v>
       </c>
-      <c r="D56" s="26" t="inlineStr">
+      <c r="D56" s="25" t="inlineStr">
         <is>
           <t>Operario de MantenT. Y Serv. Tecnicos</t>
         </is>
       </c>
-      <c r="E56" s="27" t="inlineStr">
+      <c r="E56" s="26" t="inlineStr">
         <is>
           <t>VII</t>
         </is>
       </c>
-      <c r="F56" s="28" t="n">
+      <c r="F56" s="6" t="n">
         <v>4153</v>
       </c>
     </row>
@@ -4112,25 +4102,25 @@
       <c r="A57" s="5" t="n">
         <v>56</v>
       </c>
-      <c r="B57" s="29" t="inlineStr">
+      <c r="B57" s="27" t="inlineStr">
         <is>
           <t>P-2 Dos Hermanas</t>
         </is>
       </c>
-      <c r="C57" s="30" t="n">
+      <c r="C57" s="28" t="n">
         <v>43</v>
       </c>
-      <c r="D57" s="29" t="inlineStr">
+      <c r="D57" s="27" t="inlineStr">
         <is>
           <t>Operario de MantenT. Y Serv. Tecnico  JB</t>
         </is>
       </c>
-      <c r="E57" s="31" t="inlineStr">
+      <c r="E57" s="29" t="inlineStr">
         <is>
           <t>XII</t>
         </is>
       </c>
-      <c r="F57" s="32" t="n">
+      <c r="F57" s="12" t="n">
         <v>5770</v>
       </c>
     </row>
@@ -4138,7 +4128,7 @@
       <c r="A58" s="5" t="n">
         <v>57</v>
       </c>
-      <c r="B58" s="26" t="inlineStr">
+      <c r="B58" s="25" t="inlineStr">
         <is>
           <t>P-2 Dos Hermanas</t>
         </is>
@@ -4146,17 +4136,17 @@
       <c r="C58" s="7" t="n">
         <v>44</v>
       </c>
-      <c r="D58" s="26" t="inlineStr">
+      <c r="D58" s="25" t="inlineStr">
         <is>
           <t>Chofer vehiculos de carga</t>
         </is>
       </c>
-      <c r="E58" s="27" t="inlineStr">
+      <c r="E58" s="26" t="inlineStr">
         <is>
           <t>IX</t>
         </is>
       </c>
-      <c r="F58" s="28" t="n">
+      <c r="F58" s="6" t="n">
         <v>4666</v>
       </c>
     </row>
@@ -4164,25 +4154,25 @@
       <c r="A59" s="5" t="n">
         <v>58</v>
       </c>
-      <c r="B59" s="29" t="inlineStr">
+      <c r="B59" s="27" t="inlineStr">
         <is>
           <t>P-2 Dos Hermanas</t>
         </is>
       </c>
-      <c r="C59" s="30" t="n">
+      <c r="C59" s="28" t="n">
         <v>45</v>
       </c>
-      <c r="D59" s="29" t="inlineStr">
+      <c r="D59" s="27" t="inlineStr">
         <is>
           <t>Operario LABORES AGROPECUARIAS Y Jardineria</t>
         </is>
       </c>
-      <c r="E59" s="31" t="inlineStr">
+      <c r="E59" s="29" t="inlineStr">
         <is>
           <t>VIII</t>
         </is>
       </c>
-      <c r="F59" s="32" t="n">
+      <c r="F59" s="12" t="n">
         <v>4402</v>
       </c>
     </row>
@@ -4190,7 +4180,7 @@
       <c r="A60" s="5" t="n">
         <v>59</v>
       </c>
-      <c r="B60" s="26" t="inlineStr">
+      <c r="B60" s="25" t="inlineStr">
         <is>
           <t>P-2 Dos Hermanas</t>
         </is>
@@ -4198,17 +4188,17 @@
       <c r="C60" s="7" t="n">
         <v>47</v>
       </c>
-      <c r="D60" s="26" t="inlineStr">
+      <c r="D60" s="25" t="inlineStr">
         <is>
           <t>Jefes de Grupo de Seguridad Interna</t>
         </is>
       </c>
-      <c r="E60" s="27" t="inlineStr">
+      <c r="E60" s="26" t="inlineStr">
         <is>
           <t>XII</t>
         </is>
       </c>
-      <c r="F60" s="28" t="n">
+      <c r="F60" s="6" t="n">
         <v>5770</v>
       </c>
     </row>
@@ -4216,25 +4206,25 @@
       <c r="A61" s="5" t="n">
         <v>60</v>
       </c>
-      <c r="B61" s="29" t="inlineStr">
+      <c r="B61" s="27" t="inlineStr">
         <is>
           <t>P-2 Dos Hermanas</t>
         </is>
       </c>
-      <c r="C61" s="30" t="n">
+      <c r="C61" s="28" t="n">
         <v>48</v>
       </c>
-      <c r="D61" s="29" t="inlineStr">
+      <c r="D61" s="27" t="inlineStr">
         <is>
           <t>Agente Seguridad y Protección</t>
         </is>
       </c>
-      <c r="E61" s="31" t="inlineStr">
+      <c r="E61" s="29" t="inlineStr">
         <is>
           <t>VIII</t>
         </is>
       </c>
-      <c r="F61" s="32" t="n">
+      <c r="F61" s="12" t="n">
         <v>4402</v>
       </c>
     </row>
@@ -4242,7 +4232,7 @@
       <c r="A62" s="5" t="n">
         <v>61</v>
       </c>
-      <c r="B62" s="26" t="inlineStr">
+      <c r="B62" s="25" t="inlineStr">
         <is>
           <t>Laguna Grande</t>
         </is>
@@ -4250,17 +4240,17 @@
       <c r="C62" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="D62" s="26" t="inlineStr">
+      <c r="D62" s="25" t="inlineStr">
         <is>
           <t>Director de las Instalaciones y/o los Complejos</t>
         </is>
       </c>
-      <c r="E62" s="27" t="inlineStr">
+      <c r="E62" s="26" t="inlineStr">
         <is>
           <t>XV</t>
         </is>
       </c>
-      <c r="F62" s="28" t="n">
+      <c r="F62" s="6" t="n">
         <v>7201</v>
       </c>
     </row>
@@ -4268,25 +4258,25 @@
       <c r="A63" s="5" t="n">
         <v>62</v>
       </c>
-      <c r="B63" s="29" t="inlineStr">
+      <c r="B63" s="27" t="inlineStr">
         <is>
           <t>Laguna Grande</t>
         </is>
       </c>
-      <c r="C63" s="30" t="n">
+      <c r="C63" s="28" t="n">
         <v>25</v>
       </c>
-      <c r="D63" s="29" t="inlineStr">
+      <c r="D63" s="27" t="inlineStr">
         <is>
           <t>Sub Director Asistente</t>
         </is>
       </c>
-      <c r="E63" s="31" t="inlineStr">
+      <c r="E63" s="29" t="inlineStr">
         <is>
           <t>XIV</t>
         </is>
       </c>
-      <c r="F63" s="32" t="n">
+      <c r="F63" s="12" t="n">
         <v>6668</v>
       </c>
     </row>
@@ -4294,7 +4284,7 @@
       <c r="A64" s="5" t="n">
         <v>63</v>
       </c>
-      <c r="B64" s="26" t="inlineStr">
+      <c r="B64" s="25" t="inlineStr">
         <is>
           <t>Laguna Grande</t>
         </is>
@@ -4302,17 +4292,17 @@
       <c r="C64" s="7" t="n">
         <v>26</v>
       </c>
-      <c r="D64" s="26" t="inlineStr">
+      <c r="D64" s="25" t="inlineStr">
         <is>
           <t>Tecnico  en Gestión de Capital Humanos</t>
         </is>
       </c>
-      <c r="E64" s="27" t="inlineStr">
+      <c r="E64" s="26" t="inlineStr">
         <is>
           <t>XI</t>
         </is>
       </c>
-      <c r="F64" s="28" t="n">
+      <c r="F64" s="6" t="n">
         <v>5343</v>
       </c>
     </row>
@@ -4320,25 +4310,25 @@
       <c r="A65" s="5" t="n">
         <v>64</v>
       </c>
-      <c r="B65" s="29" t="inlineStr">
+      <c r="B65" s="27" t="inlineStr">
         <is>
           <t>Laguna Grande</t>
         </is>
       </c>
-      <c r="C65" s="30" t="n">
+      <c r="C65" s="28" t="n">
         <v>27</v>
       </c>
-      <c r="D65" s="29" t="inlineStr">
+      <c r="D65" s="27" t="inlineStr">
         <is>
           <t>Tecnico de Recreacion y Animacion</t>
         </is>
       </c>
-      <c r="E65" s="31" t="inlineStr">
+      <c r="E65" s="29" t="inlineStr">
         <is>
           <t>IX</t>
         </is>
       </c>
-      <c r="F65" s="32" t="n">
+      <c r="F65" s="12" t="n">
         <v>4666</v>
       </c>
     </row>
@@ -4346,7 +4336,7 @@
       <c r="A66" s="5" t="n">
         <v>65</v>
       </c>
-      <c r="B66" s="26" t="inlineStr">
+      <c r="B66" s="25" t="inlineStr">
         <is>
           <t>Laguna Grande</t>
         </is>
@@ -4354,17 +4344,17 @@
       <c r="C66" s="7" t="n">
         <v>29</v>
       </c>
-      <c r="D66" s="26" t="inlineStr">
+      <c r="D66" s="25" t="inlineStr">
         <is>
           <t>Especialista en Gestion   Económica</t>
         </is>
       </c>
-      <c r="E66" s="27" t="inlineStr">
+      <c r="E66" s="26" t="inlineStr">
         <is>
           <t>XIII</t>
         </is>
       </c>
-      <c r="F66" s="28" t="n">
+      <c r="F66" s="6" t="n">
         <v>6174</v>
       </c>
     </row>
@@ -4372,25 +4362,25 @@
       <c r="A67" s="5" t="n">
         <v>66</v>
       </c>
-      <c r="B67" s="29" t="inlineStr">
+      <c r="B67" s="27" t="inlineStr">
         <is>
           <t>Laguna Grande</t>
         </is>
       </c>
-      <c r="C67" s="30" t="n">
+      <c r="C67" s="28" t="n">
         <v>30</v>
       </c>
-      <c r="D67" s="29" t="inlineStr">
+      <c r="D67" s="27" t="inlineStr">
         <is>
           <t>Técnico  en Gestión Económica</t>
         </is>
       </c>
-      <c r="E67" s="31" t="inlineStr">
+      <c r="E67" s="29" t="inlineStr">
         <is>
           <t>XI</t>
         </is>
       </c>
-      <c r="F67" s="32" t="n">
+      <c r="F67" s="12" t="n">
         <v>5343</v>
       </c>
     </row>
@@ -4398,7 +4388,7 @@
       <c r="A68" s="5" t="n">
         <v>67</v>
       </c>
-      <c r="B68" s="26" t="inlineStr">
+      <c r="B68" s="25" t="inlineStr">
         <is>
           <t>Laguna Grande</t>
         </is>
@@ -4406,17 +4396,17 @@
       <c r="C68" s="7" t="n">
         <v>32</v>
       </c>
-      <c r="D68" s="26" t="inlineStr">
+      <c r="D68" s="25" t="inlineStr">
         <is>
           <t>Dependiente Gastronomico</t>
         </is>
       </c>
-      <c r="E68" s="27" t="inlineStr">
+      <c r="E68" s="26" t="inlineStr">
         <is>
           <t>IX</t>
         </is>
       </c>
-      <c r="F68" s="28" t="n">
+      <c r="F68" s="6" t="n">
         <v>4666</v>
       </c>
     </row>
@@ -4424,25 +4414,25 @@
       <c r="A69" s="5" t="n">
         <v>68</v>
       </c>
-      <c r="B69" s="29" t="inlineStr">
+      <c r="B69" s="27" t="inlineStr">
         <is>
           <t>Laguna Grande</t>
         </is>
       </c>
-      <c r="C69" s="30" t="n">
+      <c r="C69" s="28" t="n">
         <v>33</v>
       </c>
-      <c r="D69" s="29" t="inlineStr">
+      <c r="D69" s="27" t="inlineStr">
         <is>
           <t>Nivel Medio</t>
         </is>
       </c>
-      <c r="E69" s="31" t="inlineStr">
+      <c r="E69" s="29" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="F69" s="32" t="n">
+      <c r="F69" s="12" t="n">
         <v>4993</v>
       </c>
     </row>
@@ -4450,7 +4440,7 @@
       <c r="A70" s="5" t="n">
         <v>69</v>
       </c>
-      <c r="B70" s="26" t="inlineStr">
+      <c r="B70" s="25" t="inlineStr">
         <is>
           <t>Laguna Grande</t>
         </is>
@@ -4458,17 +4448,17 @@
       <c r="C70" s="7" t="n">
         <v>34</v>
       </c>
-      <c r="D70" s="26" t="inlineStr">
+      <c r="D70" s="25" t="inlineStr">
         <is>
           <t>Ayudante de Cocina</t>
         </is>
       </c>
-      <c r="E70" s="27" t="inlineStr">
+      <c r="E70" s="26" t="inlineStr">
         <is>
           <t>VIII</t>
         </is>
       </c>
-      <c r="F70" s="28" t="n">
+      <c r="F70" s="6" t="n">
         <v>4402</v>
       </c>
     </row>
@@ -4476,25 +4466,25 @@
       <c r="A71" s="5" t="n">
         <v>70</v>
       </c>
-      <c r="B71" s="29" t="inlineStr">
+      <c r="B71" s="27" t="inlineStr">
         <is>
           <t>Laguna Grande</t>
         </is>
       </c>
-      <c r="C71" s="30" t="n">
+      <c r="C71" s="28" t="n">
         <v>36</v>
       </c>
-      <c r="D71" s="29" t="inlineStr">
+      <c r="D71" s="27" t="inlineStr">
         <is>
           <t>Recepcionista Hotelero</t>
         </is>
       </c>
-      <c r="E71" s="31" t="inlineStr">
+      <c r="E71" s="29" t="inlineStr">
         <is>
           <t>IX</t>
         </is>
       </c>
-      <c r="F71" s="32" t="n">
+      <c r="F71" s="12" t="n">
         <v>4666</v>
       </c>
     </row>
@@ -4502,7 +4492,7 @@
       <c r="A72" s="5" t="n">
         <v>71</v>
       </c>
-      <c r="B72" s="26" t="inlineStr">
+      <c r="B72" s="25" t="inlineStr">
         <is>
           <t>Laguna Grande</t>
         </is>
@@ -4510,17 +4500,17 @@
       <c r="C72" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="D72" s="26" t="inlineStr">
+      <c r="D72" s="25" t="inlineStr">
         <is>
           <t>Camarera de Habitaciones</t>
         </is>
       </c>
-      <c r="E72" s="27" t="inlineStr">
+      <c r="E72" s="26" t="inlineStr">
         <is>
           <t>IX</t>
         </is>
       </c>
-      <c r="F72" s="28" t="n">
+      <c r="F72" s="6" t="n">
         <v>4666</v>
       </c>
     </row>
@@ -4528,25 +4518,25 @@
       <c r="A73" s="5" t="n">
         <v>72</v>
       </c>
-      <c r="B73" s="29" t="inlineStr">
+      <c r="B73" s="27" t="inlineStr">
         <is>
           <t>Laguna Grande</t>
         </is>
       </c>
-      <c r="C73" s="30" t="n">
+      <c r="C73" s="28" t="n">
         <v>38</v>
       </c>
-      <c r="D73" s="29" t="inlineStr">
+      <c r="D73" s="27" t="inlineStr">
         <is>
           <t>Nivel Medio Superior</t>
         </is>
       </c>
-      <c r="E73" s="31" t="inlineStr">
+      <c r="E73" s="29" t="inlineStr">
         <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="F73" s="32" t="n">
+      <c r="F73" s="12" t="n">
         <v>3918</v>
       </c>
     </row>
@@ -4554,7 +4544,7 @@
       <c r="A74" s="5" t="n">
         <v>73</v>
       </c>
-      <c r="B74" s="26" t="inlineStr">
+      <c r="B74" s="25" t="inlineStr">
         <is>
           <t>Laguna Grande</t>
         </is>
@@ -4562,17 +4552,17 @@
       <c r="C74" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="D74" s="26" t="inlineStr">
+      <c r="D74" s="25" t="inlineStr">
         <is>
           <t>Encargado de Almacèn</t>
         </is>
       </c>
-      <c r="E74" s="27" t="inlineStr">
+      <c r="E74" s="26" t="inlineStr">
         <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="F74" s="28" t="n">
+      <c r="F74" s="6" t="n">
         <v>3918</v>
       </c>
     </row>
@@ -4580,25 +4570,25 @@
       <c r="A75" s="5" t="n">
         <v>74</v>
       </c>
-      <c r="B75" s="29" t="inlineStr">
+      <c r="B75" s="27" t="inlineStr">
         <is>
           <t>Laguna Grande</t>
         </is>
       </c>
-      <c r="C75" s="30" t="n">
+      <c r="C75" s="28" t="n">
         <v>41</v>
       </c>
-      <c r="D75" s="29" t="inlineStr">
+      <c r="D75" s="27" t="inlineStr">
         <is>
           <t>Operario de Mantenimiento Y SERV. TECNICOS</t>
         </is>
       </c>
-      <c r="E75" s="31" t="inlineStr">
+      <c r="E75" s="29" t="inlineStr">
         <is>
           <t>VII</t>
         </is>
       </c>
-      <c r="F75" s="32" t="n">
+      <c r="F75" s="12" t="n">
         <v>4153</v>
       </c>
     </row>
@@ -4606,7 +4596,7 @@
       <c r="A76" s="5" t="n">
         <v>75</v>
       </c>
-      <c r="B76" s="26" t="inlineStr">
+      <c r="B76" s="25" t="inlineStr">
         <is>
           <t>Laguna Grande</t>
         </is>
@@ -4614,17 +4604,17 @@
       <c r="C76" s="7" t="n">
         <v>42</v>
       </c>
-      <c r="D76" s="26" t="inlineStr">
+      <c r="D76" s="25" t="inlineStr">
         <is>
           <t>Chofer Vehiculos carga</t>
         </is>
       </c>
-      <c r="E76" s="27" t="inlineStr">
+      <c r="E76" s="26" t="inlineStr">
         <is>
           <t>IX</t>
         </is>
       </c>
-      <c r="F76" s="28" t="n">
+      <c r="F76" s="6" t="n">
         <v>4666</v>
       </c>
     </row>
@@ -4632,25 +4622,25 @@
       <c r="A77" s="5" t="n">
         <v>76</v>
       </c>
-      <c r="B77" s="29" t="inlineStr">
+      <c r="B77" s="27" t="inlineStr">
         <is>
           <t>Laguna Grande</t>
         </is>
       </c>
-      <c r="C77" s="30" t="n">
+      <c r="C77" s="28" t="n">
         <v>44</v>
       </c>
-      <c r="D77" s="29" t="inlineStr">
+      <c r="D77" s="27" t="inlineStr">
         <is>
           <t>Jefe Grupo Seg. Interna</t>
         </is>
       </c>
-      <c r="E77" s="31" t="inlineStr">
+      <c r="E77" s="29" t="inlineStr">
         <is>
           <t>XII</t>
         </is>
       </c>
-      <c r="F77" s="32" t="n">
+      <c r="F77" s="12" t="n">
         <v>5770</v>
       </c>
     </row>
@@ -4658,7 +4648,7 @@
       <c r="A78" s="5" t="n">
         <v>77</v>
       </c>
-      <c r="B78" s="26" t="inlineStr">
+      <c r="B78" s="25" t="inlineStr">
         <is>
           <t>Laguna Grande</t>
         </is>
@@ -4666,17 +4656,17 @@
       <c r="C78" s="7" t="n">
         <v>45</v>
       </c>
-      <c r="D78" s="26" t="inlineStr">
+      <c r="D78" s="25" t="inlineStr">
         <is>
           <t>Agente de Seguridad y Protección</t>
         </is>
       </c>
-      <c r="E78" s="27" t="inlineStr">
+      <c r="E78" s="26" t="inlineStr">
         <is>
           <t>VIII</t>
         </is>
       </c>
-      <c r="F78" s="28" t="n">
+      <c r="F78" s="6" t="n">
         <v>4402</v>
       </c>
     </row>
@@ -4684,25 +4674,25 @@
       <c r="A79" s="5" t="n">
         <v>78</v>
       </c>
-      <c r="B79" s="29" t="inlineStr">
+      <c r="B79" s="27" t="inlineStr">
         <is>
           <t>P-2  Aguas Claras</t>
         </is>
       </c>
-      <c r="C79" s="30" t="n">
+      <c r="C79" s="28" t="n">
         <v>19</v>
       </c>
-      <c r="D79" s="29" t="inlineStr">
+      <c r="D79" s="27" t="inlineStr">
         <is>
           <t>Director de las Instalaciones y/o los Complejos</t>
         </is>
       </c>
-      <c r="E79" s="31" t="inlineStr">
+      <c r="E79" s="29" t="inlineStr">
         <is>
           <t>XV</t>
         </is>
       </c>
-      <c r="F79" s="32" t="n">
+      <c r="F79" s="12" t="n">
         <v>7201</v>
       </c>
     </row>
@@ -4710,7 +4700,7 @@
       <c r="A80" s="5" t="n">
         <v>79</v>
       </c>
-      <c r="B80" s="26" t="inlineStr">
+      <c r="B80" s="25" t="inlineStr">
         <is>
           <t>P-2  Aguas Claras</t>
         </is>
@@ -4718,17 +4708,17 @@
       <c r="C80" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="D80" s="26" t="inlineStr">
+      <c r="D80" s="25" t="inlineStr">
         <is>
           <t>Sub Director Asistente</t>
         </is>
       </c>
-      <c r="E80" s="27" t="inlineStr">
+      <c r="E80" s="26" t="inlineStr">
         <is>
           <t>XIV</t>
         </is>
       </c>
-      <c r="F80" s="28" t="n">
+      <c r="F80" s="6" t="n">
         <v>6668</v>
       </c>
     </row>
@@ -4736,25 +4726,25 @@
       <c r="A81" s="5" t="n">
         <v>80</v>
       </c>
-      <c r="B81" s="29" t="inlineStr">
+      <c r="B81" s="27" t="inlineStr">
         <is>
           <t>P-2  Aguas Claras</t>
         </is>
       </c>
-      <c r="C81" s="30" t="n">
+      <c r="C81" s="28" t="n">
         <v>21</v>
       </c>
-      <c r="D81" s="29" t="inlineStr">
+      <c r="D81" s="27" t="inlineStr">
         <is>
           <t>Especialista en Gestion de Capital Humanos</t>
         </is>
       </c>
-      <c r="E81" s="31" t="inlineStr">
+      <c r="E81" s="29" t="inlineStr">
         <is>
           <t>XIII</t>
         </is>
       </c>
-      <c r="F81" s="32" t="n">
+      <c r="F81" s="12" t="n">
         <v>6174</v>
       </c>
     </row>
@@ -4762,7 +4752,7 @@
       <c r="A82" s="5" t="n">
         <v>81</v>
       </c>
-      <c r="B82" s="26" t="inlineStr">
+      <c r="B82" s="25" t="inlineStr">
         <is>
           <t>P-2  Aguas Claras</t>
         </is>
@@ -4770,17 +4760,17 @@
       <c r="C82" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="D82" s="26" t="inlineStr">
+      <c r="D82" s="25" t="inlineStr">
         <is>
           <t>Especialista en Gestion Economica (EP)</t>
         </is>
       </c>
-      <c r="E82" s="27" t="inlineStr">
+      <c r="E82" s="26" t="inlineStr">
         <is>
           <t>XIV</t>
         </is>
       </c>
-      <c r="F82" s="28" t="n">
+      <c r="F82" s="6" t="n">
         <v>6668</v>
       </c>
     </row>
@@ -4788,25 +4778,25 @@
       <c r="A83" s="5" t="n">
         <v>82</v>
       </c>
-      <c r="B83" s="29" t="inlineStr">
+      <c r="B83" s="27" t="inlineStr">
         <is>
           <t>P-2  Aguas Claras</t>
         </is>
       </c>
-      <c r="C83" s="30" t="n">
+      <c r="C83" s="28" t="n">
         <v>24</v>
       </c>
-      <c r="D83" s="29" t="inlineStr">
+      <c r="D83" s="27" t="inlineStr">
         <is>
           <t>Tècnico  en Gestiòn Econòmica</t>
         </is>
       </c>
-      <c r="E83" s="31" t="inlineStr">
+      <c r="E83" s="29" t="inlineStr">
         <is>
           <t>XI</t>
         </is>
       </c>
-      <c r="F83" s="32" t="n">
+      <c r="F83" s="12" t="n">
         <v>5343</v>
       </c>
     </row>
@@ -4814,7 +4804,7 @@
       <c r="A84" s="5" t="n">
         <v>83</v>
       </c>
-      <c r="B84" s="26" t="inlineStr">
+      <c r="B84" s="25" t="inlineStr">
         <is>
           <t>P-2  Aguas Claras</t>
         </is>
@@ -4822,17 +4812,17 @@
       <c r="C84" s="7" t="n">
         <v>26</v>
       </c>
-      <c r="D84" s="26" t="inlineStr">
+      <c r="D84" s="25" t="inlineStr">
         <is>
           <t>Capitàn de SALÓN</t>
         </is>
       </c>
-      <c r="E84" s="27" t="inlineStr">
+      <c r="E84" s="26" t="inlineStr">
         <is>
           <t>XI</t>
         </is>
       </c>
-      <c r="F84" s="28" t="n">
+      <c r="F84" s="6" t="n">
         <v>5343</v>
       </c>
     </row>
@@ -4840,25 +4830,25 @@
       <c r="A85" s="5" t="n">
         <v>84</v>
       </c>
-      <c r="B85" s="29" t="inlineStr">
+      <c r="B85" s="27" t="inlineStr">
         <is>
           <t>P-2  Aguas Claras</t>
         </is>
       </c>
-      <c r="C85" s="30" t="n">
+      <c r="C85" s="28" t="n">
         <v>27</v>
       </c>
-      <c r="D85" s="29" t="inlineStr">
+      <c r="D85" s="27" t="inlineStr">
         <is>
           <t>Dependiente  GastronomicoJB</t>
         </is>
       </c>
-      <c r="E85" s="31" t="inlineStr">
+      <c r="E85" s="29" t="inlineStr">
         <is>
           <t>XII</t>
         </is>
       </c>
-      <c r="F85" s="32" t="n">
+      <c r="F85" s="12" t="n">
         <v>5770</v>
       </c>
     </row>
@@ -4866,7 +4856,7 @@
       <c r="A86" s="5" t="n">
         <v>85</v>
       </c>
-      <c r="B86" s="26" t="inlineStr">
+      <c r="B86" s="25" t="inlineStr">
         <is>
           <t>P-2  Aguas Claras</t>
         </is>
@@ -4874,17 +4864,17 @@
       <c r="C86" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="D86" s="26" t="inlineStr">
+      <c r="D86" s="25" t="inlineStr">
         <is>
           <t>Dependiente  Gastronomico</t>
         </is>
       </c>
-      <c r="E86" s="27" t="inlineStr">
+      <c r="E86" s="26" t="inlineStr">
         <is>
           <t>IX</t>
         </is>
       </c>
-      <c r="F86" s="28" t="n">
+      <c r="F86" s="6" t="n">
         <v>4666</v>
       </c>
     </row>
@@ -4892,25 +4882,25 @@
       <c r="A87" s="5" t="n">
         <v>86</v>
       </c>
-      <c r="B87" s="29" t="inlineStr">
+      <c r="B87" s="27" t="inlineStr">
         <is>
           <t>P-2  Aguas Claras</t>
         </is>
       </c>
-      <c r="C87" s="30" t="n">
+      <c r="C87" s="28" t="n">
         <v>29</v>
       </c>
-      <c r="D87" s="29" t="inlineStr">
+      <c r="D87" s="27" t="inlineStr">
         <is>
           <t>Panadero Dulcero</t>
         </is>
       </c>
-      <c r="E87" s="31" t="inlineStr">
+      <c r="E87" s="29" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="F87" s="32" t="n">
+      <c r="F87" s="12" t="n">
         <v>4993</v>
       </c>
     </row>
@@ -4918,7 +4908,7 @@
       <c r="A88" s="5" t="n">
         <v>87</v>
       </c>
-      <c r="B88" s="26" t="inlineStr">
+      <c r="B88" s="25" t="inlineStr">
         <is>
           <t>P-2  Aguas Claras</t>
         </is>
@@ -4926,17 +4916,17 @@
       <c r="C88" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="D88" s="26" t="inlineStr">
+      <c r="D88" s="25" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E88" s="27" t="inlineStr">
+      <c r="E88" s="26" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="F88" s="28" t="n">
+      <c r="F88" s="6" t="n">
         <v>4993</v>
       </c>
     </row>
@@ -4944,25 +4934,25 @@
       <c r="A89" s="5" t="n">
         <v>88</v>
       </c>
-      <c r="B89" s="29" t="inlineStr">
+      <c r="B89" s="27" t="inlineStr">
         <is>
           <t>P-2  Aguas Claras</t>
         </is>
       </c>
-      <c r="C89" s="30" t="n">
+      <c r="C89" s="28" t="n">
         <v>31</v>
       </c>
-      <c r="D89" s="29" t="inlineStr">
+      <c r="D89" s="27" t="inlineStr">
         <is>
           <t>Ayudante  de Cocina</t>
         </is>
       </c>
-      <c r="E89" s="31" t="inlineStr">
+      <c r="E89" s="29" t="inlineStr">
         <is>
           <t>VIII</t>
         </is>
       </c>
-      <c r="F89" s="32" t="n">
+      <c r="F89" s="12" t="n">
         <v>4402</v>
       </c>
     </row>
@@ -4970,7 +4960,7 @@
       <c r="A90" s="5" t="n">
         <v>89</v>
       </c>
-      <c r="B90" s="26" t="inlineStr">
+      <c r="B90" s="25" t="inlineStr">
         <is>
           <t>P-2  Aguas Claras</t>
         </is>
@@ -4978,17 +4968,17 @@
       <c r="C90" s="7" t="n">
         <v>33</v>
       </c>
-      <c r="D90" s="26" t="inlineStr">
+      <c r="D90" s="25" t="inlineStr">
         <is>
           <t>Recepcionista Hotelero JB</t>
         </is>
       </c>
-      <c r="E90" s="27" t="inlineStr">
+      <c r="E90" s="26" t="inlineStr">
         <is>
           <t>XII</t>
         </is>
       </c>
-      <c r="F90" s="28" t="n">
+      <c r="F90" s="6" t="n">
         <v>5770</v>
       </c>
     </row>
@@ -4996,25 +4986,25 @@
       <c r="A91" s="5" t="n">
         <v>90</v>
       </c>
-      <c r="B91" s="29" t="inlineStr">
+      <c r="B91" s="27" t="inlineStr">
         <is>
           <t>P-2  Aguas Claras</t>
         </is>
       </c>
-      <c r="C91" s="30" t="n">
+      <c r="C91" s="28" t="n">
         <v>34</v>
       </c>
-      <c r="D91" s="29" t="inlineStr">
+      <c r="D91" s="27" t="inlineStr">
         <is>
           <t>Recepcionista Hotelero</t>
         </is>
       </c>
-      <c r="E91" s="31" t="inlineStr">
+      <c r="E91" s="29" t="inlineStr">
         <is>
           <t>IX</t>
         </is>
       </c>
-      <c r="F91" s="32" t="n">
+      <c r="F91" s="12" t="n">
         <v>4666</v>
       </c>
     </row>
@@ -5022,7 +5012,7 @@
       <c r="A92" s="5" t="n">
         <v>91</v>
       </c>
-      <c r="B92" s="26" t="inlineStr">
+      <c r="B92" s="25" t="inlineStr">
         <is>
           <t>P-2  Aguas Claras</t>
         </is>
@@ -5030,17 +5020,17 @@
       <c r="C92" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="D92" s="26" t="inlineStr">
+      <c r="D92" s="25" t="inlineStr">
         <is>
           <t>Camarera de Habitaciones JB</t>
         </is>
       </c>
-      <c r="E92" s="27" t="inlineStr">
+      <c r="E92" s="26" t="inlineStr">
         <is>
           <t>XII</t>
         </is>
       </c>
-      <c r="F92" s="28" t="n">
+      <c r="F92" s="6" t="n">
         <v>5770</v>
       </c>
     </row>
@@ -5048,25 +5038,25 @@
       <c r="A93" s="5" t="n">
         <v>92</v>
       </c>
-      <c r="B93" s="29" t="inlineStr">
+      <c r="B93" s="27" t="inlineStr">
         <is>
           <t>P-2  Aguas Claras</t>
         </is>
       </c>
-      <c r="C93" s="30" t="n">
+      <c r="C93" s="28" t="n">
         <v>36</v>
       </c>
-      <c r="D93" s="29" t="inlineStr">
+      <c r="D93" s="27" t="inlineStr">
         <is>
           <t>Camarera de Habitaciones</t>
         </is>
       </c>
-      <c r="E93" s="31" t="inlineStr">
+      <c r="E93" s="29" t="inlineStr">
         <is>
           <t>IX</t>
         </is>
       </c>
-      <c r="F93" s="32" t="n">
+      <c r="F93" s="12" t="n">
         <v>4666</v>
       </c>
     </row>
@@ -5074,7 +5064,7 @@
       <c r="A94" s="5" t="n">
         <v>93</v>
       </c>
-      <c r="B94" s="26" t="inlineStr">
+      <c r="B94" s="25" t="inlineStr">
         <is>
           <t>P-2  Aguas Claras</t>
         </is>
@@ -5082,17 +5072,17 @@
       <c r="C94" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="D94" s="26" t="inlineStr">
+      <c r="D94" s="25" t="inlineStr">
         <is>
           <t>Limpiadora de Areas Publicas para Centros Turisticos</t>
         </is>
       </c>
-      <c r="E94" s="27" t="inlineStr">
+      <c r="E94" s="26" t="inlineStr">
         <is>
           <t>VII</t>
         </is>
       </c>
-      <c r="F94" s="28" t="n">
+      <c r="F94" s="6" t="n">
         <v>4153</v>
       </c>
     </row>
@@ -5100,25 +5090,25 @@
       <c r="A95" s="5" t="n">
         <v>94</v>
       </c>
-      <c r="B95" s="29" t="inlineStr">
+      <c r="B95" s="27" t="inlineStr">
         <is>
           <t>P-2  Aguas Claras</t>
         </is>
       </c>
-      <c r="C95" s="30" t="n">
+      <c r="C95" s="28" t="n">
         <v>39</v>
       </c>
-      <c r="D95" s="29" t="inlineStr">
+      <c r="D95" s="27" t="inlineStr">
         <is>
           <t>Tècnico en  Recreación y Animación</t>
         </is>
       </c>
-      <c r="E95" s="31" t="inlineStr">
+      <c r="E95" s="29" t="inlineStr">
         <is>
           <t>IX</t>
         </is>
       </c>
-      <c r="F95" s="32" t="n">
+      <c r="F95" s="12" t="n">
         <v>4666</v>
       </c>
     </row>
@@ -5126,7 +5116,7 @@
       <c r="A96" s="5" t="n">
         <v>95</v>
       </c>
-      <c r="B96" s="26" t="inlineStr">
+      <c r="B96" s="25" t="inlineStr">
         <is>
           <t>P-2  Aguas Claras</t>
         </is>
@@ -5134,17 +5124,17 @@
       <c r="C96" s="7" t="n">
         <v>41</v>
       </c>
-      <c r="D96" s="26" t="inlineStr">
+      <c r="D96" s="25" t="inlineStr">
         <is>
           <t>Operario de Mant. Y serv. Tecn.</t>
         </is>
       </c>
-      <c r="E96" s="27" t="inlineStr">
+      <c r="E96" s="26" t="inlineStr">
         <is>
           <t>VII</t>
         </is>
       </c>
-      <c r="F96" s="28" t="n">
+      <c r="F96" s="6" t="n">
         <v>4153</v>
       </c>
     </row>
@@ -5152,25 +5142,25 @@
       <c r="A97" s="5" t="n">
         <v>96</v>
       </c>
-      <c r="B97" s="29" t="inlineStr">
+      <c r="B97" s="27" t="inlineStr">
         <is>
           <t>P-2  Aguas Claras</t>
         </is>
       </c>
-      <c r="C97" s="30" t="n">
+      <c r="C97" s="28" t="n">
         <v>42</v>
       </c>
-      <c r="D97" s="29" t="inlineStr">
+      <c r="D97" s="27" t="inlineStr">
         <is>
           <t>Encargado de Almacèn</t>
         </is>
       </c>
-      <c r="E97" s="31" t="inlineStr">
+      <c r="E97" s="29" t="inlineStr">
         <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="F97" s="32" t="n">
+      <c r="F97" s="12" t="n">
         <v>3918</v>
       </c>
     </row>
@@ -5178,7 +5168,7 @@
       <c r="A98" s="5" t="n">
         <v>97</v>
       </c>
-      <c r="B98" s="26" t="inlineStr">
+      <c r="B98" s="25" t="inlineStr">
         <is>
           <t>P-2  Aguas Claras</t>
         </is>
@@ -5186,17 +5176,17 @@
       <c r="C98" s="7" t="n">
         <v>44</v>
       </c>
-      <c r="D98" s="26" t="inlineStr">
+      <c r="D98" s="25" t="inlineStr">
         <is>
           <t>Jefes de Grupo de Seguridad Interna</t>
         </is>
       </c>
-      <c r="E98" s="27" t="inlineStr">
+      <c r="E98" s="26" t="inlineStr">
         <is>
           <t>XII</t>
         </is>
       </c>
-      <c r="F98" s="28" t="n">
+      <c r="F98" s="6" t="n">
         <v>5770</v>
       </c>
     </row>
@@ -5204,25 +5194,25 @@
       <c r="A99" s="5" t="n">
         <v>98</v>
       </c>
-      <c r="B99" s="29" t="inlineStr">
+      <c r="B99" s="27" t="inlineStr">
         <is>
           <t>P-2  Aguas Claras</t>
         </is>
       </c>
-      <c r="C99" s="30" t="n">
+      <c r="C99" s="28" t="n">
         <v>45</v>
       </c>
-      <c r="D99" s="29" t="inlineStr">
+      <c r="D99" s="27" t="inlineStr">
         <is>
           <t>Agente de Seguridad y Protecciòn</t>
         </is>
       </c>
-      <c r="E99" s="31" t="inlineStr">
+      <c r="E99" s="29" t="inlineStr">
         <is>
           <t>VIII</t>
         </is>
       </c>
-      <c r="F99" s="32" t="n">
+      <c r="F99" s="12" t="n">
         <v>4402</v>
       </c>
     </row>
@@ -5230,7 +5220,7 @@
       <c r="A100" s="5" t="n">
         <v>99</v>
       </c>
-      <c r="B100" s="26" t="inlineStr">
+      <c r="B100" s="25" t="inlineStr">
         <is>
           <t>P-2 CUEVA LOS PORTALES</t>
         </is>
@@ -5238,17 +5228,17 @@
       <c r="C100" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="D100" s="26" t="inlineStr">
+      <c r="D100" s="25" t="inlineStr">
         <is>
           <t>Director de las Instalaciones y/o los Complejos</t>
         </is>
       </c>
-      <c r="E100" s="27" t="inlineStr">
+      <c r="E100" s="26" t="inlineStr">
         <is>
           <t>XV</t>
         </is>
       </c>
-      <c r="F100" s="28" t="n">
+      <c r="F100" s="6" t="n">
         <v>7201</v>
       </c>
     </row>
@@ -5256,25 +5246,25 @@
       <c r="A101" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="B101" s="29" t="inlineStr">
+      <c r="B101" s="27" t="inlineStr">
         <is>
           <t>P-2 CUEVA LOS PORTALES</t>
         </is>
       </c>
-      <c r="C101" s="30" t="n">
+      <c r="C101" s="28" t="n">
         <v>26</v>
       </c>
-      <c r="D101" s="29" t="inlineStr">
+      <c r="D101" s="27" t="inlineStr">
         <is>
           <t>Sub Dtor Asistente Servicios y Calidad</t>
         </is>
       </c>
-      <c r="E101" s="31" t="inlineStr">
+      <c r="E101" s="29" t="inlineStr">
         <is>
           <t>XIV</t>
         </is>
       </c>
-      <c r="F101" s="32" t="n">
+      <c r="F101" s="12" t="n">
         <v>6668</v>
       </c>
     </row>
@@ -5282,7 +5272,7 @@
       <c r="A102" s="5" t="n">
         <v>101</v>
       </c>
-      <c r="B102" s="26" t="inlineStr">
+      <c r="B102" s="25" t="inlineStr">
         <is>
           <t>P-2 CUEVA LOS PORTALES</t>
         </is>
@@ -5290,17 +5280,17 @@
       <c r="C102" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="D102" s="26" t="inlineStr">
+      <c r="D102" s="25" t="inlineStr">
         <is>
           <t>Chofer vehiculos ligeros</t>
         </is>
       </c>
-      <c r="E102" s="27" t="inlineStr">
+      <c r="E102" s="26" t="inlineStr">
         <is>
           <t>VIII</t>
         </is>
       </c>
-      <c r="F102" s="28" t="n">
+      <c r="F102" s="6" t="n">
         <v>4402</v>
       </c>
     </row>
@@ -5308,25 +5298,25 @@
       <c r="A103" s="5" t="n">
         <v>102</v>
       </c>
-      <c r="B103" s="29" t="inlineStr">
+      <c r="B103" s="27" t="inlineStr">
         <is>
           <t>P-2 CUEVA LOS PORTALES</t>
         </is>
       </c>
-      <c r="C103" s="30" t="n">
+      <c r="C103" s="28" t="n">
         <v>28</v>
       </c>
-      <c r="D103" s="29" t="inlineStr">
+      <c r="D103" s="27" t="inlineStr">
         <is>
           <t>Tecnico  en Gestion de Capital  Humanos</t>
         </is>
       </c>
-      <c r="E103" s="31" t="inlineStr">
+      <c r="E103" s="29" t="inlineStr">
         <is>
           <t>XI</t>
         </is>
       </c>
-      <c r="F103" s="32" t="n">
+      <c r="F103" s="12" t="n">
         <v>5343</v>
       </c>
     </row>
@@ -5334,7 +5324,7 @@
       <c r="A104" s="5" t="n">
         <v>103</v>
       </c>
-      <c r="B104" s="26" t="inlineStr">
+      <c r="B104" s="25" t="inlineStr">
         <is>
           <t>P-2 CUEVA LOS PORTALES</t>
         </is>
@@ -5342,17 +5332,17 @@
       <c r="C104" s="7" t="n">
         <v>29</v>
       </c>
-      <c r="D104" s="26" t="inlineStr">
+      <c r="D104" s="25" t="inlineStr">
         <is>
           <t>Operario labores agropec. Y jardineria</t>
         </is>
       </c>
-      <c r="E104" s="27" t="inlineStr">
+      <c r="E104" s="26" t="inlineStr">
         <is>
           <t>VIII</t>
         </is>
       </c>
-      <c r="F104" s="28" t="n">
+      <c r="F104" s="6" t="n">
         <v>4402</v>
       </c>
     </row>
@@ -5360,25 +5350,25 @@
       <c r="A105" s="5" t="n">
         <v>104</v>
       </c>
-      <c r="B105" s="29" t="inlineStr">
+      <c r="B105" s="27" t="inlineStr">
         <is>
           <t>P-2 CUEVA LOS PORTALES</t>
         </is>
       </c>
-      <c r="C105" s="30" t="n">
+      <c r="C105" s="28" t="n">
         <v>31</v>
       </c>
-      <c r="D105" s="29" t="inlineStr">
+      <c r="D105" s="27" t="inlineStr">
         <is>
           <t>Técnico en Gestión Económica</t>
         </is>
       </c>
-      <c r="E105" s="31" t="inlineStr">
+      <c r="E105" s="29" t="inlineStr">
         <is>
           <t>XI</t>
         </is>
       </c>
-      <c r="F105" s="32" t="n">
+      <c r="F105" s="12" t="n">
         <v>5343</v>
       </c>
     </row>
@@ -5386,7 +5376,7 @@
       <c r="A106" s="5" t="n">
         <v>105</v>
       </c>
-      <c r="B106" s="26" t="inlineStr">
+      <c r="B106" s="25" t="inlineStr">
         <is>
           <t>P-2 CUEVA LOS PORTALES</t>
         </is>
@@ -5394,17 +5384,17 @@
       <c r="C106" s="7" t="n">
         <v>33</v>
       </c>
-      <c r="D106" s="26" t="inlineStr">
+      <c r="D106" s="25" t="inlineStr">
         <is>
           <t>Dependiente  GastronomIco</t>
         </is>
       </c>
-      <c r="E106" s="27" t="inlineStr">
+      <c r="E106" s="26" t="inlineStr">
         <is>
           <t>IX</t>
         </is>
       </c>
-      <c r="F106" s="28" t="n">
+      <c r="F106" s="6" t="n">
         <v>4666</v>
       </c>
     </row>
@@ -5412,25 +5402,25 @@
       <c r="A107" s="5" t="n">
         <v>106</v>
       </c>
-      <c r="B107" s="29" t="inlineStr">
+      <c r="B107" s="27" t="inlineStr">
         <is>
           <t>P-2 CUEVA LOS PORTALES</t>
         </is>
       </c>
-      <c r="C107" s="30" t="n">
+      <c r="C107" s="28" t="n">
         <v>34</v>
       </c>
-      <c r="D107" s="29" t="inlineStr">
+      <c r="D107" s="27" t="inlineStr">
         <is>
           <t>Nivel Medio Superior</t>
         </is>
       </c>
-      <c r="E107" s="31" t="inlineStr">
+      <c r="E107" s="29" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="F107" s="32" t="n">
+      <c r="F107" s="12" t="n">
         <v>4993</v>
       </c>
     </row>
@@ -5438,7 +5428,7 @@
       <c r="A108" s="5" t="n">
         <v>107</v>
       </c>
-      <c r="B108" s="26" t="inlineStr">
+      <c r="B108" s="25" t="inlineStr">
         <is>
           <t>P-2 CUEVA LOS PORTALES</t>
         </is>
@@ -5446,17 +5436,17 @@
       <c r="C108" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="D108" s="26" t="inlineStr">
+      <c r="D108" s="25" t="inlineStr">
         <is>
           <t>Elaborador de Alimentos</t>
         </is>
       </c>
-      <c r="E108" s="27" t="inlineStr">
+      <c r="E108" s="26" t="inlineStr">
         <is>
           <t>IX</t>
         </is>
       </c>
-      <c r="F108" s="28" t="n">
+      <c r="F108" s="6" t="n">
         <v>4666</v>
       </c>
     </row>
@@ -5464,25 +5454,25 @@
       <c r="A109" s="5" t="n">
         <v>108</v>
       </c>
-      <c r="B109" s="29" t="inlineStr">
+      <c r="B109" s="27" t="inlineStr">
         <is>
           <t>P-2 CUEVA LOS PORTALES</t>
         </is>
       </c>
-      <c r="C109" s="30" t="n">
+      <c r="C109" s="28" t="n">
         <v>37</v>
       </c>
-      <c r="D109" s="29" t="inlineStr">
+      <c r="D109" s="27" t="inlineStr">
         <is>
           <t>Recepcionista Hotelero</t>
         </is>
       </c>
-      <c r="E109" s="31" t="inlineStr">
+      <c r="E109" s="29" t="inlineStr">
         <is>
           <t>IX</t>
         </is>
       </c>
-      <c r="F109" s="32" t="n">
+      <c r="F109" s="12" t="n">
         <v>4666</v>
       </c>
     </row>
@@ -5490,7 +5480,7 @@
       <c r="A110" s="5" t="n">
         <v>109</v>
       </c>
-      <c r="B110" s="26" t="inlineStr">
+      <c r="B110" s="25" t="inlineStr">
         <is>
           <t>P-2 CUEVA LOS PORTALES</t>
         </is>
@@ -5498,17 +5488,17 @@
       <c r="C110" s="7" t="n">
         <v>38</v>
       </c>
-      <c r="D110" s="26" t="inlineStr">
+      <c r="D110" s="25" t="inlineStr">
         <is>
           <t>Camarera de Habitaciones</t>
         </is>
       </c>
-      <c r="E110" s="27" t="inlineStr">
+      <c r="E110" s="26" t="inlineStr">
         <is>
           <t>IX</t>
         </is>
       </c>
-      <c r="F110" s="28" t="n">
+      <c r="F110" s="6" t="n">
         <v>4666</v>
       </c>
     </row>
@@ -5516,25 +5506,25 @@
       <c r="A111" s="5" t="n">
         <v>110</v>
       </c>
-      <c r="B111" s="29" t="inlineStr">
+      <c r="B111" s="27" t="inlineStr">
         <is>
           <t>P-2 CUEVA LOS PORTALES</t>
         </is>
       </c>
-      <c r="C111" s="30" t="n">
+      <c r="C111" s="28" t="n">
         <v>39</v>
       </c>
-      <c r="D111" s="29" t="inlineStr">
+      <c r="D111" s="27" t="inlineStr">
         <is>
           <t>Técnico en Recreación y animación</t>
         </is>
       </c>
-      <c r="E111" s="31" t="inlineStr">
+      <c r="E111" s="29" t="inlineStr">
         <is>
           <t>IX</t>
         </is>
       </c>
-      <c r="F111" s="32" t="n">
+      <c r="F111" s="12" t="n">
         <v>4666</v>
       </c>
     </row>
@@ -5542,7 +5532,7 @@
       <c r="A112" s="5" t="n">
         <v>111</v>
       </c>
-      <c r="B112" s="26" t="inlineStr">
+      <c r="B112" s="25" t="inlineStr">
         <is>
           <t>P-2 CUEVA LOS PORTALES</t>
         </is>
@@ -5550,17 +5540,17 @@
       <c r="C112" s="7" t="n">
         <v>41</v>
       </c>
-      <c r="D112" s="26" t="inlineStr">
+      <c r="D112" s="25" t="inlineStr">
         <is>
           <t>Encargado de Almacén</t>
         </is>
       </c>
-      <c r="E112" s="27" t="inlineStr">
+      <c r="E112" s="26" t="inlineStr">
         <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="F112" s="28" t="n">
+      <c r="F112" s="6" t="n">
         <v>3918</v>
       </c>
     </row>
@@ -5568,25 +5558,25 @@
       <c r="A113" s="5" t="n">
         <v>112</v>
       </c>
-      <c r="B113" s="29" t="inlineStr">
+      <c r="B113" s="27" t="inlineStr">
         <is>
           <t>P-2 CUEVA LOS PORTALES</t>
         </is>
       </c>
-      <c r="C113" s="30" t="n">
+      <c r="C113" s="28" t="n">
         <v>42</v>
       </c>
-      <c r="D113" s="29" t="inlineStr">
+      <c r="D113" s="27" t="inlineStr">
         <is>
           <t>Operario de Mante. Y Serv. Tecn.</t>
         </is>
       </c>
-      <c r="E113" s="31" t="inlineStr">
+      <c r="E113" s="29" t="inlineStr">
         <is>
           <t>VII</t>
         </is>
       </c>
-      <c r="F113" s="32" t="n">
+      <c r="F113" s="12" t="n">
         <v>4153</v>
       </c>
     </row>
@@ -5594,7 +5584,7 @@
       <c r="A114" s="5" t="n">
         <v>113</v>
       </c>
-      <c r="B114" s="26" t="inlineStr">
+      <c r="B114" s="25" t="inlineStr">
         <is>
           <t>P-2 CUEVA LOS PORTALES</t>
         </is>
@@ -5602,17 +5592,17 @@
       <c r="C114" s="7" t="n">
         <v>43</v>
       </c>
-      <c r="D114" s="26" t="inlineStr">
+      <c r="D114" s="25" t="inlineStr">
         <is>
           <t>Chofer vehiculos de carga</t>
         </is>
       </c>
-      <c r="E114" s="27" t="inlineStr">
+      <c r="E114" s="26" t="inlineStr">
         <is>
           <t>IX</t>
         </is>
       </c>
-      <c r="F114" s="28" t="n">
+      <c r="F114" s="6" t="n">
         <v>4666</v>
       </c>
     </row>
@@ -5620,25 +5610,25 @@
       <c r="A115" s="5" t="n">
         <v>114</v>
       </c>
-      <c r="B115" s="29" t="inlineStr">
+      <c r="B115" s="27" t="inlineStr">
         <is>
           <t>P-2 CUEVA LOS PORTALES</t>
         </is>
       </c>
-      <c r="C115" s="30" t="n">
+      <c r="C115" s="28" t="n">
         <v>45</v>
       </c>
-      <c r="D115" s="29" t="inlineStr">
+      <c r="D115" s="27" t="inlineStr">
         <is>
           <t>Agente de Seguridad y Protección</t>
         </is>
       </c>
-      <c r="E115" s="31" t="inlineStr">
+      <c r="E115" s="29" t="inlineStr">
         <is>
           <t>VIII</t>
         </is>
       </c>
-      <c r="F115" s="32" t="n">
+      <c r="F115" s="12" t="n">
         <v>4402</v>
       </c>
     </row>
@@ -5646,7 +5636,7 @@
       <c r="A116" s="5" t="n">
         <v>115</v>
       </c>
-      <c r="B116" s="26" t="inlineStr">
+      <c r="B116" s="25" t="inlineStr">
         <is>
           <t>P-2 SALTO LOS PORTALES</t>
         </is>
@@ -5654,17 +5644,17 @@
       <c r="C116" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="D116" s="26" t="inlineStr">
+      <c r="D116" s="25" t="inlineStr">
         <is>
           <t>Director de las Instalaciones y/o los Complejos</t>
         </is>
       </c>
-      <c r="E116" s="27" t="inlineStr">
+      <c r="E116" s="26" t="inlineStr">
         <is>
           <t>XIV</t>
         </is>
       </c>
-      <c r="F116" s="28" t="n">
+      <c r="F116" s="6" t="n">
         <v>6668</v>
       </c>
     </row>
@@ -5672,25 +5662,25 @@
       <c r="A117" s="5" t="n">
         <v>116</v>
       </c>
-      <c r="B117" s="29" t="inlineStr">
+      <c r="B117" s="27" t="inlineStr">
         <is>
           <t>P-2 SALTO LOS PORTALES</t>
         </is>
       </c>
-      <c r="C117" s="30" t="n">
+      <c r="C117" s="28" t="n">
         <v>23</v>
       </c>
-      <c r="D117" s="29" t="inlineStr">
+      <c r="D117" s="27" t="inlineStr">
         <is>
           <t>Subdirector Asistente</t>
         </is>
       </c>
-      <c r="E117" s="31" t="inlineStr">
+      <c r="E117" s="29" t="inlineStr">
         <is>
           <t>XIII</t>
         </is>
       </c>
-      <c r="F117" s="32" t="n">
+      <c r="F117" s="12" t="n">
         <v>6174</v>
       </c>
     </row>
@@ -5698,7 +5688,7 @@
       <c r="A118" s="5" t="n">
         <v>117</v>
       </c>
-      <c r="B118" s="26" t="inlineStr">
+      <c r="B118" s="25" t="inlineStr">
         <is>
           <t>P-2 SALTO LOS PORTALES</t>
         </is>
@@ -5706,17 +5696,17 @@
       <c r="C118" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="D118" s="26" t="inlineStr">
+      <c r="D118" s="25" t="inlineStr">
         <is>
           <t>Técnico  en Gestion de Capital   Humanos</t>
         </is>
       </c>
-      <c r="E118" s="27" t="inlineStr">
+      <c r="E118" s="26" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="F118" s="28" t="n">
+      <c r="F118" s="6" t="n">
         <v>4993</v>
       </c>
     </row>
@@ -5724,25 +5714,25 @@
       <c r="A119" s="5" t="n">
         <v>118</v>
       </c>
-      <c r="B119" s="29" t="inlineStr">
+      <c r="B119" s="27" t="inlineStr">
         <is>
           <t>P-2 SALTO LOS PORTALES</t>
         </is>
       </c>
-      <c r="C119" s="30" t="n">
+      <c r="C119" s="28" t="n">
         <v>26</v>
       </c>
-      <c r="D119" s="29" t="inlineStr">
+      <c r="D119" s="27" t="inlineStr">
         <is>
           <t>Especialista en Gestion  Economico.</t>
         </is>
       </c>
-      <c r="E119" s="31" t="inlineStr">
+      <c r="E119" s="29" t="inlineStr">
         <is>
           <t>XII</t>
         </is>
       </c>
-      <c r="F119" s="32" t="n">
+      <c r="F119" s="12" t="n">
         <v>5770</v>
       </c>
     </row>
@@ -5750,7 +5740,7 @@
       <c r="A120" s="5" t="n">
         <v>119</v>
       </c>
-      <c r="B120" s="26" t="inlineStr">
+      <c r="B120" s="25" t="inlineStr">
         <is>
           <t>P-2 SALTO LOS PORTALES</t>
         </is>
@@ -5758,17 +5748,17 @@
       <c r="C120" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="D120" s="26" t="inlineStr">
+      <c r="D120" s="25" t="inlineStr">
         <is>
           <t>Tec. Gest. Economica(Cajero)</t>
         </is>
       </c>
-      <c r="E120" s="27" t="inlineStr">
+      <c r="E120" s="26" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="F120" s="28" t="n">
+      <c r="F120" s="6" t="n">
         <v>4993</v>
       </c>
     </row>
@@ -5776,25 +5766,25 @@
       <c r="A121" s="5" t="n">
         <v>120</v>
       </c>
-      <c r="B121" s="29" t="inlineStr">
+      <c r="B121" s="27" t="inlineStr">
         <is>
           <t>P-2 SALTO LOS PORTALES</t>
         </is>
       </c>
-      <c r="C121" s="30" t="n">
+      <c r="C121" s="28" t="n">
         <v>29</v>
       </c>
-      <c r="D121" s="29" t="inlineStr">
+      <c r="D121" s="27" t="inlineStr">
         <is>
           <t>Jefe de Brigada de los Servicios</t>
         </is>
       </c>
-      <c r="E121" s="31" t="inlineStr">
+      <c r="E121" s="29" t="inlineStr">
         <is>
           <t>XI</t>
         </is>
       </c>
-      <c r="F121" s="32" t="n">
+      <c r="F121" s="12" t="n">
         <v>5343</v>
       </c>
     </row>
@@ -5802,7 +5792,7 @@
       <c r="A122" s="5" t="n">
         <v>121</v>
       </c>
-      <c r="B122" s="26" t="inlineStr">
+      <c r="B122" s="25" t="inlineStr">
         <is>
           <t>P-2 SALTO LOS PORTALES</t>
         </is>
@@ -5810,17 +5800,17 @@
       <c r="C122" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="D122" s="26" t="inlineStr">
+      <c r="D122" s="25" t="inlineStr">
         <is>
           <t>Dependiente Gastronómico</t>
         </is>
       </c>
-      <c r="E122" s="27" t="inlineStr">
+      <c r="E122" s="26" t="inlineStr">
         <is>
           <t>VIII</t>
         </is>
       </c>
-      <c r="F122" s="28" t="n">
+      <c r="F122" s="6" t="n">
         <v>4402</v>
       </c>
     </row>
@@ -5828,25 +5818,25 @@
       <c r="A123" s="5" t="n">
         <v>122</v>
       </c>
-      <c r="B123" s="29" t="inlineStr">
+      <c r="B123" s="27" t="inlineStr">
         <is>
           <t>P-2 SALTO LOS PORTALES</t>
         </is>
       </c>
-      <c r="C123" s="30" t="n">
+      <c r="C123" s="28" t="n">
         <v>31</v>
       </c>
-      <c r="D123" s="29" t="inlineStr">
+      <c r="D123" s="27" t="inlineStr">
         <is>
           <t>Nivel Medio Superior</t>
         </is>
       </c>
-      <c r="E123" s="31" t="inlineStr">
+      <c r="E123" s="29" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="F123" s="32" t="n">
+      <c r="F123" s="12" t="n">
         <v>4993</v>
       </c>
     </row>
@@ -5854,7 +5844,7 @@
       <c r="A124" s="5" t="n">
         <v>123</v>
       </c>
-      <c r="B124" s="26" t="inlineStr">
+      <c r="B124" s="25" t="inlineStr">
         <is>
           <t>P-2 SALTO LOS PORTALES</t>
         </is>
@@ -5862,17 +5852,17 @@
       <c r="C124" s="7" t="n">
         <v>32</v>
       </c>
-      <c r="D124" s="26" t="inlineStr">
+      <c r="D124" s="25" t="inlineStr">
         <is>
           <t>Nivel Medio</t>
         </is>
       </c>
-      <c r="E124" s="27" t="inlineStr">
+      <c r="E124" s="26" t="inlineStr">
         <is>
           <t>IX</t>
         </is>
       </c>
-      <c r="F124" s="28" t="n">
+      <c r="F124" s="6" t="n">
         <v>4666</v>
       </c>
     </row>
@@ -5880,25 +5870,25 @@
       <c r="A125" s="5" t="n">
         <v>124</v>
       </c>
-      <c r="B125" s="29" t="inlineStr">
+      <c r="B125" s="27" t="inlineStr">
         <is>
           <t>P-2 SALTO LOS PORTALES</t>
         </is>
       </c>
-      <c r="C125" s="30" t="n">
+      <c r="C125" s="28" t="n">
         <v>33</v>
       </c>
-      <c r="D125" s="29" t="inlineStr">
+      <c r="D125" s="27" t="inlineStr">
         <is>
           <t>Elaborador de Alimentos</t>
         </is>
       </c>
-      <c r="E125" s="31" t="inlineStr">
+      <c r="E125" s="29" t="inlineStr">
         <is>
           <t>VIII</t>
         </is>
       </c>
-      <c r="F125" s="32" t="n">
+      <c r="F125" s="12" t="n">
         <v>4402</v>
       </c>
     </row>
@@ -5906,7 +5896,7 @@
       <c r="A126" s="5" t="n">
         <v>125</v>
       </c>
-      <c r="B126" s="26" t="inlineStr">
+      <c r="B126" s="25" t="inlineStr">
         <is>
           <t>P-2 SALTO LOS PORTALES</t>
         </is>
@@ -5914,17 +5904,17 @@
       <c r="C126" s="7" t="n">
         <v>34</v>
       </c>
-      <c r="D126" s="26" t="inlineStr">
+      <c r="D126" s="25" t="inlineStr">
         <is>
           <t>Ayudante de Cocina</t>
         </is>
       </c>
-      <c r="E126" s="27" t="inlineStr">
+      <c r="E126" s="26" t="inlineStr">
         <is>
           <t>VII</t>
         </is>
       </c>
-      <c r="F126" s="28" t="n">
+      <c r="F126" s="6" t="n">
         <v>4153</v>
       </c>
     </row>
@@ -5932,25 +5922,25 @@
       <c r="A127" s="5" t="n">
         <v>126</v>
       </c>
-      <c r="B127" s="29" t="inlineStr">
+      <c r="B127" s="27" t="inlineStr">
         <is>
           <t>P-2 SALTO LOS PORTALES</t>
         </is>
       </c>
-      <c r="C127" s="30" t="n">
+      <c r="C127" s="28" t="n">
         <v>36</v>
       </c>
-      <c r="D127" s="29" t="inlineStr">
+      <c r="D127" s="27" t="inlineStr">
         <is>
           <t>Recepcionista Hotelero</t>
         </is>
       </c>
-      <c r="E127" s="31" t="inlineStr">
+      <c r="E127" s="29" t="inlineStr">
         <is>
           <t>VIII</t>
         </is>
       </c>
-      <c r="F127" s="32" t="n">
+      <c r="F127" s="12" t="n">
         <v>4402</v>
       </c>
     </row>
@@ -5958,7 +5948,7 @@
       <c r="A128" s="5" t="n">
         <v>127</v>
       </c>
-      <c r="B128" s="26" t="inlineStr">
+      <c r="B128" s="25" t="inlineStr">
         <is>
           <t>P-2 SALTO LOS PORTALES</t>
         </is>
@@ -5966,17 +5956,17 @@
       <c r="C128" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="D128" s="26" t="inlineStr">
+      <c r="D128" s="25" t="inlineStr">
         <is>
           <t>Camarera de Habitaciones</t>
         </is>
       </c>
-      <c r="E128" s="27" t="inlineStr">
+      <c r="E128" s="26" t="inlineStr">
         <is>
           <t>VIII</t>
         </is>
       </c>
-      <c r="F128" s="28" t="n">
+      <c r="F128" s="6" t="n">
         <v>4402</v>
       </c>
     </row>
@@ -5984,25 +5974,25 @@
       <c r="A129" s="5" t="n">
         <v>128</v>
       </c>
-      <c r="B129" s="29" t="inlineStr">
+      <c r="B129" s="27" t="inlineStr">
         <is>
           <t>P-2 SALTO LOS PORTALES</t>
         </is>
       </c>
-      <c r="C129" s="30" t="n">
+      <c r="C129" s="28" t="n">
         <v>38</v>
       </c>
-      <c r="D129" s="29" t="inlineStr">
+      <c r="D129" s="27" t="inlineStr">
         <is>
           <t>Técnico en Recreación y Animación</t>
         </is>
       </c>
-      <c r="E129" s="31" t="inlineStr">
+      <c r="E129" s="29" t="inlineStr">
         <is>
           <t>VIII</t>
         </is>
       </c>
-      <c r="F129" s="32" t="n">
+      <c r="F129" s="12" t="n">
         <v>4402</v>
       </c>
     </row>
@@ -6010,7 +6000,7 @@
       <c r="A130" s="5" t="n">
         <v>129</v>
       </c>
-      <c r="B130" s="26" t="inlineStr">
+      <c r="B130" s="25" t="inlineStr">
         <is>
           <t>P-2 SALTO LOS PORTALES</t>
         </is>
@@ -6018,17 +6008,17 @@
       <c r="C130" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="D130" s="26" t="inlineStr">
+      <c r="D130" s="25" t="inlineStr">
         <is>
           <t>Encargado de Almacén</t>
         </is>
       </c>
-      <c r="E130" s="27" t="inlineStr">
+      <c r="E130" s="26" t="inlineStr">
         <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="F130" s="28" t="n">
+      <c r="F130" s="6" t="n">
         <v>3918</v>
       </c>
     </row>
@@ -6036,25 +6026,25 @@
       <c r="A131" s="5" t="n">
         <v>130</v>
       </c>
-      <c r="B131" s="29" t="inlineStr">
+      <c r="B131" s="27" t="inlineStr">
         <is>
           <t>P-2 SALTO LOS PORTALES</t>
         </is>
       </c>
-      <c r="C131" s="30" t="n">
+      <c r="C131" s="28" t="n">
         <v>41</v>
       </c>
-      <c r="D131" s="29" t="inlineStr">
+      <c r="D131" s="27" t="inlineStr">
         <is>
           <t>Chofer vehiculos de carga</t>
         </is>
       </c>
-      <c r="E131" s="31" t="inlineStr">
+      <c r="E131" s="29" t="inlineStr">
         <is>
           <t>VIII</t>
         </is>
       </c>
-      <c r="F131" s="32" t="n">
+      <c r="F131" s="12" t="n">
         <v>4402</v>
       </c>
     </row>
@@ -6062,7 +6052,7 @@
       <c r="A132" s="5" t="n">
         <v>131</v>
       </c>
-      <c r="B132" s="26" t="inlineStr">
+      <c r="B132" s="25" t="inlineStr">
         <is>
           <t>P-2 SALTO LOS PORTALES</t>
         </is>
@@ -6070,17 +6060,17 @@
       <c r="C132" s="7" t="n">
         <v>42</v>
       </c>
-      <c r="D132" s="26" t="inlineStr">
+      <c r="D132" s="25" t="inlineStr">
         <is>
           <t>Operario de Mant. Y SERV. Tecnicos</t>
         </is>
       </c>
-      <c r="E132" s="27" t="inlineStr">
+      <c r="E132" s="26" t="inlineStr">
         <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="F132" s="28" t="n">
+      <c r="F132" s="6" t="n">
         <v>3918</v>
       </c>
     </row>
@@ -6088,25 +6078,25 @@
       <c r="A133" s="5" t="n">
         <v>132</v>
       </c>
-      <c r="B133" s="29" t="inlineStr">
+      <c r="B133" s="27" t="inlineStr">
         <is>
           <t>P-2 SALTO LOS PORTALES</t>
         </is>
       </c>
-      <c r="C133" s="30" t="n">
+      <c r="C133" s="28" t="n">
         <v>44</v>
       </c>
-      <c r="D133" s="29" t="inlineStr">
+      <c r="D133" s="27" t="inlineStr">
         <is>
           <t>Jefe de Grupo de Seguridad Interna</t>
         </is>
       </c>
-      <c r="E133" s="31" t="inlineStr">
+      <c r="E133" s="29" t="inlineStr">
         <is>
           <t>XI</t>
         </is>
       </c>
-      <c r="F133" s="32" t="n">
+      <c r="F133" s="12" t="n">
         <v>5343</v>
       </c>
     </row>
@@ -6114,7 +6104,7 @@
       <c r="A134" s="5" t="n">
         <v>133</v>
       </c>
-      <c r="B134" s="26" t="inlineStr">
+      <c r="B134" s="25" t="inlineStr">
         <is>
           <t>P-2 SALTO LOS PORTALES</t>
         </is>
@@ -6122,17 +6112,17 @@
       <c r="C134" s="7" t="n">
         <v>45</v>
       </c>
-      <c r="D134" s="26" t="inlineStr">
+      <c r="D134" s="25" t="inlineStr">
         <is>
           <t>Agente de Seguridad  y Protección</t>
         </is>
       </c>
-      <c r="E134" s="27" t="inlineStr">
+      <c r="E134" s="26" t="inlineStr">
         <is>
           <t>VII</t>
         </is>
       </c>
-      <c r="F134" s="28" t="n">
+      <c r="F134" s="6" t="n">
         <v>4153</v>
       </c>
     </row>
@@ -6140,25 +6130,25 @@
       <c r="A135" s="5" t="n">
         <v>134</v>
       </c>
-      <c r="B135" s="29" t="inlineStr">
+      <c r="B135" s="27" t="inlineStr">
         <is>
           <t>P-2 EL COPEY</t>
         </is>
       </c>
-      <c r="C135" s="30" t="n">
+      <c r="C135" s="28" t="n">
         <v>24</v>
       </c>
-      <c r="D135" s="29" t="inlineStr">
+      <c r="D135" s="27" t="inlineStr">
         <is>
           <t>Director de las Instalaciones y/o los Complejos</t>
         </is>
       </c>
-      <c r="E135" s="31" t="inlineStr">
+      <c r="E135" s="29" t="inlineStr">
         <is>
           <t>XIII</t>
         </is>
       </c>
-      <c r="F135" s="32" t="n">
+      <c r="F135" s="12" t="n">
         <v>6174</v>
       </c>
     </row>
@@ -6166,7 +6156,7 @@
       <c r="A136" s="5" t="n">
         <v>135</v>
       </c>
-      <c r="B136" s="26" t="inlineStr">
+      <c r="B136" s="25" t="inlineStr">
         <is>
           <t>P-2 EL COPEY</t>
         </is>
@@ -6174,17 +6164,17 @@
       <c r="C136" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="D136" s="26" t="inlineStr">
+      <c r="D136" s="25" t="inlineStr">
         <is>
           <t>Subdirector Asistente</t>
         </is>
       </c>
-      <c r="E136" s="27" t="inlineStr">
+      <c r="E136" s="26" t="inlineStr">
         <is>
           <t>XII</t>
         </is>
       </c>
-      <c r="F136" s="28" t="n">
+      <c r="F136" s="6" t="n">
         <v>5770</v>
       </c>
     </row>
@@ -6192,25 +6182,25 @@
       <c r="A137" s="5" t="n">
         <v>136</v>
       </c>
-      <c r="B137" s="29" t="inlineStr">
+      <c r="B137" s="27" t="inlineStr">
         <is>
           <t>P-2 EL COPEY</t>
         </is>
       </c>
-      <c r="C137" s="30" t="n">
+      <c r="C137" s="28" t="n">
         <v>26</v>
       </c>
-      <c r="D137" s="29" t="inlineStr">
+      <c r="D137" s="27" t="inlineStr">
         <is>
           <t>Sub Director Servicios</t>
         </is>
       </c>
-      <c r="E137" s="31" t="inlineStr">
+      <c r="E137" s="29" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="F137" s="32" t="n">
+      <c r="F137" s="12" t="n">
         <v>4993</v>
       </c>
     </row>
@@ -6218,7 +6208,7 @@
       <c r="A138" s="5" t="n">
         <v>137</v>
       </c>
-      <c r="B138" s="26" t="inlineStr">
+      <c r="B138" s="25" t="inlineStr">
         <is>
           <t>P-2 EL COPEY</t>
         </is>
@@ -6226,17 +6216,17 @@
       <c r="C138" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="D138" s="26" t="inlineStr">
+      <c r="D138" s="25" t="inlineStr">
         <is>
           <t>Chofer vehiculos ligeros</t>
         </is>
       </c>
-      <c r="E138" s="27" t="inlineStr">
+      <c r="E138" s="26" t="inlineStr">
         <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="F138" s="28" t="n">
+      <c r="F138" s="6" t="n">
         <v>3918</v>
       </c>
     </row>
@@ -6244,25 +6234,25 @@
       <c r="A139" s="5" t="n">
         <v>138</v>
       </c>
-      <c r="B139" s="29" t="inlineStr">
+      <c r="B139" s="27" t="inlineStr">
         <is>
           <t>P-2 EL COPEY</t>
         </is>
       </c>
-      <c r="C139" s="30" t="n">
+      <c r="C139" s="28" t="n">
         <v>28</v>
       </c>
-      <c r="D139" s="29" t="inlineStr">
+      <c r="D139" s="27" t="inlineStr">
         <is>
           <t>Tècnico en gestion de capital  Humanos</t>
         </is>
       </c>
-      <c r="E139" s="31" t="inlineStr">
+      <c r="E139" s="29" t="inlineStr">
         <is>
           <t>IX</t>
         </is>
       </c>
-      <c r="F139" s="32" t="n">
+      <c r="F139" s="12" t="n">
         <v>4666</v>
       </c>
     </row>
@@ -6270,7 +6260,7 @@
       <c r="A140" s="5" t="n">
         <v>139</v>
       </c>
-      <c r="B140" s="26" t="inlineStr">
+      <c r="B140" s="25" t="inlineStr">
         <is>
           <t>P-2 EL COPEY</t>
         </is>
@@ -6278,17 +6268,17 @@
       <c r="C140" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="D140" s="26" t="inlineStr">
+      <c r="D140" s="25" t="inlineStr">
         <is>
           <t>Tecnico en Gestion Economica</t>
         </is>
       </c>
-      <c r="E140" s="27" t="inlineStr">
+      <c r="E140" s="26" t="inlineStr">
         <is>
           <t>IX</t>
         </is>
       </c>
-      <c r="F140" s="28" t="n">
+      <c r="F140" s="6" t="n">
         <v>4666</v>
       </c>
     </row>
@@ -6296,25 +6286,25 @@
       <c r="A141" s="5" t="n">
         <v>140</v>
       </c>
-      <c r="B141" s="29" t="inlineStr">
+      <c r="B141" s="27" t="inlineStr">
         <is>
           <t>P-2 EL COPEY</t>
         </is>
       </c>
-      <c r="C141" s="30" t="n">
+      <c r="C141" s="28" t="n">
         <v>31</v>
       </c>
-      <c r="D141" s="29" t="inlineStr">
+      <c r="D141" s="27" t="inlineStr">
         <is>
           <t>Tecnico en Gestion Economica Cajero Pagador</t>
         </is>
       </c>
-      <c r="E141" s="31" t="inlineStr">
+      <c r="E141" s="29" t="inlineStr">
         <is>
           <t>IX</t>
         </is>
       </c>
-      <c r="F141" s="32" t="n">
+      <c r="F141" s="12" t="n">
         <v>4666</v>
       </c>
     </row>
@@ -6322,7 +6312,7 @@
       <c r="A142" s="5" t="n">
         <v>141</v>
       </c>
-      <c r="B142" s="26" t="inlineStr">
+      <c r="B142" s="25" t="inlineStr">
         <is>
           <t>P-2 EL COPEY</t>
         </is>
@@ -6330,17 +6320,17 @@
       <c r="C142" s="7" t="n">
         <v>33</v>
       </c>
-      <c r="D142" s="26" t="inlineStr">
+      <c r="D142" s="25" t="inlineStr">
         <is>
           <t>Dependiente Gastronomico</t>
         </is>
       </c>
-      <c r="E142" s="27" t="inlineStr">
+      <c r="E142" s="26" t="inlineStr">
         <is>
           <t>VII</t>
         </is>
       </c>
-      <c r="F142" s="28" t="n">
+      <c r="F142" s="6" t="n">
         <v>4153</v>
       </c>
     </row>
@@ -6348,25 +6338,25 @@
       <c r="A143" s="5" t="n">
         <v>142</v>
       </c>
-      <c r="B143" s="29" t="inlineStr">
+      <c r="B143" s="27" t="inlineStr">
         <is>
           <t>P-2 EL COPEY</t>
         </is>
       </c>
-      <c r="C143" s="30" t="n">
+      <c r="C143" s="28" t="n">
         <v>34</v>
       </c>
-      <c r="D143" s="29" t="inlineStr">
+      <c r="D143" s="27" t="inlineStr">
         <is>
           <t>Nivel Medio Superior</t>
         </is>
       </c>
-      <c r="E143" s="31" t="inlineStr">
+      <c r="E143" s="29" t="inlineStr">
         <is>
           <t>VIII</t>
         </is>
       </c>
-      <c r="F143" s="32" t="n">
+      <c r="F143" s="12" t="n">
         <v>4402</v>
       </c>
     </row>
@@ -6374,7 +6364,7 @@
       <c r="A144" s="5" t="n">
         <v>143</v>
       </c>
-      <c r="B144" s="26" t="inlineStr">
+      <c r="B144" s="25" t="inlineStr">
         <is>
           <t>P-2 EL COPEY</t>
         </is>
@@ -6382,17 +6372,17 @@
       <c r="C144" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="D144" s="26" t="inlineStr">
+      <c r="D144" s="25" t="inlineStr">
         <is>
           <t>Elaborador de Alimentos</t>
         </is>
       </c>
-      <c r="E144" s="27" t="inlineStr">
+      <c r="E144" s="26" t="inlineStr">
         <is>
           <t>VII</t>
         </is>
       </c>
-      <c r="F144" s="28" t="n">
+      <c r="F144" s="6" t="n">
         <v>4153</v>
       </c>
     </row>
@@ -6400,25 +6390,25 @@
       <c r="A145" s="5" t="n">
         <v>144</v>
       </c>
-      <c r="B145" s="29" t="inlineStr">
+      <c r="B145" s="27" t="inlineStr">
         <is>
           <t>P-2 EL COPEY</t>
         </is>
       </c>
-      <c r="C145" s="30" t="n">
+      <c r="C145" s="28" t="n">
         <v>37</v>
       </c>
-      <c r="D145" s="29" t="inlineStr">
+      <c r="D145" s="27" t="inlineStr">
         <is>
           <t>Recepcionista Hotelero</t>
         </is>
       </c>
-      <c r="E145" s="31" t="inlineStr">
+      <c r="E145" s="29" t="inlineStr">
         <is>
           <t>VII</t>
         </is>
       </c>
-      <c r="F145" s="32" t="n">
+      <c r="F145" s="12" t="n">
         <v>4153</v>
       </c>
     </row>
@@ -6426,7 +6416,7 @@
       <c r="A146" s="5" t="n">
         <v>145</v>
       </c>
-      <c r="B146" s="26" t="inlineStr">
+      <c r="B146" s="25" t="inlineStr">
         <is>
           <t>P-2 EL COPEY</t>
         </is>
@@ -6434,17 +6424,17 @@
       <c r="C146" s="7" t="n">
         <v>38</v>
       </c>
-      <c r="D146" s="26" t="inlineStr">
+      <c r="D146" s="25" t="inlineStr">
         <is>
           <t>Camarera de Habitaciones</t>
         </is>
       </c>
-      <c r="E146" s="27" t="inlineStr">
+      <c r="E146" s="26" t="inlineStr">
         <is>
           <t>VII</t>
         </is>
       </c>
-      <c r="F146" s="28" t="n">
+      <c r="F146" s="6" t="n">
         <v>4153</v>
       </c>
     </row>
@@ -6452,25 +6442,25 @@
       <c r="A147" s="5" t="n">
         <v>146</v>
       </c>
-      <c r="B147" s="29" t="inlineStr">
+      <c r="B147" s="27" t="inlineStr">
         <is>
           <t>P-2 EL COPEY</t>
         </is>
       </c>
-      <c r="C147" s="30" t="n">
+      <c r="C147" s="28" t="n">
         <v>40</v>
       </c>
-      <c r="D147" s="29" t="inlineStr">
+      <c r="D147" s="27" t="inlineStr">
         <is>
           <t>Tècnico de Recreación y Animación</t>
         </is>
       </c>
-      <c r="E147" s="31" t="inlineStr">
+      <c r="E147" s="29" t="inlineStr">
         <is>
           <t>VII</t>
         </is>
       </c>
-      <c r="F147" s="32" t="n">
+      <c r="F147" s="12" t="n">
         <v>4153</v>
       </c>
     </row>
@@ -6478,7 +6468,7 @@
       <c r="A148" s="5" t="n">
         <v>147</v>
       </c>
-      <c r="B148" s="26" t="inlineStr">
+      <c r="B148" s="25" t="inlineStr">
         <is>
           <t>P-2 EL COPEY</t>
         </is>
@@ -6486,17 +6476,17 @@
       <c r="C148" s="7" t="n">
         <v>42</v>
       </c>
-      <c r="D148" s="26" t="inlineStr">
+      <c r="D148" s="25" t="inlineStr">
         <is>
           <t>Encargado de Almacèn</t>
         </is>
       </c>
-      <c r="E148" s="27" t="inlineStr">
+      <c r="E148" s="26" t="inlineStr">
         <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="F148" s="28" t="n">
+      <c r="F148" s="6" t="n">
         <v>3918</v>
       </c>
     </row>
@@ -6504,25 +6494,25 @@
       <c r="A149" s="5" t="n">
         <v>148</v>
       </c>
-      <c r="B149" s="29" t="inlineStr">
+      <c r="B149" s="27" t="inlineStr">
         <is>
           <t>P-2 EL COPEY</t>
         </is>
       </c>
-      <c r="C149" s="30" t="n">
+      <c r="C149" s="28" t="n">
         <v>43</v>
       </c>
-      <c r="D149" s="29" t="inlineStr">
+      <c r="D149" s="27" t="inlineStr">
         <is>
           <t>Operario de Mant. Y Serv. Tecnicos</t>
         </is>
       </c>
-      <c r="E149" s="31" t="inlineStr">
+      <c r="E149" s="29" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="F149" s="32" t="n">
+      <c r="F149" s="12" t="n">
         <v>3696</v>
       </c>
     </row>
@@ -6530,7 +6520,7 @@
       <c r="A150" s="5" t="n">
         <v>149</v>
       </c>
-      <c r="B150" s="26" t="inlineStr">
+      <c r="B150" s="25" t="inlineStr">
         <is>
           <t>P-2 EL COPEY</t>
         </is>
@@ -6538,17 +6528,17 @@
       <c r="C150" s="7" t="n">
         <v>45</v>
       </c>
-      <c r="D150" s="26" t="inlineStr">
+      <c r="D150" s="25" t="inlineStr">
         <is>
           <t>Jefe de Grupo de Seguridad Interna</t>
         </is>
       </c>
-      <c r="E150" s="27" t="inlineStr">
+      <c r="E150" s="26" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="F150" s="28" t="n">
+      <c r="F150" s="6" t="n">
         <v>4993</v>
       </c>
     </row>
@@ -6556,25 +6546,25 @@
       <c r="A151" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="B151" s="29" t="inlineStr">
+      <c r="B151" s="27" t="inlineStr">
         <is>
           <t>P-2 EL COPEY</t>
         </is>
       </c>
-      <c r="C151" s="30" t="n">
+      <c r="C151" s="28" t="n">
         <v>46</v>
       </c>
-      <c r="D151" s="29" t="inlineStr">
+      <c r="D151" s="27" t="inlineStr">
         <is>
           <t>Agente de Seguridad y Protecciòn</t>
         </is>
       </c>
-      <c r="E151" s="31" t="inlineStr">
+      <c r="E151" s="29" t="inlineStr">
         <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="F151" s="32" t="n">
+      <c r="F151" s="12" t="n">
         <v>3918</v>
       </c>
     </row>
@@ -6582,7 +6572,7 @@
       <c r="A152" s="5" t="n">
         <v>151</v>
       </c>
-      <c r="B152" s="26" t="inlineStr">
+      <c r="B152" s="25" t="inlineStr">
         <is>
           <t>P-2 PAJARITO</t>
         </is>
@@ -6590,17 +6580,17 @@
       <c r="C152" s="7" t="n">
         <v>26</v>
       </c>
-      <c r="D152" s="26" t="inlineStr">
+      <c r="D152" s="25" t="inlineStr">
         <is>
           <t>Director de las Instalaciones y/o los Complejos</t>
         </is>
       </c>
-      <c r="E152" s="27" t="inlineStr">
+      <c r="E152" s="26" t="inlineStr">
         <is>
           <t>XIII</t>
         </is>
       </c>
-      <c r="F152" s="28" t="n">
+      <c r="F152" s="6" t="n">
         <v>6174</v>
       </c>
     </row>
@@ -6608,25 +6598,25 @@
       <c r="A153" s="5" t="n">
         <v>152</v>
       </c>
-      <c r="B153" s="29" t="inlineStr">
+      <c r="B153" s="27" t="inlineStr">
         <is>
           <t>P-2 PAJARITO</t>
         </is>
       </c>
-      <c r="C153" s="30" t="n">
+      <c r="C153" s="28" t="n">
         <v>27</v>
       </c>
-      <c r="D153" s="29" t="inlineStr">
+      <c r="D153" s="27" t="inlineStr">
         <is>
           <t>Subdirector Asistente de Servicios y Calidad</t>
         </is>
       </c>
-      <c r="E153" s="31" t="inlineStr">
+      <c r="E153" s="29" t="inlineStr">
         <is>
           <t>XII</t>
         </is>
       </c>
-      <c r="F153" s="32" t="n">
+      <c r="F153" s="12" t="n">
         <v>5770</v>
       </c>
     </row>
@@ -6634,7 +6624,7 @@
       <c r="A154" s="5" t="n">
         <v>153</v>
       </c>
-      <c r="B154" s="26" t="inlineStr">
+      <c r="B154" s="25" t="inlineStr">
         <is>
           <t>P-2 PAJARITO</t>
         </is>
@@ -6642,17 +6632,17 @@
       <c r="C154" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="D154" s="26" t="inlineStr">
+      <c r="D154" s="25" t="inlineStr">
         <is>
           <t>Subdirector Asistente de  Control Interno</t>
         </is>
       </c>
-      <c r="E154" s="27" t="inlineStr">
+      <c r="E154" s="26" t="inlineStr">
         <is>
           <t>XII</t>
         </is>
       </c>
-      <c r="F154" s="28" t="n">
+      <c r="F154" s="6" t="n">
         <v>5770</v>
       </c>
     </row>
@@ -6660,25 +6650,25 @@
       <c r="A155" s="5" t="n">
         <v>154</v>
       </c>
-      <c r="B155" s="29" t="inlineStr">
+      <c r="B155" s="27" t="inlineStr">
         <is>
           <t>P-2 PAJARITO</t>
         </is>
       </c>
-      <c r="C155" s="30" t="n">
+      <c r="C155" s="28" t="n">
         <v>29</v>
       </c>
-      <c r="D155" s="29" t="inlineStr">
+      <c r="D155" s="27" t="inlineStr">
         <is>
           <t>Tecnico  en Gestion de Capital Humanos</t>
         </is>
       </c>
-      <c r="E155" s="31" t="inlineStr">
+      <c r="E155" s="29" t="inlineStr">
         <is>
           <t>IX</t>
         </is>
       </c>
-      <c r="F155" s="32" t="n">
+      <c r="F155" s="12" t="n">
         <v>4666</v>
       </c>
     </row>
@@ -6686,7 +6676,7 @@
       <c r="A156" s="5" t="n">
         <v>155</v>
       </c>
-      <c r="B156" s="26" t="inlineStr">
+      <c r="B156" s="25" t="inlineStr">
         <is>
           <t>P-2 PAJARITO</t>
         </is>
@@ -6694,17 +6684,17 @@
       <c r="C156" s="7" t="n">
         <v>31</v>
       </c>
-      <c r="D156" s="26" t="inlineStr">
+      <c r="D156" s="25" t="inlineStr">
         <is>
           <t>Técnico  en Gestión Económica</t>
         </is>
       </c>
-      <c r="E156" s="27" t="inlineStr">
+      <c r="E156" s="26" t="inlineStr">
         <is>
           <t>IX</t>
         </is>
       </c>
-      <c r="F156" s="28" t="n">
+      <c r="F156" s="6" t="n">
         <v>4666</v>
       </c>
     </row>
@@ -6712,25 +6702,25 @@
       <c r="A157" s="5" t="n">
         <v>156</v>
       </c>
-      <c r="B157" s="29" t="inlineStr">
+      <c r="B157" s="27" t="inlineStr">
         <is>
           <t>P-2 PAJARITO</t>
         </is>
       </c>
-      <c r="C157" s="30" t="n">
+      <c r="C157" s="28" t="n">
         <v>33</v>
       </c>
-      <c r="D157" s="29" t="inlineStr">
+      <c r="D157" s="27" t="inlineStr">
         <is>
           <t>Dependiente Gastronómico</t>
         </is>
       </c>
-      <c r="E157" s="31" t="inlineStr">
+      <c r="E157" s="29" t="inlineStr">
         <is>
           <t>VII</t>
         </is>
       </c>
-      <c r="F157" s="32" t="n">
+      <c r="F157" s="12" t="n">
         <v>4153</v>
       </c>
     </row>
@@ -6738,7 +6728,7 @@
       <c r="A158" s="5" t="n">
         <v>157</v>
       </c>
-      <c r="B158" s="26" t="inlineStr">
+      <c r="B158" s="25" t="inlineStr">
         <is>
           <t>P-2 PAJARITO</t>
         </is>
@@ -6746,17 +6736,17 @@
       <c r="C158" s="7" t="n">
         <v>34</v>
       </c>
-      <c r="D158" s="26" t="inlineStr">
+      <c r="D158" s="25" t="inlineStr">
         <is>
           <t>Nivel Medio Superior</t>
         </is>
       </c>
-      <c r="E158" s="27" t="inlineStr">
+      <c r="E158" s="26" t="inlineStr">
         <is>
           <t>VIII</t>
         </is>
       </c>
-      <c r="F158" s="28" t="n">
+      <c r="F158" s="6" t="n">
         <v>4402</v>
       </c>
     </row>
@@ -6764,25 +6754,25 @@
       <c r="A159" s="5" t="n">
         <v>158</v>
       </c>
-      <c r="B159" s="29" t="inlineStr">
+      <c r="B159" s="27" t="inlineStr">
         <is>
           <t>P-2 PAJARITO</t>
         </is>
       </c>
-      <c r="C159" s="30" t="n">
+      <c r="C159" s="28" t="n">
         <v>35</v>
       </c>
-      <c r="D159" s="29" t="inlineStr">
+      <c r="D159" s="27" t="inlineStr">
         <is>
           <t>Elaborador de Alimentos</t>
         </is>
       </c>
-      <c r="E159" s="31" t="inlineStr">
+      <c r="E159" s="29" t="inlineStr">
         <is>
           <t>VII</t>
         </is>
       </c>
-      <c r="F159" s="32" t="n">
+      <c r="F159" s="12" t="n">
         <v>4153</v>
       </c>
     </row>
@@ -6790,7 +6780,7 @@
       <c r="A160" s="5" t="n">
         <v>159</v>
       </c>
-      <c r="B160" s="26" t="inlineStr">
+      <c r="B160" s="25" t="inlineStr">
         <is>
           <t>P-2 PAJARITO</t>
         </is>
@@ -6798,17 +6788,17 @@
       <c r="C160" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="D160" s="26" t="inlineStr">
+      <c r="D160" s="25" t="inlineStr">
         <is>
           <t>Recepcionista Hotelero</t>
         </is>
       </c>
-      <c r="E160" s="27" t="inlineStr">
+      <c r="E160" s="26" t="inlineStr">
         <is>
           <t>VII</t>
         </is>
       </c>
-      <c r="F160" s="28" t="n">
+      <c r="F160" s="6" t="n">
         <v>4153</v>
       </c>
     </row>
@@ -6816,25 +6806,25 @@
       <c r="A161" s="5" t="n">
         <v>160</v>
       </c>
-      <c r="B161" s="29" t="inlineStr">
+      <c r="B161" s="27" t="inlineStr">
         <is>
           <t>P-2 PAJARITO</t>
         </is>
       </c>
-      <c r="C161" s="30" t="n">
+      <c r="C161" s="28" t="n">
         <v>38</v>
       </c>
-      <c r="D161" s="29" t="inlineStr">
+      <c r="D161" s="27" t="inlineStr">
         <is>
           <t>Camarera de Habitaciones</t>
         </is>
       </c>
-      <c r="E161" s="31" t="inlineStr">
+      <c r="E161" s="29" t="inlineStr">
         <is>
           <t>VII</t>
         </is>
       </c>
-      <c r="F161" s="32" t="n">
+      <c r="F161" s="12" t="n">
         <v>4153</v>
       </c>
     </row>
@@ -6842,7 +6832,7 @@
       <c r="A162" s="5" t="n">
         <v>161</v>
       </c>
-      <c r="B162" s="26" t="inlineStr">
+      <c r="B162" s="25" t="inlineStr">
         <is>
           <t>P-2 PAJARITO</t>
         </is>
@@ -6850,17 +6840,17 @@
       <c r="C162" s="7" t="n">
         <v>39</v>
       </c>
-      <c r="D162" s="26" t="inlineStr">
+      <c r="D162" s="25" t="inlineStr">
         <is>
           <t>Técnico  en Recreación y Animación</t>
         </is>
       </c>
-      <c r="E162" s="27" t="inlineStr">
+      <c r="E162" s="26" t="inlineStr">
         <is>
           <t>VII</t>
         </is>
       </c>
-      <c r="F162" s="28" t="n">
+      <c r="F162" s="6" t="n">
         <v>4153</v>
       </c>
     </row>
@@ -6868,25 +6858,25 @@
       <c r="A163" s="5" t="n">
         <v>162</v>
       </c>
-      <c r="B163" s="29" t="inlineStr">
+      <c r="B163" s="27" t="inlineStr">
         <is>
           <t>P-2 PAJARITO</t>
         </is>
       </c>
-      <c r="C163" s="30" t="n">
+      <c r="C163" s="28" t="n">
         <v>41</v>
       </c>
-      <c r="D163" s="29" t="inlineStr">
+      <c r="D163" s="27" t="inlineStr">
         <is>
           <t>Encargado de Almacén</t>
         </is>
       </c>
-      <c r="E163" s="31" t="inlineStr">
+      <c r="E163" s="29" t="inlineStr">
         <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="F163" s="32" t="n">
+      <c r="F163" s="12" t="n">
         <v>3918</v>
       </c>
     </row>
@@ -6894,7 +6884,7 @@
       <c r="A164" s="5" t="n">
         <v>163</v>
       </c>
-      <c r="B164" s="26" t="inlineStr">
+      <c r="B164" s="25" t="inlineStr">
         <is>
           <t>P-2 PAJARITO</t>
         </is>
@@ -6902,17 +6892,17 @@
       <c r="C164" s="7" t="n">
         <v>42</v>
       </c>
-      <c r="D164" s="26" t="inlineStr">
+      <c r="D164" s="25" t="inlineStr">
         <is>
           <t>Operario de Mant. Y SERV. TEC.</t>
         </is>
       </c>
-      <c r="E164" s="27" t="inlineStr">
+      <c r="E164" s="26" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="F164" s="28" t="n">
+      <c r="F164" s="6" t="n">
         <v>3696</v>
       </c>
     </row>
@@ -6920,25 +6910,25 @@
       <c r="A165" s="5" t="n">
         <v>164</v>
       </c>
-      <c r="B165" s="29" t="inlineStr">
+      <c r="B165" s="27" t="inlineStr">
         <is>
           <t>P-2 PAJARITO</t>
         </is>
       </c>
-      <c r="C165" s="30" t="n">
+      <c r="C165" s="28" t="n">
         <v>44</v>
       </c>
-      <c r="D165" s="29" t="inlineStr">
+      <c r="D165" s="27" t="inlineStr">
         <is>
           <t>Agente de Seguridad y Proteccion</t>
         </is>
       </c>
-      <c r="E165" s="31" t="inlineStr">
+      <c r="E165" s="29" t="inlineStr">
         <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="F165" s="32" t="n">
+      <c r="F165" s="12" t="n">
         <v>3918</v>
       </c>
     </row>
@@ -6946,7 +6936,7 @@
       <c r="A166" s="5" t="n">
         <v>165</v>
       </c>
-      <c r="B166" s="26" t="inlineStr">
+      <c r="B166" s="25" t="inlineStr">
         <is>
           <t>Boca de Galafre</t>
         </is>
@@ -6954,17 +6944,17 @@
       <c r="C166" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="D166" s="26" t="inlineStr">
+      <c r="D166" s="25" t="inlineStr">
         <is>
           <t>Director de las Instalaciones y/o los Complejos</t>
         </is>
       </c>
-      <c r="E166" s="27" t="inlineStr">
+      <c r="E166" s="26" t="inlineStr">
         <is>
           <t>XIII</t>
         </is>
       </c>
-      <c r="F166" s="28" t="n">
+      <c r="F166" s="6" t="n">
         <v>6174</v>
       </c>
     </row>
@@ -6972,25 +6962,25 @@
       <c r="A167" s="5" t="n">
         <v>166</v>
       </c>
-      <c r="B167" s="29" t="inlineStr">
+      <c r="B167" s="27" t="inlineStr">
         <is>
           <t>Boca de Galafre</t>
         </is>
       </c>
-      <c r="C167" s="30" t="n">
+      <c r="C167" s="28" t="n">
         <v>25</v>
       </c>
-      <c r="D167" s="29" t="inlineStr">
+      <c r="D167" s="27" t="inlineStr">
         <is>
           <t>Subdirector Asistente</t>
         </is>
       </c>
-      <c r="E167" s="31" t="inlineStr">
+      <c r="E167" s="29" t="inlineStr">
         <is>
           <t>XII</t>
         </is>
       </c>
-      <c r="F167" s="32" t="n">
+      <c r="F167" s="12" t="n">
         <v>5770</v>
       </c>
     </row>
@@ -6998,7 +6988,7 @@
       <c r="A168" s="5" t="n">
         <v>167</v>
       </c>
-      <c r="B168" s="26" t="inlineStr">
+      <c r="B168" s="25" t="inlineStr">
         <is>
           <t>Boca de Galafre</t>
         </is>
@@ -7006,17 +6996,17 @@
       <c r="C168" s="7" t="n">
         <v>26</v>
       </c>
-      <c r="D168" s="26" t="inlineStr">
+      <c r="D168" s="25" t="inlineStr">
         <is>
           <t>Jefe de Brigada de los Servicios</t>
         </is>
       </c>
-      <c r="E168" s="27" t="inlineStr">
+      <c r="E168" s="26" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="F168" s="28" t="n">
+      <c r="F168" s="6" t="n">
         <v>4993</v>
       </c>
     </row>
@@ -7024,25 +7014,25 @@
       <c r="A169" s="5" t="n">
         <v>168</v>
       </c>
-      <c r="B169" s="29" t="inlineStr">
+      <c r="B169" s="27" t="inlineStr">
         <is>
           <t>Boca de Galafre</t>
         </is>
       </c>
-      <c r="C169" s="30" t="n">
+      <c r="C169" s="28" t="n">
         <v>27</v>
       </c>
-      <c r="D169" s="29" t="inlineStr">
+      <c r="D169" s="27" t="inlineStr">
         <is>
           <t>Chofer Vehiculos Ligeros</t>
         </is>
       </c>
-      <c r="E169" s="31" t="inlineStr">
+      <c r="E169" s="29" t="inlineStr">
         <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="F169" s="32" t="n">
+      <c r="F169" s="12" t="n">
         <v>3918</v>
       </c>
     </row>
@@ -7050,7 +7040,7 @@
       <c r="A170" s="5" t="n">
         <v>169</v>
       </c>
-      <c r="B170" s="26" t="inlineStr">
+      <c r="B170" s="25" t="inlineStr">
         <is>
           <t>Boca de Galafre</t>
         </is>
@@ -7058,17 +7048,17 @@
       <c r="C170" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="D170" s="26" t="inlineStr">
+      <c r="D170" s="25" t="inlineStr">
         <is>
           <t>Tecnico  en Gestion de Capital Humanos</t>
         </is>
       </c>
-      <c r="E170" s="27" t="inlineStr">
+      <c r="E170" s="26" t="inlineStr">
         <is>
           <t>IX</t>
         </is>
       </c>
-      <c r="F170" s="28" t="n">
+      <c r="F170" s="6" t="n">
         <v>4666</v>
       </c>
     </row>
@@ -7076,25 +7066,25 @@
       <c r="A171" s="5" t="n">
         <v>170</v>
       </c>
-      <c r="B171" s="29" t="inlineStr">
+      <c r="B171" s="27" t="inlineStr">
         <is>
           <t>Boca de Galafre</t>
         </is>
       </c>
-      <c r="C171" s="30" t="n">
+      <c r="C171" s="28" t="n">
         <v>30</v>
       </c>
-      <c r="D171" s="29" t="inlineStr">
+      <c r="D171" s="27" t="inlineStr">
         <is>
           <t>Especialista en Gestion  Economica</t>
         </is>
       </c>
-      <c r="E171" s="31" t="inlineStr">
+      <c r="E171" s="29" t="inlineStr">
         <is>
           <t>XI</t>
         </is>
       </c>
-      <c r="F171" s="32" t="n">
+      <c r="F171" s="12" t="n">
         <v>5343</v>
       </c>
     </row>
@@ -7102,7 +7092,7 @@
       <c r="A172" s="5" t="n">
         <v>171</v>
       </c>
-      <c r="B172" s="26" t="inlineStr">
+      <c r="B172" s="25" t="inlineStr">
         <is>
           <t>Boca de Galafre</t>
         </is>
@@ -7110,17 +7100,17 @@
       <c r="C172" s="7" t="n">
         <v>31</v>
       </c>
-      <c r="D172" s="26" t="inlineStr">
+      <c r="D172" s="25" t="inlineStr">
         <is>
           <t>Técnico  en Gestión Económica</t>
         </is>
       </c>
-      <c r="E172" s="27" t="inlineStr">
+      <c r="E172" s="26" t="inlineStr">
         <is>
           <t>IX</t>
         </is>
       </c>
-      <c r="F172" s="28" t="n">
+      <c r="F172" s="6" t="n">
         <v>4666</v>
       </c>
     </row>
@@ -7128,25 +7118,25 @@
       <c r="A173" s="5" t="n">
         <v>172</v>
       </c>
-      <c r="B173" s="29" t="inlineStr">
+      <c r="B173" s="27" t="inlineStr">
         <is>
           <t>Boca de Galafre</t>
         </is>
       </c>
-      <c r="C173" s="30" t="n">
+      <c r="C173" s="28" t="n">
         <v>33</v>
       </c>
-      <c r="D173" s="29" t="inlineStr">
+      <c r="D173" s="27" t="inlineStr">
         <is>
           <t>Dependiente Gastronomico</t>
         </is>
       </c>
-      <c r="E173" s="31" t="inlineStr">
+      <c r="E173" s="29" t="inlineStr">
         <is>
           <t>VII</t>
         </is>
       </c>
-      <c r="F173" s="32" t="n">
+      <c r="F173" s="12" t="n">
         <v>4153</v>
       </c>
     </row>
@@ -7154,7 +7144,7 @@
       <c r="A174" s="5" t="n">
         <v>173</v>
       </c>
-      <c r="B174" s="26" t="inlineStr">
+      <c r="B174" s="25" t="inlineStr">
         <is>
           <t>Boca de Galafre</t>
         </is>
@@ -7162,17 +7152,17 @@
       <c r="C174" s="7" t="n">
         <v>34</v>
       </c>
-      <c r="D174" s="26" t="inlineStr">
+      <c r="D174" s="25" t="inlineStr">
         <is>
           <t>Nivel Medio Superior</t>
         </is>
       </c>
-      <c r="E174" s="27" t="inlineStr">
+      <c r="E174" s="26" t="inlineStr">
         <is>
           <t>VIII</t>
         </is>
       </c>
-      <c r="F174" s="28" t="n">
+      <c r="F174" s="6" t="n">
         <v>4402</v>
       </c>
     </row>
@@ -7180,25 +7170,25 @@
       <c r="A175" s="5" t="n">
         <v>174</v>
       </c>
-      <c r="B175" s="29" t="inlineStr">
+      <c r="B175" s="27" t="inlineStr">
         <is>
           <t>Boca de Galafre</t>
         </is>
       </c>
-      <c r="C175" s="30" t="n">
+      <c r="C175" s="28" t="n">
         <v>35</v>
       </c>
-      <c r="D175" s="29" t="inlineStr">
+      <c r="D175" s="27" t="inlineStr">
         <is>
           <t>Elaborador de Alimentos</t>
         </is>
       </c>
-      <c r="E175" s="31" t="inlineStr">
+      <c r="E175" s="29" t="inlineStr">
         <is>
           <t>VII</t>
         </is>
       </c>
-      <c r="F175" s="32" t="n">
+      <c r="F175" s="12" t="n">
         <v>4153</v>
       </c>
     </row>
@@ -7206,7 +7196,7 @@
       <c r="A176" s="5" t="n">
         <v>175</v>
       </c>
-      <c r="B176" s="26" t="inlineStr">
+      <c r="B176" s="25" t="inlineStr">
         <is>
           <t>Boca de Galafre</t>
         </is>
@@ -7214,17 +7204,17 @@
       <c r="C176" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="D176" s="26" t="inlineStr">
+      <c r="D176" s="25" t="inlineStr">
         <is>
           <t>Recepcionista Hotelero</t>
         </is>
       </c>
-      <c r="E176" s="27" t="inlineStr">
+      <c r="E176" s="26" t="inlineStr">
         <is>
           <t>VII</t>
         </is>
       </c>
-      <c r="F176" s="28" t="n">
+      <c r="F176" s="6" t="n">
         <v>4153</v>
       </c>
     </row>
@@ -7232,25 +7222,25 @@
       <c r="A177" s="5" t="n">
         <v>176</v>
       </c>
-      <c r="B177" s="29" t="inlineStr">
+      <c r="B177" s="27" t="inlineStr">
         <is>
           <t>Boca de Galafre</t>
         </is>
       </c>
-      <c r="C177" s="30" t="n">
+      <c r="C177" s="28" t="n">
         <v>38</v>
       </c>
-      <c r="D177" s="29" t="inlineStr">
+      <c r="D177" s="27" t="inlineStr">
         <is>
           <t>Camarera de Habitaciones</t>
         </is>
       </c>
-      <c r="E177" s="31" t="inlineStr">
+      <c r="E177" s="29" t="inlineStr">
         <is>
           <t>VII</t>
         </is>
       </c>
-      <c r="F177" s="32" t="n">
+      <c r="F177" s="12" t="n">
         <v>4153</v>
       </c>
     </row>
@@ -7258,7 +7248,7 @@
       <c r="A178" s="5" t="n">
         <v>177</v>
       </c>
-      <c r="B178" s="26" t="inlineStr">
+      <c r="B178" s="25" t="inlineStr">
         <is>
           <t>Boca de Galafre</t>
         </is>
@@ -7266,17 +7256,17 @@
       <c r="C178" s="7" t="n">
         <v>39</v>
       </c>
-      <c r="D178" s="26" t="inlineStr">
+      <c r="D178" s="25" t="inlineStr">
         <is>
           <t>Auxiliar General de  Servicios</t>
         </is>
       </c>
-      <c r="E178" s="27" t="inlineStr">
+      <c r="E178" s="26" t="inlineStr">
         <is>
           <t>IV</t>
         </is>
       </c>
-      <c r="F178" s="28" t="n">
+      <c r="F178" s="6" t="n">
         <v>3487</v>
       </c>
     </row>
@@ -7284,25 +7274,25 @@
       <c r="A179" s="5" t="n">
         <v>178</v>
       </c>
-      <c r="B179" s="29" t="inlineStr">
+      <c r="B179" s="27" t="inlineStr">
         <is>
           <t>Boca de Galafre</t>
         </is>
       </c>
-      <c r="C179" s="30" t="n">
+      <c r="C179" s="28" t="n">
         <v>40</v>
       </c>
-      <c r="D179" s="29" t="inlineStr">
+      <c r="D179" s="27" t="inlineStr">
         <is>
           <t>Técnico en Recreación y Animación JB</t>
         </is>
       </c>
-      <c r="E179" s="31" t="inlineStr">
+      <c r="E179" s="29" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="F179" s="32" t="n">
+      <c r="F179" s="12" t="n">
         <v>4993</v>
       </c>
     </row>
@@ -7310,7 +7300,7 @@
       <c r="A180" s="5" t="n">
         <v>179</v>
       </c>
-      <c r="B180" s="26" t="inlineStr">
+      <c r="B180" s="25" t="inlineStr">
         <is>
           <t>Boca de Galafre</t>
         </is>
@@ -7318,17 +7308,17 @@
       <c r="C180" s="7" t="n">
         <v>41</v>
       </c>
-      <c r="D180" s="26" t="inlineStr">
+      <c r="D180" s="25" t="inlineStr">
         <is>
           <t>Técnico en Recreación y Animación</t>
         </is>
       </c>
-      <c r="E180" s="27" t="inlineStr">
+      <c r="E180" s="26" t="inlineStr">
         <is>
           <t>VII</t>
         </is>
       </c>
-      <c r="F180" s="28" t="n">
+      <c r="F180" s="6" t="n">
         <v>4153</v>
       </c>
     </row>
@@ -7336,25 +7326,25 @@
       <c r="A181" s="5" t="n">
         <v>180</v>
       </c>
-      <c r="B181" s="29" t="inlineStr">
+      <c r="B181" s="27" t="inlineStr">
         <is>
           <t>Boca de Galafre</t>
         </is>
       </c>
-      <c r="C181" s="30" t="n">
+      <c r="C181" s="28" t="n">
         <v>43</v>
       </c>
-      <c r="D181" s="29" t="inlineStr">
+      <c r="D181" s="27" t="inlineStr">
         <is>
           <t>Encargado de Almacén</t>
         </is>
       </c>
-      <c r="E181" s="31" t="inlineStr">
+      <c r="E181" s="29" t="inlineStr">
         <is>
           <t>VII</t>
         </is>
       </c>
-      <c r="F181" s="32" t="n">
+      <c r="F181" s="12" t="n">
         <v>4153</v>
       </c>
     </row>
@@ -7362,7 +7352,7 @@
       <c r="A182" s="5" t="n">
         <v>181</v>
       </c>
-      <c r="B182" s="26" t="inlineStr">
+      <c r="B182" s="25" t="inlineStr">
         <is>
           <t>Boca de Galafre</t>
         </is>
@@ -7370,17 +7360,17 @@
       <c r="C182" s="7" t="n">
         <v>44</v>
       </c>
-      <c r="D182" s="26" t="inlineStr">
+      <c r="D182" s="25" t="inlineStr">
         <is>
           <t>Operario de Mant. Y Serv, Tec.</t>
         </is>
       </c>
-      <c r="E182" s="27" t="inlineStr">
+      <c r="E182" s="26" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="F182" s="28" t="n">
+      <c r="F182" s="6" t="n">
         <v>3696</v>
       </c>
     </row>
@@ -7388,25 +7378,25 @@
       <c r="A183" s="5" t="n">
         <v>182</v>
       </c>
-      <c r="B183" s="29" t="inlineStr">
+      <c r="B183" s="27" t="inlineStr">
         <is>
           <t>Boca de Galafre</t>
         </is>
       </c>
-      <c r="C183" s="30" t="n">
+      <c r="C183" s="28" t="n">
         <v>46</v>
       </c>
-      <c r="D183" s="29" t="inlineStr">
+      <c r="D183" s="27" t="inlineStr">
         <is>
           <t>Jefes de Grupo de Seguridad Interna</t>
         </is>
       </c>
-      <c r="E183" s="31" t="inlineStr">
+      <c r="E183" s="29" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="F183" s="32" t="n">
+      <c r="F183" s="12" t="n">
         <v>4993</v>
       </c>
     </row>
@@ -7414,7 +7404,7 @@
       <c r="A184" s="5" t="n">
         <v>183</v>
       </c>
-      <c r="B184" s="26" t="inlineStr">
+      <c r="B184" s="25" t="inlineStr">
         <is>
           <t>Boca de Galafre</t>
         </is>
@@ -7422,17 +7412,17 @@
       <c r="C184" s="7" t="n">
         <v>47</v>
       </c>
-      <c r="D184" s="26" t="inlineStr">
+      <c r="D184" s="25" t="inlineStr">
         <is>
           <t>Agente de Seguridad y Protección</t>
         </is>
       </c>
-      <c r="E184" s="27" t="inlineStr">
+      <c r="E184" s="26" t="inlineStr">
         <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="F184" s="28" t="n">
+      <c r="F184" s="6" t="n">
         <v>3918</v>
       </c>
     </row>
@@ -7455,72 +7445,72 @@
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1">
-      <c r="A1" s="33" t="inlineStr">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>METODOLOGÍA Y FUENTES</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="34" t="inlineStr"/>
+      <c r="A2" s="31" t="inlineStr"/>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="34" t="inlineStr">
-        <is>
-          <t>1. Salario mínimo: $3,210.00 mensuales, Resolución 14/2026 del MTSS (GOC-2026-393-O60, Gaceta Oficial No. 60 Ordinaria de 17/07/2026, p. 1839).</t>
+      <c r="A3" s="31" t="inlineStr">
+        <is>
+          <t>1. Salario mínimo: $ 3,210.00 mensuales, Resolución 14/2026 del MTSS (GOC-2026-393-O60, Gaceta Oficial No. 60 Ordinaria de 17/07/2026, p. 1839).</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="34" t="inlineStr">
+      <c r="A4" s="31" t="inlineStr">
         <is>
           <t>2. Escala oficial de 32 grupos (I a XXXII), régimen de 44 horas: Resolución 15/2026 (GOC-2026-394-O60), pp. 1839-1840. Los valores son los publicados oficialmente (redondeados).</t>
         </is>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="34" t="inlineStr">
+      <c r="A5" s="31" t="inlineStr">
         <is>
           <t>3. Escala anterior: Resolución 29/2020, leída de TES/Salariales/Escala 3210_OK.xlsx.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="34" t="inlineStr">
+      <c r="A6" s="31" t="inlineStr">
         <is>
           <t>4. Columna “Salario propuesto Plantilla Decreto 87”: extraída del libro “propuesta de plantilla por la resolucion 87.xls” (9 hojas de cargos). Por cada planta se localiza el encabezado G.E.A/G.E.P (grupo escala propuesto) y se toma el salario de la columna siguiente; cuando un grupo aparece con varios salarios, se adopta el valor mayoritario.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="34" t="inlineStr">
+      <c r="A7" s="31" t="inlineStr">
         <is>
           <t>5. Grupos sin propuesta en la plantilla: I, II, III y XIX al XXXII (la plantilla solo propone cargos entre los grupos IV y XVIII).</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="34" t="inlineStr">
+      <c r="A8" s="31" t="inlineStr">
         <is>
           <t>6. La hoja “Escala por correlacion” replica el cálculo automático (salario_n = correlación_n × salario_n-1) con fórmulas vivas de Excel; difiere levemente de la escala oficial porque esta última está redondeada.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="34" t="inlineStr"/>
+      <c r="A9" s="31" t="inlineStr"/>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="33" t="inlineStr">
+      <c r="A10" s="30" t="inlineStr">
         <is>
           <t>ANOMALÍAS DETECTADAS EN LA PLANTILLA (.xls)</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="34" t="inlineStr"/>
+      <c r="A11" s="31" t="inlineStr"/>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="34" t="inlineStr">
+      <c r="A12" s="31" t="inlineStr">
         <is>
           <t>LENGUAJE DE PROGRAMACIÓN UTILIZADO: Python 3 — librerías xlrd (lectura del .xls heredado), openpyxl (Excel con fórmulas/estilos) y fpdf2 (PDF). Es la opción más adecuada porque lee formatos legacy, permite auditoría registro a registro, se re-ejecuta sin intervención manual y genera ambos formatos de salida con un único código mantenible.</t>
         </is>
@@ -7537,7 +7527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -7550,20 +7540,20 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="35" t="inlineStr">
+      <c r="A1" s="32" t="inlineStr">
         <is>
           <t>TRAZABILIDAD DE FUENTES · CAPITAL HUMANO</t>
         </is>
       </c>
-      <c r="B1" s="35" t="n"/>
-      <c r="C1" s="35" t="n"/>
-      <c r="D1" s="35" t="n"/>
-      <c r="E1" s="35" t="n"/>
-      <c r="F1" s="35" t="n"/>
-      <c r="G1" s="35" t="n"/>
+      <c r="B1" s="32" t="n"/>
+      <c r="C1" s="32" t="n"/>
+      <c r="D1" s="32" t="n"/>
+      <c r="E1" s="32" t="n"/>
+      <c r="F1" s="32" t="n"/>
+      <c r="G1" s="32" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="36" t="inlineStr">
+      <c r="A2" s="33" t="inlineStr">
         <is>
           <t>Versión de la aplicación</t>
         </is>
@@ -7575,7 +7565,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="36" t="inlineStr">
+      <c r="A3" s="33" t="inlineStr">
         <is>
           <t>Integridad del manifiesto</t>
         </is>
@@ -7587,308 +7577,343 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="36" t="inlineStr">
+      <c r="A4" s="33" t="inlineStr">
         <is>
           <t>Verificación UTC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:52:01+00:00</t>
+          <t>2026-10-29T02:29:55+00:00</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="37" t="inlineStr">
+      <c r="A5" s="34" t="inlineStr">
         <is>
           <t>SHA-256 compara los bytes con el manifiesto versionado; no sustituye revisión normativa ni firma digital.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="36" customHeight="1">
-      <c r="A6" s="38" t="inlineStr">
+      <c r="A6" s="35" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B6" s="38" t="inlineStr">
+      <c r="B6" s="35" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
-      <c r="C6" s="38" t="inlineStr">
+      <c r="C6" s="35" t="inlineStr">
         <is>
           <t>Ruta del repositorio</t>
         </is>
       </c>
-      <c r="D6" s="38" t="inlineStr">
+      <c r="D6" s="35" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="E6" s="38" t="inlineStr">
+      <c r="E6" s="35" t="inlineStr">
         <is>
           <t>SHA-256 aprobado</t>
         </is>
       </c>
-      <c r="F6" s="38" t="inlineStr">
+      <c r="F6" s="35" t="inlineStr">
         <is>
           <t>SHA-256 actual</t>
         </is>
       </c>
-      <c r="G6" s="38" t="inlineStr">
+      <c r="G6" s="35" t="inlineStr">
         <is>
           <t>Tamaño (bytes)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="39" t="inlineStr">
+      <c r="A7" s="36" t="inlineStr">
         <is>
           <t>plantilla_res87</t>
         </is>
       </c>
-      <c r="B7" s="40" t="inlineStr">
+      <c r="B7" s="37" t="inlineStr">
         <is>
           <t>Plantilla de cargos · propuesta Resolución 87</t>
         </is>
       </c>
-      <c r="C7" s="40" t="inlineStr">
+      <c r="C7" s="37" t="inlineStr">
         <is>
           <t>Nueva Estructura de Plantilla/Organigrama/propuesta de plantilla por la resolucion 87.xls</t>
         </is>
       </c>
-      <c r="D7" s="41" t="inlineStr">
+      <c r="D7" s="38" t="inlineStr">
         <is>
           <t>VERIFICADA</t>
         </is>
       </c>
-      <c r="E7" s="42" t="inlineStr">
+      <c r="E7" s="39" t="inlineStr">
         <is>
           <t>5542e23b705462738e66a82ed1aec8d60727c6d1352438266e620878ab63e473</t>
         </is>
       </c>
-      <c r="F7" s="42" t="inlineStr">
+      <c r="F7" s="39" t="inlineStr">
         <is>
           <t>5542e23b705462738e66a82ed1aec8d60727c6d1352438266e620878ab63e473</t>
         </is>
       </c>
-      <c r="G7" s="39" t="n">
+      <c r="G7" s="36" t="n">
         <v>2780672</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="39" t="inlineStr">
+      <c r="A8" s="36" t="inlineStr">
         <is>
           <t>escala_res29</t>
         </is>
       </c>
-      <c r="B8" s="40" t="inlineStr">
+      <c r="B8" s="37" t="inlineStr">
         <is>
           <t>Escala histórica · Resolución 29/2020</t>
         </is>
       </c>
-      <c r="C8" s="40" t="inlineStr">
+      <c r="C8" s="37" t="inlineStr">
         <is>
           <t>TES/Salariales/Escala 3210_OK.xlsx</t>
         </is>
       </c>
-      <c r="D8" s="41" t="inlineStr">
+      <c r="D8" s="38" t="inlineStr">
         <is>
           <t>VERIFICADA</t>
         </is>
       </c>
-      <c r="E8" s="42" t="inlineStr">
+      <c r="E8" s="39" t="inlineStr">
         <is>
           <t>fbf1764dd6d77a5845dbbd01a7453e119915feb798dc7b43f25e431f67217d01</t>
         </is>
       </c>
-      <c r="F8" s="42" t="inlineStr">
+      <c r="F8" s="39" t="inlineStr">
         <is>
           <t>fbf1764dd6d77a5845dbbd01a7453e119915feb798dc7b43f25e431f67217d01</t>
         </is>
       </c>
-      <c r="G8" s="39" t="n">
+      <c r="G8" s="36" t="n">
         <v>13968</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="39" t="inlineStr">
+      <c r="A9" s="36" t="inlineStr">
         <is>
           <t>gaceta_2026</t>
         </is>
       </c>
-      <c r="B9" s="40" t="inlineStr">
+      <c r="B9" s="37" t="inlineStr">
         <is>
           <t>Gaceta Oficial · Resoluciones 14/2026 y 15/2026</t>
         </is>
       </c>
-      <c r="C9" s="40" t="inlineStr">
+      <c r="C9" s="37" t="inlineStr">
         <is>
           <t>TES/Salariales/goc-2026-o60.pdf</t>
         </is>
       </c>
-      <c r="D9" s="41" t="inlineStr">
+      <c r="D9" s="38" t="inlineStr">
         <is>
           <t>VERIFICADA</t>
         </is>
       </c>
-      <c r="E9" s="42" t="inlineStr">
+      <c r="E9" s="39" t="inlineStr">
         <is>
           <t>7dfe261ae1db5de5ceee1e9ebe141693a5a1ca474809158960c6bd94a2c0a1e1</t>
         </is>
       </c>
-      <c r="F9" s="42" t="inlineStr">
+      <c r="F9" s="39" t="inlineStr">
         <is>
           <t>7dfe261ae1db5de5ceee1e9ebe141693a5a1ca474809158960c6bd94a2c0a1e1</t>
         </is>
       </c>
-      <c r="G9" s="39" t="n">
+      <c r="G9" s="36" t="n">
         <v>1104320</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="39" t="inlineStr">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>motor_calculo</t>
         </is>
       </c>
-      <c r="B10" s="40" t="inlineStr">
+      <c r="B10" s="37" t="inlineStr">
         <is>
           <t>Código de extracción y cálculo</t>
         </is>
       </c>
-      <c r="C10" s="40" t="inlineStr">
+      <c r="C10" s="37" t="inlineStr">
         <is>
           <t>TES/Salariales/Nueva Escala 3210/generar_escala.py</t>
         </is>
       </c>
-      <c r="D10" s="41" t="inlineStr">
+      <c r="D10" s="38" t="inlineStr">
         <is>
           <t>VERIFICADA</t>
         </is>
       </c>
-      <c r="E10" s="42" t="inlineStr">
-        <is>
-          <t>11da9e812e996110373df74759d9eb17c49a7fce58fa00e5d7c4c24b1d05adbf</t>
-        </is>
-      </c>
-      <c r="F10" s="42" t="inlineStr">
-        <is>
-          <t>11da9e812e996110373df74759d9eb17c49a7fce58fa00e5d7c4c24b1d05adbf</t>
-        </is>
-      </c>
-      <c r="G10" s="39" t="n">
-        <v>43127</v>
+      <c r="E10" s="39" t="inlineStr">
+        <is>
+          <t>de0bf4986d5886dd0a51ede02a663fa0f5a0955b0156f13083396380d11c05b1</t>
+        </is>
+      </c>
+      <c r="F10" s="39" t="inlineStr">
+        <is>
+          <t>de0bf4986d5886dd0a51ede02a663fa0f5a0955b0156f13083396380d11c05b1</t>
+        </is>
+      </c>
+      <c r="G10" s="36" t="n">
+        <v>51656</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="39" t="inlineStr">
+      <c r="A11" s="36" t="inlineStr">
         <is>
           <t>interfaz_app</t>
         </is>
       </c>
-      <c r="B11" s="40" t="inlineStr">
+      <c r="B11" s="37" t="inlineStr">
         <is>
           <t>Código de la aplicación y exportadores</t>
         </is>
       </c>
-      <c r="C11" s="40" t="inlineStr">
+      <c r="C11" s="37" t="inlineStr">
         <is>
           <t>TES/Salariales/Nueva Escala 3210/app_escala.py</t>
         </is>
       </c>
-      <c r="D11" s="41" t="inlineStr">
+      <c r="D11" s="38" t="inlineStr">
         <is>
           <t>VERIFICADA</t>
         </is>
       </c>
-      <c r="E11" s="42" t="inlineStr">
-        <is>
-          <t>749b33588504192a5ccf2d062bcb689e7498f75547c355918252216bcec97ef1</t>
-        </is>
-      </c>
-      <c r="F11" s="42" t="inlineStr">
-        <is>
-          <t>749b33588504192a5ccf2d062bcb689e7498f75547c355918252216bcec97ef1</t>
-        </is>
-      </c>
-      <c r="G11" s="39" t="n">
-        <v>75282</v>
+      <c r="E11" s="39" t="inlineStr">
+        <is>
+          <t>96d4aa8d3cfdaeee40d8a154a7a324e78ebe2ec3e81867d7a02f3ec524ad5436</t>
+        </is>
+      </c>
+      <c r="F11" s="39" t="inlineStr">
+        <is>
+          <t>96d4aa8d3cfdaeee40d8a154a7a324e78ebe2ec3e81867d7a02f3ec524ad5436</t>
+        </is>
+      </c>
+      <c r="G11" s="36" t="n">
+        <v>94529</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="39" t="inlineStr">
+      <c r="A12" s="36" t="inlineStr">
+        <is>
+          <t>interfaz_traducciones</t>
+        </is>
+      </c>
+      <c r="B12" s="37" t="inlineStr">
+        <is>
+          <t>Traducciones de interfaz</t>
+        </is>
+      </c>
+      <c r="C12" s="37" t="inlineStr">
+        <is>
+          <t>TES/Salariales/Nueva Escala 3210/i18n.py</t>
+        </is>
+      </c>
+      <c r="D12" s="38" t="inlineStr">
+        <is>
+          <t>VERIFICADA</t>
+        </is>
+      </c>
+      <c r="E12" s="39" t="inlineStr">
+        <is>
+          <t>5fca7870d83ad14bf547298513d6f08bad9cc3a752da1c5e328d7f8889dd3d62</t>
+        </is>
+      </c>
+      <c r="F12" s="39" t="inlineStr">
+        <is>
+          <t>5fca7870d83ad14bf547298513d6f08bad9cc3a752da1c5e328d7f8889dd3d62</t>
+        </is>
+      </c>
+      <c r="G12" s="36" t="n">
+        <v>31418</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="36" t="inlineStr">
         <is>
           <t>actualizador_manifest</t>
         </is>
       </c>
-      <c r="B12" s="40" t="inlineStr">
+      <c r="B13" s="37" t="inlineStr">
         <is>
           <t>Herramienta de actualización del manifiesto</t>
         </is>
       </c>
-      <c r="C12" s="40" t="inlineStr">
+      <c r="C13" s="37" t="inlineStr">
         <is>
           <t>tools/actualizar_manifiesto_fuentes.py</t>
         </is>
       </c>
-      <c r="D12" s="41" t="inlineStr">
+      <c r="D13" s="38" t="inlineStr">
         <is>
           <t>VERIFICADA</t>
         </is>
       </c>
-      <c r="E12" s="42" t="inlineStr">
+      <c r="E13" s="39" t="inlineStr">
         <is>
           <t>6b820ded8d9c01129c0d5fbfa223e43039be6126db75809c15d5ea675f2c5e85</t>
         </is>
       </c>
-      <c r="F12" s="42" t="inlineStr">
+      <c r="F13" s="39" t="inlineStr">
         <is>
           <t>6b820ded8d9c01129c0d5fbfa223e43039be6126db75809c15d5ea675f2c5e85</t>
         </is>
       </c>
-      <c r="G12" s="39" t="n">
+      <c r="G13" s="36" t="n">
         <v>865</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="39" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="36" t="inlineStr">
         <is>
           <t>verificador_paquete</t>
         </is>
       </c>
-      <c r="B13" s="40" t="inlineStr">
+      <c r="B14" s="37" t="inlineStr">
         <is>
           <t>Verificador offline de paquetes de exportación</t>
         </is>
       </c>
-      <c r="C13" s="40" t="inlineStr">
+      <c r="C14" s="37" t="inlineStr">
         <is>
           <t>tools/verificar_paquete_exportacion.py</t>
         </is>
       </c>
-      <c r="D13" s="41" t="inlineStr">
+      <c r="D14" s="38" t="inlineStr">
         <is>
           <t>VERIFICADA</t>
         </is>
       </c>
-      <c r="E13" s="42" t="inlineStr">
+      <c r="E14" s="39" t="inlineStr">
         <is>
           <t>0633c843d086b003c6ebaffafdd2c88abd2b463bcf912c80c0ba9a607ec5cbdb</t>
         </is>
       </c>
-      <c r="F13" s="42" t="inlineStr">
+      <c r="F14" s="39" t="inlineStr">
         <is>
           <t>0633c843d086b003c6ebaffafdd2c88abd2b463bcf912c80c0ba9a607ec5cbdb</t>
         </is>
       </c>
-      <c r="G13" s="39" t="n">
+      <c r="G14" s="36" t="n">
         <v>8341</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A6:G13"/>
+  <autoFilter ref="A6:G14"/>
   <mergeCells count="2">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A5:G5"/>
